--- a/development/MS/spec/MSBB/Panel/MSBBPA0010_SlsSchdSrch.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBPA0010_SlsSchdSrch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FA13E5-AACD-4A1F-B6FF-86335A57D92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68A2A08-5D4A-427D-BA72-5CCD07B03A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="678">
   <si>
     <t>*</t>
   </si>
@@ -2192,22 +2192,10 @@
     <t>Delivery destination name</t>
   </si>
   <si>
-    <t>PIC cd.</t>
-  </si>
-  <si>
-    <t>PIC name</t>
-  </si>
-  <si>
     <t>Customer item cd.</t>
   </si>
   <si>
     <t>Customer item name</t>
-  </si>
-  <si>
-    <t>Canceling reason cd.</t>
-  </si>
-  <si>
-    <t>Canceling reason name</t>
   </si>
   <si>
     <t>Delivery destination classification 1</t>
@@ -2650,6 +2638,12 @@
   </si>
   <si>
     <t>zoho_sls_schd_no</t>
+  </si>
+  <si>
+    <t>Project manager user cd.</t>
+  </si>
+  <si>
+    <t>Project manager user name</t>
   </si>
 </sst>
 </file>
@@ -3436,6 +3430,84 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3497,84 +3569,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4057,7 +4051,7 @@
       </c>
       <c r="H2" s="50"/>
       <c r="I2" s="45" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="J2" s="46"/>
       <c r="K2" s="48" t="s">
@@ -4110,7 +4104,7 @@
       </c>
       <c r="H3" s="50"/>
       <c r="I3" s="45" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="J3" s="46"/>
       <c r="K3" s="48" t="s">
@@ -4149,7 +4143,7 @@
       </c>
       <c r="H4" s="50"/>
       <c r="I4" s="45" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="J4" s="46"/>
       <c r="K4" s="48" t="s">
@@ -4224,7 +4218,7 @@
         <v>302</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="F6" s="49"/>
       <c r="G6" s="49"/>
@@ -4374,7 +4368,7 @@
         <v>310</v>
       </c>
       <c r="AH8" s="23" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="AI8" s="7"/>
       <c r="AJ8" s="13" t="s">
@@ -4490,10 +4484,10 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH10" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AI10" s="4"/>
       <c r="AJ10" s="8"/>
@@ -4559,10 +4553,10 @@
     <row r="12" spans="1:36" ht="40.5">
       <c r="A12" s="5"/>
       <c r="AG12" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH12" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ12" s="9"/>
     </row>
@@ -4627,10 +4621,10 @@
     <row r="14" spans="1:36" ht="40.5">
       <c r="A14" s="5"/>
       <c r="AG14" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH14" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ14" s="9"/>
     </row>
@@ -4826,10 +4820,10 @@
     <row r="19" spans="1:36" ht="40.5">
       <c r="A19" s="5"/>
       <c r="AG19" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH19" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ19" s="9"/>
     </row>
@@ -5074,10 +5068,10 @@
     <row r="25" spans="1:36" ht="40.5">
       <c r="A25" s="5"/>
       <c r="AG25" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH25" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ25" s="9"/>
     </row>
@@ -5177,10 +5171,10 @@
     <row r="28" spans="1:36" ht="40.5">
       <c r="A28" s="5"/>
       <c r="AG28" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH28" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ28" s="9"/>
     </row>
@@ -5280,10 +5274,10 @@
     <row r="31" spans="1:36" ht="40.5">
       <c r="A31" s="5"/>
       <c r="AG31" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH31" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ31" s="9"/>
     </row>
@@ -5383,10 +5377,10 @@
     <row r="34" spans="1:36" ht="40.5">
       <c r="A34" s="5"/>
       <c r="AG34" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH34" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ34" s="9"/>
     </row>
@@ -5556,7 +5550,7 @@
         <v>521</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="G39" s="18" t="s">
         <v>14</v>
@@ -5613,7 +5607,7 @@
         <v>522</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="G40" s="23" t="s">
         <v>14</v>
@@ -5724,13 +5718,13 @@
         <v>39</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="H42" s="23"/>
       <c r="I42" s="23" t="s">
@@ -5781,10 +5775,10 @@
         <v>40</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>15</v>
@@ -5838,13 +5832,13 @@
         <v>275</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="H44" s="23"/>
       <c r="I44" s="23" t="s">
@@ -5895,10 +5889,10 @@
         <v>276</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="G45" s="23" t="s">
         <v>15</v>
@@ -5949,13 +5943,13 @@
       <c r="B46" s="23"/>
       <c r="C46" s="23"/>
       <c r="D46" s="23" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="G46" s="23" t="s">
         <v>13</v>
@@ -6006,13 +6000,13 @@
       <c r="B47" s="23"/>
       <c r="C47" s="23"/>
       <c r="D47" s="23" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E47" s="24" t="s">
         <v>526</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G47" s="23" t="s">
         <v>13</v>
@@ -6073,13 +6067,13 @@
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
       <c r="D48" s="23" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E48" s="24" t="s">
         <v>527</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G48" s="23" t="s">
         <v>13</v>
@@ -6133,10 +6127,10 @@
         <v>166</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="G49" s="23" t="s">
         <v>46</v>
@@ -6196,10 +6190,10 @@
         <v>167</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="G50" s="23"/>
       <c r="H50" s="23"/>
@@ -6251,13 +6245,13 @@
         <v>44</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>532</v>
+        <v>623</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="H51" s="23"/>
       <c r="I51" s="23" t="s">
@@ -6314,10 +6308,10 @@
         <v>45</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>533</v>
+        <v>624</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="G52" s="23"/>
       <c r="H52" s="23"/>
@@ -6366,13 +6360,13 @@
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
       <c r="D53" s="23" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="G53" s="23" t="s">
         <v>47</v>
@@ -6429,13 +6423,13 @@
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
       <c r="D54" s="23" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="F54" s="23" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="G54" s="23"/>
       <c r="H54" s="23"/>
@@ -6484,16 +6478,16 @@
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>532</v>
+        <v>610</v>
       </c>
       <c r="F55" s="23" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G55" s="23" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="H55" s="23"/>
       <c r="I55" s="23" t="s">
@@ -6547,13 +6541,13 @@
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
       <c r="D56" s="23" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>533</v>
+        <v>611</v>
       </c>
       <c r="F56" s="23" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="G56" s="23"/>
       <c r="H56" s="23"/>
@@ -6602,16 +6596,16 @@
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
       <c r="D57" s="23" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>532</v>
+        <v>676</v>
       </c>
       <c r="F57" s="23" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="H57" s="23"/>
       <c r="I57" s="23" t="s">
@@ -6665,13 +6659,13 @@
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
       <c r="D58" s="23" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>533</v>
+        <v>677</v>
       </c>
       <c r="F58" s="23" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="G58" s="23"/>
       <c r="H58" s="23"/>
@@ -6720,16 +6714,16 @@
       <c r="B59" s="23"/>
       <c r="C59" s="23"/>
       <c r="D59" s="23" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>532</v>
+        <v>615</v>
       </c>
       <c r="F59" s="23" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="H59" s="23"/>
       <c r="I59" s="23" t="s">
@@ -6783,13 +6777,13 @@
       <c r="B60" s="23"/>
       <c r="C60" s="23"/>
       <c r="D60" s="23" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>533</v>
+        <v>616</v>
       </c>
       <c r="F60" s="23" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G60" s="23"/>
       <c r="H60" s="23"/>
@@ -6898,7 +6892,7 @@
       </c>
       <c r="E62" s="24"/>
       <c r="F62" s="23" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="G62" s="23"/>
       <c r="H62" s="23"/>
@@ -7244,7 +7238,7 @@
         <v>182</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F70" s="23" t="s">
         <v>221</v>
@@ -7291,7 +7285,7 @@
         <v>183</v>
       </c>
       <c r="E71" s="24" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F71" s="23" t="s">
         <v>222</v>
@@ -7338,7 +7332,7 @@
         <v>184</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F72" s="23" t="s">
         <v>223</v>
@@ -7426,7 +7420,7 @@
         <v>186</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F74" s="23" t="s">
         <v>224</v>
@@ -7473,7 +7467,7 @@
         <v>187</v>
       </c>
       <c r="E75" s="24" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F75" s="23" t="s">
         <v>225</v>
@@ -7520,7 +7514,7 @@
         <v>188</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F76" s="23" t="s">
         <v>226</v>
@@ -7608,7 +7602,7 @@
         <v>190</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F78" s="23" t="s">
         <v>228</v>
@@ -7655,7 +7649,7 @@
         <v>191</v>
       </c>
       <c r="E79" s="24" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F79" s="23" t="s">
         <v>229</v>
@@ -7702,7 +7696,7 @@
         <v>192</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F80" s="23" t="s">
         <v>230</v>
@@ -7790,7 +7784,7 @@
         <v>194</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F82" s="23" t="s">
         <v>232</v>
@@ -7837,7 +7831,7 @@
         <v>195</v>
       </c>
       <c r="E83" s="24" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="F83" s="23" t="s">
         <v>233</v>
@@ -7884,7 +7878,7 @@
         <v>196</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F84" s="23" t="s">
         <v>234</v>
@@ -7972,7 +7966,7 @@
         <v>198</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F86" s="23" t="s">
         <v>236</v>
@@ -8019,7 +8013,7 @@
         <v>199</v>
       </c>
       <c r="E87" s="24" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="F87" s="23" t="s">
         <v>237</v>
@@ -8066,7 +8060,7 @@
         <v>200</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F88" s="23" t="s">
         <v>238</v>
@@ -8154,7 +8148,7 @@
         <v>202</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F90" s="23" t="s">
         <v>240</v>
@@ -8201,7 +8195,7 @@
         <v>203</v>
       </c>
       <c r="E91" s="24" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F91" s="23" t="s">
         <v>241</v>
@@ -8248,7 +8242,7 @@
         <v>204</v>
       </c>
       <c r="E92" s="24" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F92" s="23" t="s">
         <v>242</v>
@@ -8336,7 +8330,7 @@
         <v>206</v>
       </c>
       <c r="E94" s="24" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F94" s="23" t="s">
         <v>244</v>
@@ -8383,7 +8377,7 @@
         <v>207</v>
       </c>
       <c r="E95" s="24" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F95" s="23" t="s">
         <v>245</v>
@@ -8430,7 +8424,7 @@
         <v>208</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F96" s="23" t="s">
         <v>246</v>
@@ -8518,7 +8512,7 @@
         <v>210</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F98" s="23" t="s">
         <v>247</v>
@@ -8565,7 +8559,7 @@
         <v>211</v>
       </c>
       <c r="E99" s="24" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F99" s="23" t="s">
         <v>248</v>
@@ -8612,7 +8606,7 @@
         <v>212</v>
       </c>
       <c r="E100" s="24" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F100" s="23" t="s">
         <v>249</v>
@@ -8700,7 +8694,7 @@
         <v>214</v>
       </c>
       <c r="E102" s="24" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F102" s="23" t="s">
         <v>251</v>
@@ -8747,7 +8741,7 @@
         <v>215</v>
       </c>
       <c r="E103" s="24" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F103" s="23" t="s">
         <v>252</v>
@@ -8794,7 +8788,7 @@
         <v>216</v>
       </c>
       <c r="E104" s="24" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F104" s="23" t="s">
         <v>253</v>
@@ -8882,7 +8876,7 @@
         <v>218</v>
       </c>
       <c r="E106" s="24" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F106" s="23" t="s">
         <v>254</v>
@@ -8929,7 +8923,7 @@
         <v>219</v>
       </c>
       <c r="E107" s="24" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="F107" s="23" t="s">
         <v>255</v>
@@ -8976,7 +8970,7 @@
         <v>220</v>
       </c>
       <c r="E108" s="24" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="F108" s="23" t="s">
         <v>256</v>
@@ -9120,7 +9114,7 @@
         <v>52</v>
       </c>
       <c r="E111" s="24" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F111" s="23" t="s">
         <v>49</v>
@@ -9167,7 +9161,7 @@
         <v>53</v>
       </c>
       <c r="E112" s="24" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F112" s="23" t="s">
         <v>50</v>
@@ -9214,7 +9208,7 @@
         <v>54</v>
       </c>
       <c r="E113" s="24" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="F113" s="23" t="s">
         <v>51</v>
@@ -9302,7 +9296,7 @@
         <v>122</v>
       </c>
       <c r="E115" s="24" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="F115" s="23" t="s">
         <v>55</v>
@@ -9349,7 +9343,7 @@
         <v>83</v>
       </c>
       <c r="E116" s="24" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="F116" s="23" t="s">
         <v>56</v>
@@ -9396,7 +9390,7 @@
         <v>84</v>
       </c>
       <c r="E117" s="24" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="F117" s="23" t="s">
         <v>57</v>
@@ -9484,7 +9478,7 @@
         <v>86</v>
       </c>
       <c r="E119" s="24" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F119" s="23" t="s">
         <v>58</v>
@@ -9531,7 +9525,7 @@
         <v>87</v>
       </c>
       <c r="E120" s="24" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F120" s="23" t="s">
         <v>59</v>
@@ -9578,7 +9572,7 @@
         <v>88</v>
       </c>
       <c r="E121" s="24" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F121" s="23" t="s">
         <v>60</v>
@@ -9666,7 +9660,7 @@
         <v>90</v>
       </c>
       <c r="E123" s="24" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F123" s="23" t="s">
         <v>61</v>
@@ -9713,7 +9707,7 @@
         <v>91</v>
       </c>
       <c r="E124" s="24" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="F124" s="23" t="s">
         <v>62</v>
@@ -9760,7 +9754,7 @@
         <v>92</v>
       </c>
       <c r="E125" s="24" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F125" s="23" t="s">
         <v>63</v>
@@ -9848,7 +9842,7 @@
         <v>94</v>
       </c>
       <c r="E127" s="24" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F127" s="23" t="s">
         <v>64</v>
@@ -9895,7 +9889,7 @@
         <v>95</v>
       </c>
       <c r="E128" s="24" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="F128" s="23" t="s">
         <v>65</v>
@@ -9942,7 +9936,7 @@
         <v>96</v>
       </c>
       <c r="E129" s="24" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F129" s="23" t="s">
         <v>66</v>
@@ -10030,7 +10024,7 @@
         <v>98</v>
       </c>
       <c r="E131" s="24" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F131" s="23" t="s">
         <v>67</v>
@@ -10077,7 +10071,7 @@
         <v>99</v>
       </c>
       <c r="E132" s="24" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F132" s="23" t="s">
         <v>68</v>
@@ -10124,7 +10118,7 @@
         <v>100</v>
       </c>
       <c r="E133" s="24" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="F133" s="23" t="s">
         <v>69</v>
@@ -10212,7 +10206,7 @@
         <v>102</v>
       </c>
       <c r="E135" s="24" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F135" s="23" t="s">
         <v>70</v>
@@ -10259,7 +10253,7 @@
         <v>103</v>
       </c>
       <c r="E136" s="24" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F136" s="23" t="s">
         <v>71</v>
@@ -10306,7 +10300,7 @@
         <v>104</v>
       </c>
       <c r="E137" s="24" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F137" s="23" t="s">
         <v>72</v>
@@ -10394,7 +10388,7 @@
         <v>106</v>
       </c>
       <c r="E139" s="24" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F139" s="23" t="s">
         <v>73</v>
@@ -10441,7 +10435,7 @@
         <v>107</v>
       </c>
       <c r="E140" s="24" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="F140" s="23" t="s">
         <v>74</v>
@@ -10488,7 +10482,7 @@
         <v>108</v>
       </c>
       <c r="E141" s="24" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F141" s="23" t="s">
         <v>75</v>
@@ -10576,7 +10570,7 @@
         <v>110</v>
       </c>
       <c r="E143" s="24" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F143" s="23" t="s">
         <v>76</v>
@@ -10623,7 +10617,7 @@
         <v>111</v>
       </c>
       <c r="E144" s="24" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F144" s="23" t="s">
         <v>77</v>
@@ -10670,7 +10664,7 @@
         <v>112</v>
       </c>
       <c r="E145" s="24" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="F145" s="23" t="s">
         <v>78</v>
@@ -10758,7 +10752,7 @@
         <v>114</v>
       </c>
       <c r="E147" s="24" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F147" s="23" t="s">
         <v>79</v>
@@ -10805,7 +10799,7 @@
         <v>115</v>
       </c>
       <c r="E148" s="24" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="F148" s="23" t="s">
         <v>80</v>
@@ -10852,7 +10846,7 @@
         <v>116</v>
       </c>
       <c r="E149" s="24" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F149" s="23" t="s">
         <v>81</v>
@@ -12628,10 +12622,10 @@
     <row r="191" spans="1:36" ht="40.5">
       <c r="A191" s="5"/>
       <c r="AG191" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH191" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ191" s="9"/>
     </row>
@@ -12690,10 +12684,10 @@
     <row r="193" spans="1:36" ht="40.5">
       <c r="A193" s="5"/>
       <c r="AG193" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH193" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ193" s="9"/>
     </row>
@@ -12810,10 +12804,10 @@
     <row r="197" spans="1:36" ht="40.5">
       <c r="A197" s="5"/>
       <c r="AG197" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH197" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ197" s="9"/>
     </row>
@@ -12917,10 +12911,10 @@
     <row r="200" spans="1:36" ht="40.5">
       <c r="A200" s="5"/>
       <c r="AG200" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH200" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ200" s="9"/>
     </row>
@@ -12988,7 +12982,7 @@
         <v>270</v>
       </c>
       <c r="E202" s="19" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F202" s="18" t="s">
         <v>271</v>
@@ -13040,10 +13034,10 @@
     <row r="203" spans="1:36" ht="40.5">
       <c r="A203" s="5"/>
       <c r="AG203" s="36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AH203" s="36" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AJ203" s="9"/>
     </row>
@@ -13109,17 +13103,17 @@
         <v>38</v>
       </c>
       <c r="E205" s="19" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F205" s="18" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="G205" s="18" t="s">
         <v>14</v>
       </c>
       <c r="H205" s="18"/>
       <c r="I205" s="18" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="J205" s="18"/>
       <c r="K205" s="18" t="s">
@@ -13163,20 +13157,20 @@
       <c r="B206" s="23"/>
       <c r="C206" s="23"/>
       <c r="D206" s="23" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E206" s="24" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F206" s="23" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G206" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H206" s="23"/>
       <c r="I206" s="23" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="J206" s="23"/>
       <c r="K206" s="23" t="s">
@@ -13220,20 +13214,20 @@
       <c r="B207" s="23"/>
       <c r="C207" s="23"/>
       <c r="D207" s="23" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E207" s="24" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="F207" s="23" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G207" s="23" t="s">
         <v>13</v>
       </c>
       <c r="H207" s="23"/>
       <c r="I207" s="23" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J207" s="23"/>
       <c r="K207" s="23" t="s">
@@ -13283,14 +13277,14 @@
         <v>524</v>
       </c>
       <c r="F208" s="23" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="G208" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H208" s="23"/>
       <c r="I208" s="23" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="J208" s="23"/>
       <c r="K208" s="23" t="s">
@@ -13340,14 +13334,14 @@
         <v>525</v>
       </c>
       <c r="F209" s="23" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="G209" s="23" t="s">
         <v>13</v>
       </c>
       <c r="H209" s="23"/>
       <c r="I209" s="23" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="J209" s="23"/>
       <c r="K209" s="23" t="s">
@@ -13391,20 +13385,20 @@
       <c r="B210" s="23"/>
       <c r="C210" s="23"/>
       <c r="D210" s="23" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E210" s="24" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F210" s="23" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G210" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H210" s="23"/>
       <c r="I210" s="23" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="J210" s="23"/>
       <c r="K210" s="23" t="s">
@@ -13448,20 +13442,20 @@
       <c r="B211" s="23"/>
       <c r="C211" s="23"/>
       <c r="D211" s="23" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E211" s="24" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="F211" s="23" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="G211" s="23" t="s">
         <v>13</v>
       </c>
       <c r="H211" s="23"/>
       <c r="I211" s="23" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="J211" s="23"/>
       <c r="K211" s="23" t="s">
@@ -13505,20 +13499,20 @@
       <c r="B212" s="23"/>
       <c r="C212" s="23"/>
       <c r="D212" s="23" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E212" s="24" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="F212" s="23" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G212" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H212" s="23"/>
       <c r="I212" s="23" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="J212" s="23"/>
       <c r="K212" s="23" t="s">
@@ -13562,20 +13556,20 @@
       <c r="B213" s="23"/>
       <c r="C213" s="23"/>
       <c r="D213" s="23" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="E213" s="24" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F213" s="23" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="G213" s="23" t="s">
         <v>13</v>
       </c>
       <c r="H213" s="23"/>
       <c r="I213" s="23" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="J213" s="23"/>
       <c r="K213" s="23" t="s">
@@ -13622,10 +13616,10 @@
         <v>279</v>
       </c>
       <c r="E214" s="24" t="s">
-        <v>528</v>
+        <v>676</v>
       </c>
       <c r="F214" s="23" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="G214" s="23" t="s">
         <v>13</v>
@@ -13679,10 +13673,10 @@
         <v>43</v>
       </c>
       <c r="E215" s="24" t="s">
-        <v>529</v>
+        <v>677</v>
       </c>
       <c r="F215" s="23" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="G215" s="23" t="s">
         <v>14</v>
@@ -13736,17 +13730,17 @@
         <v>273</v>
       </c>
       <c r="E216" s="24" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="F216" s="23" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G216" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H216" s="23"/>
       <c r="I216" s="23" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="J216" s="23"/>
       <c r="K216" s="23" t="s">
@@ -13795,10 +13789,10 @@
         <v>274</v>
       </c>
       <c r="E217" s="24" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="F217" s="23" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G217" s="23" t="s">
         <v>14</v>
@@ -13851,20 +13845,20 @@
       <c r="B218" s="23"/>
       <c r="C218" s="23"/>
       <c r="D218" s="23" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="E218" s="24" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="F218" s="23" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G218" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H218" s="23"/>
       <c r="I218" s="23" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="J218" s="23"/>
       <c r="K218" s="23" t="s">
@@ -13908,20 +13902,20 @@
       <c r="B219" s="23"/>
       <c r="C219" s="23"/>
       <c r="D219" s="23" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="E219" s="24" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="F219" s="23" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="G219" s="23" t="s">
         <v>278</v>
       </c>
       <c r="H219" s="23"/>
       <c r="I219" s="23" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="J219" s="23"/>
       <c r="K219" s="23" t="s">
@@ -13965,20 +13959,20 @@
       <c r="B220" s="23"/>
       <c r="C220" s="23"/>
       <c r="D220" s="23" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="E220" s="24" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="F220" s="23" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="G220" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H220" s="23"/>
       <c r="I220" s="23" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="J220" s="23"/>
       <c r="K220" s="23" t="s">
@@ -14022,20 +14016,20 @@
       <c r="B221" s="23"/>
       <c r="C221" s="23"/>
       <c r="D221" s="23" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E221" s="24" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="F221" s="23" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="G221" s="23" t="s">
         <v>13</v>
       </c>
       <c r="H221" s="23"/>
       <c r="I221" s="23" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="J221" s="23"/>
       <c r="K221" s="23" t="s">
@@ -14138,7 +14132,7 @@
         <v>170</v>
       </c>
       <c r="E224" s="24" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F224" s="23" t="s">
         <v>171</v>
@@ -14465,65 +14459,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="52"/>
-      <c r="AF1" s="52"/>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="52"/>
-      <c r="BB1" s="52"/>
-      <c r="BC1" s="52"/>
-      <c r="BD1" s="52"/>
-      <c r="BE1" s="53"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
+      <c r="AM1" s="78"/>
+      <c r="AN1" s="78"/>
+      <c r="AO1" s="78"/>
+      <c r="AP1" s="78"/>
+      <c r="AQ1" s="78"/>
+      <c r="AR1" s="78"/>
+      <c r="AS1" s="78"/>
+      <c r="AT1" s="78"/>
+      <c r="AU1" s="78"/>
+      <c r="AV1" s="78"/>
+      <c r="AW1" s="78"/>
+      <c r="AX1" s="78"/>
+      <c r="AY1" s="78"/>
+      <c r="AZ1" s="78"/>
+      <c r="BA1" s="78"/>
+      <c r="BB1" s="78"/>
+      <c r="BC1" s="78"/>
+      <c r="BD1" s="78"/>
+      <c r="BE1" s="79"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="11"/>
@@ -14570,2064 +14564,1993 @@
       <c r="AP2" s="11"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57" t="s">
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="57" t="s">
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="58"/>
-      <c r="Y3" s="58"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="58"/>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="58"/>
-      <c r="AD3" s="58"/>
-      <c r="AE3" s="58"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="58"/>
-      <c r="AH3" s="58"/>
-      <c r="AI3" s="58"/>
-      <c r="AJ3" s="58"/>
-      <c r="AK3" s="58"/>
-      <c r="AL3" s="58"/>
-      <c r="AM3" s="58"/>
-      <c r="AN3" s="58"/>
-      <c r="AO3" s="58"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="57" t="s">
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
+      <c r="X3" s="84"/>
+      <c r="Y3" s="84"/>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="84"/>
+      <c r="AC3" s="84"/>
+      <c r="AD3" s="84"/>
+      <c r="AE3" s="84"/>
+      <c r="AF3" s="84"/>
+      <c r="AG3" s="84"/>
+      <c r="AH3" s="84"/>
+      <c r="AI3" s="84"/>
+      <c r="AJ3" s="84"/>
+      <c r="AK3" s="84"/>
+      <c r="AL3" s="84"/>
+      <c r="AM3" s="84"/>
+      <c r="AN3" s="84"/>
+      <c r="AO3" s="84"/>
+      <c r="AP3" s="85"/>
+      <c r="AQ3" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="AR3" s="60"/>
-      <c r="AS3" s="60"/>
-      <c r="AT3" s="60"/>
-      <c r="AU3" s="60"/>
-      <c r="AV3" s="60"/>
-      <c r="AW3" s="60"/>
-      <c r="AX3" s="60"/>
-      <c r="AY3" s="60"/>
-      <c r="AZ3" s="60"/>
-      <c r="BA3" s="60"/>
-      <c r="BB3" s="60"/>
-      <c r="BC3" s="60"/>
-      <c r="BD3" s="60"/>
-      <c r="BE3" s="61"/>
+      <c r="AR3" s="86"/>
+      <c r="AS3" s="86"/>
+      <c r="AT3" s="86"/>
+      <c r="AU3" s="86"/>
+      <c r="AV3" s="86"/>
+      <c r="AW3" s="86"/>
+      <c r="AX3" s="86"/>
+      <c r="AY3" s="86"/>
+      <c r="AZ3" s="86"/>
+      <c r="BA3" s="86"/>
+      <c r="BB3" s="86"/>
+      <c r="BC3" s="86"/>
+      <c r="BD3" s="86"/>
+      <c r="BE3" s="87"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="88">
         <v>1</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="65" t="s">
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="68"/>
-      <c r="U4" s="68"/>
-      <c r="V4" s="68"/>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
-      <c r="Y4" s="68"/>
-      <c r="Z4" s="68"/>
-      <c r="AA4" s="68"/>
-      <c r="AB4" s="68"/>
-      <c r="AC4" s="68"/>
-      <c r="AD4" s="68"/>
-      <c r="AE4" s="68"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
-      <c r="AM4" s="68"/>
-      <c r="AN4" s="68"/>
-      <c r="AO4" s="68"/>
-      <c r="AP4" s="69"/>
-      <c r="AQ4" s="70"/>
-      <c r="AR4" s="68"/>
-      <c r="AS4" s="68"/>
-      <c r="AT4" s="68"/>
-      <c r="AU4" s="68"/>
-      <c r="AV4" s="68"/>
-      <c r="AW4" s="68"/>
-      <c r="AX4" s="68"/>
-      <c r="AY4" s="68"/>
-      <c r="AZ4" s="68"/>
-      <c r="BA4" s="68"/>
-      <c r="BB4" s="68"/>
-      <c r="BC4" s="68"/>
-      <c r="BD4" s="68"/>
-      <c r="BE4" s="71"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="94"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95"/>
+      <c r="AQ4" s="96"/>
+      <c r="AR4" s="94"/>
+      <c r="AS4" s="94"/>
+      <c r="AT4" s="94"/>
+      <c r="AU4" s="94"/>
+      <c r="AV4" s="94"/>
+      <c r="AW4" s="94"/>
+      <c r="AX4" s="94"/>
+      <c r="AY4" s="94"/>
+      <c r="AZ4" s="94"/>
+      <c r="BA4" s="94"/>
+      <c r="BB4" s="94"/>
+      <c r="BC4" s="94"/>
+      <c r="BD4" s="94"/>
+      <c r="BE4" s="97"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1">
-      <c r="A5" s="72">
+      <c r="A5" s="61">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="82" t="s">
-        <v>598</v>
-      </c>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="83"/>
-      <c r="Y5" s="83"/>
-      <c r="Z5" s="83"/>
-      <c r="AA5" s="83"/>
-      <c r="AB5" s="83"/>
-      <c r="AC5" s="83"/>
-      <c r="AD5" s="83"/>
-      <c r="AE5" s="83"/>
-      <c r="AF5" s="83"/>
-      <c r="AG5" s="83"/>
-      <c r="AH5" s="83"/>
-      <c r="AI5" s="83"/>
-      <c r="AJ5" s="83"/>
-      <c r="AK5" s="83"/>
-      <c r="AL5" s="83"/>
-      <c r="AM5" s="83"/>
-      <c r="AN5" s="83"/>
-      <c r="AO5" s="83"/>
-      <c r="AP5" s="84"/>
-      <c r="AQ5" s="85" t="s">
-        <v>599</v>
-      </c>
-      <c r="AR5" s="86"/>
-      <c r="AS5" s="86"/>
-      <c r="AT5" s="86"/>
-      <c r="AU5" s="86"/>
-      <c r="AV5" s="86"/>
-      <c r="AW5" s="86"/>
-      <c r="AX5" s="86"/>
-      <c r="AY5" s="86"/>
-      <c r="AZ5" s="86"/>
-      <c r="BA5" s="86"/>
-      <c r="BB5" s="86"/>
-      <c r="BC5" s="86"/>
-      <c r="BD5" s="86"/>
-      <c r="BE5" s="87"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="71" t="s">
+        <v>594</v>
+      </c>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="72"/>
+      <c r="U5" s="72"/>
+      <c r="V5" s="72"/>
+      <c r="W5" s="72"/>
+      <c r="X5" s="72"/>
+      <c r="Y5" s="72"/>
+      <c r="Z5" s="72"/>
+      <c r="AA5" s="72"/>
+      <c r="AB5" s="72"/>
+      <c r="AC5" s="72"/>
+      <c r="AD5" s="72"/>
+      <c r="AE5" s="72"/>
+      <c r="AF5" s="72"/>
+      <c r="AG5" s="72"/>
+      <c r="AH5" s="72"/>
+      <c r="AI5" s="72"/>
+      <c r="AJ5" s="72"/>
+      <c r="AK5" s="72"/>
+      <c r="AL5" s="72"/>
+      <c r="AM5" s="72"/>
+      <c r="AN5" s="72"/>
+      <c r="AO5" s="72"/>
+      <c r="AP5" s="73"/>
+      <c r="AQ5" s="74" t="s">
+        <v>595</v>
+      </c>
+      <c r="AR5" s="75"/>
+      <c r="AS5" s="75"/>
+      <c r="AT5" s="75"/>
+      <c r="AU5" s="75"/>
+      <c r="AV5" s="75"/>
+      <c r="AW5" s="75"/>
+      <c r="AX5" s="75"/>
+      <c r="AY5" s="75"/>
+      <c r="AZ5" s="75"/>
+      <c r="BA5" s="75"/>
+      <c r="BB5" s="75"/>
+      <c r="BC5" s="75"/>
+      <c r="BD5" s="75"/>
+      <c r="BE5" s="76"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1">
-      <c r="A6" s="72"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="75"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78"/>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
-      <c r="V6" s="78"/>
-      <c r="W6" s="78"/>
-      <c r="X6" s="78"/>
-      <c r="Y6" s="78"/>
-      <c r="Z6" s="78"/>
-      <c r="AA6" s="78"/>
-      <c r="AB6" s="78"/>
-      <c r="AC6" s="78"/>
-      <c r="AD6" s="78"/>
-      <c r="AE6" s="78"/>
-      <c r="AF6" s="78"/>
-      <c r="AG6" s="78"/>
-      <c r="AH6" s="78"/>
-      <c r="AI6" s="78"/>
-      <c r="AJ6" s="78"/>
-      <c r="AK6" s="78"/>
-      <c r="AL6" s="78"/>
-      <c r="AM6" s="78"/>
-      <c r="AN6" s="78"/>
-      <c r="AO6" s="78"/>
-      <c r="AP6" s="79"/>
-      <c r="AQ6" s="80"/>
-      <c r="AR6" s="78"/>
-      <c r="AS6" s="78"/>
-      <c r="AT6" s="78"/>
-      <c r="AU6" s="78"/>
-      <c r="AV6" s="78"/>
-      <c r="AW6" s="78"/>
-      <c r="AX6" s="78"/>
-      <c r="AY6" s="78"/>
-      <c r="AZ6" s="78"/>
-      <c r="BA6" s="78"/>
-      <c r="BB6" s="78"/>
-      <c r="BC6" s="78"/>
-      <c r="BD6" s="78"/>
-      <c r="BE6" s="81"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="67"/>
+      <c r="AL6" s="67"/>
+      <c r="AM6" s="67"/>
+      <c r="AN6" s="67"/>
+      <c r="AO6" s="67"/>
+      <c r="AP6" s="68"/>
+      <c r="AQ6" s="69"/>
+      <c r="AR6" s="67"/>
+      <c r="AS6" s="67"/>
+      <c r="AT6" s="67"/>
+      <c r="AU6" s="67"/>
+      <c r="AV6" s="67"/>
+      <c r="AW6" s="67"/>
+      <c r="AX6" s="67"/>
+      <c r="AY6" s="67"/>
+      <c r="AZ6" s="67"/>
+      <c r="BA6" s="67"/>
+      <c r="BB6" s="67"/>
+      <c r="BC6" s="67"/>
+      <c r="BD6" s="67"/>
+      <c r="BE6" s="70"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="72"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="76"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="78"/>
-      <c r="S7" s="78"/>
-      <c r="T7" s="78"/>
-      <c r="U7" s="78"/>
-      <c r="V7" s="78"/>
-      <c r="W7" s="78"/>
-      <c r="X7" s="78"/>
-      <c r="Y7" s="78"/>
-      <c r="Z7" s="78"/>
-      <c r="AA7" s="78"/>
-      <c r="AB7" s="78"/>
-      <c r="AC7" s="78"/>
-      <c r="AD7" s="78"/>
-      <c r="AE7" s="78"/>
-      <c r="AF7" s="78"/>
-      <c r="AG7" s="78"/>
-      <c r="AH7" s="78"/>
-      <c r="AI7" s="78"/>
-      <c r="AJ7" s="78"/>
-      <c r="AK7" s="78"/>
-      <c r="AL7" s="78"/>
-      <c r="AM7" s="78"/>
-      <c r="AN7" s="78"/>
-      <c r="AO7" s="78"/>
-      <c r="AP7" s="79"/>
-      <c r="AQ7" s="80"/>
-      <c r="AR7" s="78"/>
-      <c r="AS7" s="78"/>
-      <c r="AT7" s="78"/>
-      <c r="AU7" s="78"/>
-      <c r="AV7" s="78"/>
-      <c r="AW7" s="78"/>
-      <c r="AX7" s="78"/>
-      <c r="AY7" s="78"/>
-      <c r="AZ7" s="78"/>
-      <c r="BA7" s="78"/>
-      <c r="BB7" s="78"/>
-      <c r="BC7" s="78"/>
-      <c r="BD7" s="78"/>
-      <c r="BE7" s="81"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+      <c r="U7" s="67"/>
+      <c r="V7" s="67"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="67"/>
+      <c r="Z7" s="67"/>
+      <c r="AA7" s="67"/>
+      <c r="AB7" s="67"/>
+      <c r="AC7" s="67"/>
+      <c r="AD7" s="67"/>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="67"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
+      <c r="AK7" s="67"/>
+      <c r="AL7" s="67"/>
+      <c r="AM7" s="67"/>
+      <c r="AN7" s="67"/>
+      <c r="AO7" s="67"/>
+      <c r="AP7" s="68"/>
+      <c r="AQ7" s="69"/>
+      <c r="AR7" s="67"/>
+      <c r="AS7" s="67"/>
+      <c r="AT7" s="67"/>
+      <c r="AU7" s="67"/>
+      <c r="AV7" s="67"/>
+      <c r="AW7" s="67"/>
+      <c r="AX7" s="67"/>
+      <c r="AY7" s="67"/>
+      <c r="AZ7" s="67"/>
+      <c r="BA7" s="67"/>
+      <c r="BB7" s="67"/>
+      <c r="BC7" s="67"/>
+      <c r="BD7" s="67"/>
+      <c r="BE7" s="70"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="72"/>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="76"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="75"/>
-      <c r="P8" s="78"/>
-      <c r="Q8" s="78"/>
-      <c r="R8" s="78"/>
-      <c r="S8" s="78"/>
-      <c r="T8" s="78"/>
-      <c r="U8" s="78"/>
-      <c r="V8" s="78"/>
-      <c r="W8" s="78"/>
-      <c r="X8" s="78"/>
-      <c r="Y8" s="78"/>
-      <c r="Z8" s="78"/>
-      <c r="AA8" s="78"/>
-      <c r="AB8" s="78"/>
-      <c r="AC8" s="78"/>
-      <c r="AD8" s="78"/>
-      <c r="AE8" s="78"/>
-      <c r="AF8" s="78"/>
-      <c r="AG8" s="78"/>
-      <c r="AH8" s="78"/>
-      <c r="AI8" s="78"/>
-      <c r="AJ8" s="78"/>
-      <c r="AK8" s="78"/>
-      <c r="AL8" s="78"/>
-      <c r="AM8" s="78"/>
-      <c r="AN8" s="78"/>
-      <c r="AO8" s="78"/>
-      <c r="AP8" s="79"/>
-      <c r="AQ8" s="80"/>
-      <c r="AR8" s="78"/>
-      <c r="AS8" s="78"/>
-      <c r="AT8" s="78"/>
-      <c r="AU8" s="78"/>
-      <c r="AV8" s="78"/>
-      <c r="AW8" s="78"/>
-      <c r="AX8" s="78"/>
-      <c r="AY8" s="78"/>
-      <c r="AZ8" s="78"/>
-      <c r="BA8" s="78"/>
-      <c r="BB8" s="78"/>
-      <c r="BC8" s="78"/>
-      <c r="BD8" s="78"/>
-      <c r="BE8" s="81"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="67"/>
+      <c r="V8" s="67"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="67"/>
+      <c r="Y8" s="67"/>
+      <c r="Z8" s="67"/>
+      <c r="AA8" s="67"/>
+      <c r="AB8" s="67"/>
+      <c r="AC8" s="67"/>
+      <c r="AD8" s="67"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="67"/>
+      <c r="AG8" s="67"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="67"/>
+      <c r="AK8" s="67"/>
+      <c r="AL8" s="67"/>
+      <c r="AM8" s="67"/>
+      <c r="AN8" s="67"/>
+      <c r="AO8" s="67"/>
+      <c r="AP8" s="68"/>
+      <c r="AQ8" s="69"/>
+      <c r="AR8" s="67"/>
+      <c r="AS8" s="67"/>
+      <c r="AT8" s="67"/>
+      <c r="AU8" s="67"/>
+      <c r="AV8" s="67"/>
+      <c r="AW8" s="67"/>
+      <c r="AX8" s="67"/>
+      <c r="AY8" s="67"/>
+      <c r="AZ8" s="67"/>
+      <c r="BA8" s="67"/>
+      <c r="BB8" s="67"/>
+      <c r="BC8" s="67"/>
+      <c r="BD8" s="67"/>
+      <c r="BE8" s="70"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="72"/>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="76"/>
-      <c r="M9" s="76"/>
-      <c r="N9" s="77"/>
-      <c r="O9" s="75"/>
-      <c r="P9" s="78"/>
-      <c r="Q9" s="78"/>
-      <c r="R9" s="78"/>
-      <c r="S9" s="78"/>
-      <c r="T9" s="78"/>
-      <c r="U9" s="78"/>
-      <c r="V9" s="78"/>
-      <c r="W9" s="78"/>
-      <c r="X9" s="78"/>
-      <c r="Y9" s="78"/>
-      <c r="Z9" s="78"/>
-      <c r="AA9" s="78"/>
-      <c r="AB9" s="78"/>
-      <c r="AC9" s="78"/>
-      <c r="AD9" s="78"/>
-      <c r="AE9" s="78"/>
-      <c r="AF9" s="78"/>
-      <c r="AG9" s="78"/>
-      <c r="AH9" s="78"/>
-      <c r="AI9" s="78"/>
-      <c r="AJ9" s="78"/>
-      <c r="AK9" s="78"/>
-      <c r="AL9" s="78"/>
-      <c r="AM9" s="78"/>
-      <c r="AN9" s="78"/>
-      <c r="AO9" s="78"/>
-      <c r="AP9" s="79"/>
-      <c r="AQ9" s="80"/>
-      <c r="AR9" s="78"/>
-      <c r="AS9" s="78"/>
-      <c r="AT9" s="78"/>
-      <c r="AU9" s="78"/>
-      <c r="AV9" s="78"/>
-      <c r="AW9" s="78"/>
-      <c r="AX9" s="78"/>
-      <c r="AY9" s="78"/>
-      <c r="AZ9" s="78"/>
-      <c r="BA9" s="78"/>
-      <c r="BB9" s="78"/>
-      <c r="BC9" s="78"/>
-      <c r="BD9" s="78"/>
-      <c r="BE9" s="81"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="67"/>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="67"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="67"/>
+      <c r="U9" s="67"/>
+      <c r="V9" s="67"/>
+      <c r="W9" s="67"/>
+      <c r="X9" s="67"/>
+      <c r="Y9" s="67"/>
+      <c r="Z9" s="67"/>
+      <c r="AA9" s="67"/>
+      <c r="AB9" s="67"/>
+      <c r="AC9" s="67"/>
+      <c r="AD9" s="67"/>
+      <c r="AE9" s="67"/>
+      <c r="AF9" s="67"/>
+      <c r="AG9" s="67"/>
+      <c r="AH9" s="67"/>
+      <c r="AI9" s="67"/>
+      <c r="AJ9" s="67"/>
+      <c r="AK9" s="67"/>
+      <c r="AL9" s="67"/>
+      <c r="AM9" s="67"/>
+      <c r="AN9" s="67"/>
+      <c r="AO9" s="67"/>
+      <c r="AP9" s="68"/>
+      <c r="AQ9" s="69"/>
+      <c r="AR9" s="67"/>
+      <c r="AS9" s="67"/>
+      <c r="AT9" s="67"/>
+      <c r="AU9" s="67"/>
+      <c r="AV9" s="67"/>
+      <c r="AW9" s="67"/>
+      <c r="AX9" s="67"/>
+      <c r="AY9" s="67"/>
+      <c r="AZ9" s="67"/>
+      <c r="BA9" s="67"/>
+      <c r="BB9" s="67"/>
+      <c r="BC9" s="67"/>
+      <c r="BD9" s="67"/>
+      <c r="BE9" s="70"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="76"/>
-      <c r="K10" s="76"/>
-      <c r="L10" s="76"/>
-      <c r="M10" s="76"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="75"/>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="78"/>
-      <c r="T10" s="78"/>
-      <c r="U10" s="78"/>
-      <c r="V10" s="78"/>
-      <c r="W10" s="78"/>
-      <c r="X10" s="78"/>
-      <c r="Y10" s="78"/>
-      <c r="Z10" s="78"/>
-      <c r="AA10" s="78"/>
-      <c r="AB10" s="78"/>
-      <c r="AC10" s="78"/>
-      <c r="AD10" s="78"/>
-      <c r="AE10" s="78"/>
-      <c r="AF10" s="78"/>
-      <c r="AG10" s="78"/>
-      <c r="AH10" s="78"/>
-      <c r="AI10" s="78"/>
-      <c r="AJ10" s="78"/>
-      <c r="AK10" s="78"/>
-      <c r="AL10" s="78"/>
-      <c r="AM10" s="78"/>
-      <c r="AN10" s="78"/>
-      <c r="AO10" s="78"/>
-      <c r="AP10" s="79"/>
-      <c r="AQ10" s="80"/>
-      <c r="AR10" s="78"/>
-      <c r="AS10" s="78"/>
-      <c r="AT10" s="78"/>
-      <c r="AU10" s="78"/>
-      <c r="AV10" s="78"/>
-      <c r="AW10" s="78"/>
-      <c r="AX10" s="78"/>
-      <c r="AY10" s="78"/>
-      <c r="AZ10" s="78"/>
-      <c r="BA10" s="78"/>
-      <c r="BB10" s="78"/>
-      <c r="BC10" s="78"/>
-      <c r="BD10" s="78"/>
-      <c r="BE10" s="81"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="67"/>
+      <c r="Y10" s="67"/>
+      <c r="Z10" s="67"/>
+      <c r="AA10" s="67"/>
+      <c r="AB10" s="67"/>
+      <c r="AC10" s="67"/>
+      <c r="AD10" s="67"/>
+      <c r="AE10" s="67"/>
+      <c r="AF10" s="67"/>
+      <c r="AG10" s="67"/>
+      <c r="AH10" s="67"/>
+      <c r="AI10" s="67"/>
+      <c r="AJ10" s="67"/>
+      <c r="AK10" s="67"/>
+      <c r="AL10" s="67"/>
+      <c r="AM10" s="67"/>
+      <c r="AN10" s="67"/>
+      <c r="AO10" s="67"/>
+      <c r="AP10" s="68"/>
+      <c r="AQ10" s="69"/>
+      <c r="AR10" s="67"/>
+      <c r="AS10" s="67"/>
+      <c r="AT10" s="67"/>
+      <c r="AU10" s="67"/>
+      <c r="AV10" s="67"/>
+      <c r="AW10" s="67"/>
+      <c r="AX10" s="67"/>
+      <c r="AY10" s="67"/>
+      <c r="AZ10" s="67"/>
+      <c r="BA10" s="67"/>
+      <c r="BB10" s="67"/>
+      <c r="BC10" s="67"/>
+      <c r="BD10" s="67"/>
+      <c r="BE10" s="70"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="76"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="78"/>
-      <c r="Q11" s="78"/>
-      <c r="R11" s="78"/>
-      <c r="S11" s="78"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="78"/>
-      <c r="V11" s="78"/>
-      <c r="W11" s="78"/>
-      <c r="X11" s="78"/>
-      <c r="Y11" s="78"/>
-      <c r="Z11" s="78"/>
-      <c r="AA11" s="78"/>
-      <c r="AB11" s="78"/>
-      <c r="AC11" s="78"/>
-      <c r="AD11" s="78"/>
-      <c r="AE11" s="78"/>
-      <c r="AF11" s="78"/>
-      <c r="AG11" s="78"/>
-      <c r="AH11" s="78"/>
-      <c r="AI11" s="78"/>
-      <c r="AJ11" s="78"/>
-      <c r="AK11" s="78"/>
-      <c r="AL11" s="78"/>
-      <c r="AM11" s="78"/>
-      <c r="AN11" s="78"/>
-      <c r="AO11" s="78"/>
-      <c r="AP11" s="79"/>
-      <c r="AQ11" s="80"/>
-      <c r="AR11" s="78"/>
-      <c r="AS11" s="78"/>
-      <c r="AT11" s="78"/>
-      <c r="AU11" s="78"/>
-      <c r="AV11" s="78"/>
-      <c r="AW11" s="78"/>
-      <c r="AX11" s="78"/>
-      <c r="AY11" s="78"/>
-      <c r="AZ11" s="78"/>
-      <c r="BA11" s="78"/>
-      <c r="BB11" s="78"/>
-      <c r="BC11" s="78"/>
-      <c r="BD11" s="78"/>
-      <c r="BE11" s="81"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="67"/>
+      <c r="V11" s="67"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="67"/>
+      <c r="Z11" s="67"/>
+      <c r="AA11" s="67"/>
+      <c r="AB11" s="67"/>
+      <c r="AC11" s="67"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="67"/>
+      <c r="AF11" s="67"/>
+      <c r="AG11" s="67"/>
+      <c r="AH11" s="67"/>
+      <c r="AI11" s="67"/>
+      <c r="AJ11" s="67"/>
+      <c r="AK11" s="67"/>
+      <c r="AL11" s="67"/>
+      <c r="AM11" s="67"/>
+      <c r="AN11" s="67"/>
+      <c r="AO11" s="67"/>
+      <c r="AP11" s="68"/>
+      <c r="AQ11" s="69"/>
+      <c r="AR11" s="67"/>
+      <c r="AS11" s="67"/>
+      <c r="AT11" s="67"/>
+      <c r="AU11" s="67"/>
+      <c r="AV11" s="67"/>
+      <c r="AW11" s="67"/>
+      <c r="AX11" s="67"/>
+      <c r="AY11" s="67"/>
+      <c r="AZ11" s="67"/>
+      <c r="BA11" s="67"/>
+      <c r="BB11" s="67"/>
+      <c r="BC11" s="67"/>
+      <c r="BD11" s="67"/>
+      <c r="BE11" s="70"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="72"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="75"/>
-      <c r="P12" s="78"/>
-      <c r="Q12" s="78"/>
-      <c r="R12" s="78"/>
-      <c r="S12" s="78"/>
-      <c r="T12" s="78"/>
-      <c r="U12" s="78"/>
-      <c r="V12" s="78"/>
-      <c r="W12" s="78"/>
-      <c r="X12" s="78"/>
-      <c r="Y12" s="78"/>
-      <c r="Z12" s="78"/>
-      <c r="AA12" s="78"/>
-      <c r="AB12" s="78"/>
-      <c r="AC12" s="78"/>
-      <c r="AD12" s="78"/>
-      <c r="AE12" s="78"/>
-      <c r="AF12" s="78"/>
-      <c r="AG12" s="78"/>
-      <c r="AH12" s="78"/>
-      <c r="AI12" s="78"/>
-      <c r="AJ12" s="78"/>
-      <c r="AK12" s="78"/>
-      <c r="AL12" s="78"/>
-      <c r="AM12" s="78"/>
-      <c r="AN12" s="78"/>
-      <c r="AO12" s="78"/>
-      <c r="AP12" s="79"/>
-      <c r="AQ12" s="80"/>
-      <c r="AR12" s="78"/>
-      <c r="AS12" s="78"/>
-      <c r="AT12" s="78"/>
-      <c r="AU12" s="78"/>
-      <c r="AV12" s="78"/>
-      <c r="AW12" s="78"/>
-      <c r="AX12" s="78"/>
-      <c r="AY12" s="78"/>
-      <c r="AZ12" s="78"/>
-      <c r="BA12" s="78"/>
-      <c r="BB12" s="78"/>
-      <c r="BC12" s="78"/>
-      <c r="BD12" s="78"/>
-      <c r="BE12" s="81"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+      <c r="U12" s="67"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="67"/>
+      <c r="Y12" s="67"/>
+      <c r="Z12" s="67"/>
+      <c r="AA12" s="67"/>
+      <c r="AB12" s="67"/>
+      <c r="AC12" s="67"/>
+      <c r="AD12" s="67"/>
+      <c r="AE12" s="67"/>
+      <c r="AF12" s="67"/>
+      <c r="AG12" s="67"/>
+      <c r="AH12" s="67"/>
+      <c r="AI12" s="67"/>
+      <c r="AJ12" s="67"/>
+      <c r="AK12" s="67"/>
+      <c r="AL12" s="67"/>
+      <c r="AM12" s="67"/>
+      <c r="AN12" s="67"/>
+      <c r="AO12" s="67"/>
+      <c r="AP12" s="68"/>
+      <c r="AQ12" s="69"/>
+      <c r="AR12" s="67"/>
+      <c r="AS12" s="67"/>
+      <c r="AT12" s="67"/>
+      <c r="AU12" s="67"/>
+      <c r="AV12" s="67"/>
+      <c r="AW12" s="67"/>
+      <c r="AX12" s="67"/>
+      <c r="AY12" s="67"/>
+      <c r="AZ12" s="67"/>
+      <c r="BA12" s="67"/>
+      <c r="BB12" s="67"/>
+      <c r="BC12" s="67"/>
+      <c r="BD12" s="67"/>
+      <c r="BE12" s="70"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="72"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="77"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="78"/>
-      <c r="R13" s="78"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="78"/>
-      <c r="U13" s="78"/>
-      <c r="V13" s="78"/>
-      <c r="W13" s="78"/>
-      <c r="X13" s="78"/>
-      <c r="Y13" s="78"/>
-      <c r="Z13" s="78"/>
-      <c r="AA13" s="78"/>
-      <c r="AB13" s="78"/>
-      <c r="AC13" s="78"/>
-      <c r="AD13" s="78"/>
-      <c r="AE13" s="78"/>
-      <c r="AF13" s="78"/>
-      <c r="AG13" s="78"/>
-      <c r="AH13" s="78"/>
-      <c r="AI13" s="78"/>
-      <c r="AJ13" s="78"/>
-      <c r="AK13" s="78"/>
-      <c r="AL13" s="78"/>
-      <c r="AM13" s="78"/>
-      <c r="AN13" s="78"/>
-      <c r="AO13" s="78"/>
-      <c r="AP13" s="79"/>
-      <c r="AQ13" s="80"/>
-      <c r="AR13" s="78"/>
-      <c r="AS13" s="78"/>
-      <c r="AT13" s="78"/>
-      <c r="AU13" s="78"/>
-      <c r="AV13" s="78"/>
-      <c r="AW13" s="78"/>
-      <c r="AX13" s="78"/>
-      <c r="AY13" s="78"/>
-      <c r="AZ13" s="78"/>
-      <c r="BA13" s="78"/>
-      <c r="BB13" s="78"/>
-      <c r="BC13" s="78"/>
-      <c r="BD13" s="78"/>
-      <c r="BE13" s="81"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="66"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+      <c r="U13" s="67"/>
+      <c r="V13" s="67"/>
+      <c r="W13" s="67"/>
+      <c r="X13" s="67"/>
+      <c r="Y13" s="67"/>
+      <c r="Z13" s="67"/>
+      <c r="AA13" s="67"/>
+      <c r="AB13" s="67"/>
+      <c r="AC13" s="67"/>
+      <c r="AD13" s="67"/>
+      <c r="AE13" s="67"/>
+      <c r="AF13" s="67"/>
+      <c r="AG13" s="67"/>
+      <c r="AH13" s="67"/>
+      <c r="AI13" s="67"/>
+      <c r="AJ13" s="67"/>
+      <c r="AK13" s="67"/>
+      <c r="AL13" s="67"/>
+      <c r="AM13" s="67"/>
+      <c r="AN13" s="67"/>
+      <c r="AO13" s="67"/>
+      <c r="AP13" s="68"/>
+      <c r="AQ13" s="69"/>
+      <c r="AR13" s="67"/>
+      <c r="AS13" s="67"/>
+      <c r="AT13" s="67"/>
+      <c r="AU13" s="67"/>
+      <c r="AV13" s="67"/>
+      <c r="AW13" s="67"/>
+      <c r="AX13" s="67"/>
+      <c r="AY13" s="67"/>
+      <c r="AZ13" s="67"/>
+      <c r="BA13" s="67"/>
+      <c r="BB13" s="67"/>
+      <c r="BC13" s="67"/>
+      <c r="BD13" s="67"/>
+      <c r="BE13" s="70"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="78"/>
-      <c r="V14" s="78"/>
-      <c r="W14" s="78"/>
-      <c r="X14" s="78"/>
-      <c r="Y14" s="78"/>
-      <c r="Z14" s="78"/>
-      <c r="AA14" s="78"/>
-      <c r="AB14" s="78"/>
-      <c r="AC14" s="78"/>
-      <c r="AD14" s="78"/>
-      <c r="AE14" s="78"/>
-      <c r="AF14" s="78"/>
-      <c r="AG14" s="78"/>
-      <c r="AH14" s="78"/>
-      <c r="AI14" s="78"/>
-      <c r="AJ14" s="78"/>
-      <c r="AK14" s="78"/>
-      <c r="AL14" s="78"/>
-      <c r="AM14" s="78"/>
-      <c r="AN14" s="78"/>
-      <c r="AO14" s="78"/>
-      <c r="AP14" s="79"/>
-      <c r="AQ14" s="80"/>
-      <c r="AR14" s="78"/>
-      <c r="AS14" s="78"/>
-      <c r="AT14" s="78"/>
-      <c r="AU14" s="78"/>
-      <c r="AV14" s="78"/>
-      <c r="AW14" s="78"/>
-      <c r="AX14" s="78"/>
-      <c r="AY14" s="78"/>
-      <c r="AZ14" s="78"/>
-      <c r="BA14" s="78"/>
-      <c r="BB14" s="78"/>
-      <c r="BC14" s="78"/>
-      <c r="BD14" s="78"/>
-      <c r="BE14" s="81"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+      <c r="U14" s="67"/>
+      <c r="V14" s="67"/>
+      <c r="W14" s="67"/>
+      <c r="X14" s="67"/>
+      <c r="Y14" s="67"/>
+      <c r="Z14" s="67"/>
+      <c r="AA14" s="67"/>
+      <c r="AB14" s="67"/>
+      <c r="AC14" s="67"/>
+      <c r="AD14" s="67"/>
+      <c r="AE14" s="67"/>
+      <c r="AF14" s="67"/>
+      <c r="AG14" s="67"/>
+      <c r="AH14" s="67"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="67"/>
+      <c r="AK14" s="67"/>
+      <c r="AL14" s="67"/>
+      <c r="AM14" s="67"/>
+      <c r="AN14" s="67"/>
+      <c r="AO14" s="67"/>
+      <c r="AP14" s="68"/>
+      <c r="AQ14" s="69"/>
+      <c r="AR14" s="67"/>
+      <c r="AS14" s="67"/>
+      <c r="AT14" s="67"/>
+      <c r="AU14" s="67"/>
+      <c r="AV14" s="67"/>
+      <c r="AW14" s="67"/>
+      <c r="AX14" s="67"/>
+      <c r="AY14" s="67"/>
+      <c r="AZ14" s="67"/>
+      <c r="BA14" s="67"/>
+      <c r="BB14" s="67"/>
+      <c r="BC14" s="67"/>
+      <c r="BD14" s="67"/>
+      <c r="BE14" s="70"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="72"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="76"/>
-      <c r="M15" s="76"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="78"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="78"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="78"/>
-      <c r="AB15" s="78"/>
-      <c r="AC15" s="78"/>
-      <c r="AD15" s="78"/>
-      <c r="AE15" s="78"/>
-      <c r="AF15" s="78"/>
-      <c r="AG15" s="78"/>
-      <c r="AH15" s="78"/>
-      <c r="AI15" s="78"/>
-      <c r="AJ15" s="78"/>
-      <c r="AK15" s="78"/>
-      <c r="AL15" s="78"/>
-      <c r="AM15" s="78"/>
-      <c r="AN15" s="78"/>
-      <c r="AO15" s="78"/>
-      <c r="AP15" s="79"/>
-      <c r="AQ15" s="80"/>
-      <c r="AR15" s="78"/>
-      <c r="AS15" s="78"/>
-      <c r="AT15" s="78"/>
-      <c r="AU15" s="78"/>
-      <c r="AV15" s="78"/>
-      <c r="AW15" s="78"/>
-      <c r="AX15" s="78"/>
-      <c r="AY15" s="78"/>
-      <c r="AZ15" s="78"/>
-      <c r="BA15" s="78"/>
-      <c r="BB15" s="78"/>
-      <c r="BC15" s="78"/>
-      <c r="BD15" s="78"/>
-      <c r="BE15" s="81"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="67"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="67"/>
+      <c r="Z15" s="67"/>
+      <c r="AA15" s="67"/>
+      <c r="AB15" s="67"/>
+      <c r="AC15" s="67"/>
+      <c r="AD15" s="67"/>
+      <c r="AE15" s="67"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="67"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="67"/>
+      <c r="AL15" s="67"/>
+      <c r="AM15" s="67"/>
+      <c r="AN15" s="67"/>
+      <c r="AO15" s="67"/>
+      <c r="AP15" s="68"/>
+      <c r="AQ15" s="69"/>
+      <c r="AR15" s="67"/>
+      <c r="AS15" s="67"/>
+      <c r="AT15" s="67"/>
+      <c r="AU15" s="67"/>
+      <c r="AV15" s="67"/>
+      <c r="AW15" s="67"/>
+      <c r="AX15" s="67"/>
+      <c r="AY15" s="67"/>
+      <c r="AZ15" s="67"/>
+      <c r="BA15" s="67"/>
+      <c r="BB15" s="67"/>
+      <c r="BC15" s="67"/>
+      <c r="BD15" s="67"/>
+      <c r="BE15" s="70"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="72"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="76"/>
-      <c r="N16" s="77"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="78"/>
-      <c r="R16" s="78"/>
-      <c r="S16" s="78"/>
-      <c r="T16" s="78"/>
-      <c r="U16" s="78"/>
-      <c r="V16" s="78"/>
-      <c r="W16" s="78"/>
-      <c r="X16" s="78"/>
-      <c r="Y16" s="78"/>
-      <c r="Z16" s="78"/>
-      <c r="AA16" s="78"/>
-      <c r="AB16" s="78"/>
-      <c r="AC16" s="78"/>
-      <c r="AD16" s="78"/>
-      <c r="AE16" s="78"/>
-      <c r="AF16" s="78"/>
-      <c r="AG16" s="78"/>
-      <c r="AH16" s="78"/>
-      <c r="AI16" s="78"/>
-      <c r="AJ16" s="78"/>
-      <c r="AK16" s="78"/>
-      <c r="AL16" s="78"/>
-      <c r="AM16" s="78"/>
-      <c r="AN16" s="78"/>
-      <c r="AO16" s="78"/>
-      <c r="AP16" s="79"/>
-      <c r="AQ16" s="80"/>
-      <c r="AR16" s="78"/>
-      <c r="AS16" s="78"/>
-      <c r="AT16" s="78"/>
-      <c r="AU16" s="78"/>
-      <c r="AV16" s="78"/>
-      <c r="AW16" s="78"/>
-      <c r="AX16" s="78"/>
-      <c r="AY16" s="78"/>
-      <c r="AZ16" s="78"/>
-      <c r="BA16" s="78"/>
-      <c r="BB16" s="78"/>
-      <c r="BC16" s="78"/>
-      <c r="BD16" s="78"/>
-      <c r="BE16" s="81"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="67"/>
+      <c r="W16" s="67"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="67"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
+      <c r="AD16" s="67"/>
+      <c r="AE16" s="67"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="67"/>
+      <c r="AH16" s="67"/>
+      <c r="AI16" s="67"/>
+      <c r="AJ16" s="67"/>
+      <c r="AK16" s="67"/>
+      <c r="AL16" s="67"/>
+      <c r="AM16" s="67"/>
+      <c r="AN16" s="67"/>
+      <c r="AO16" s="67"/>
+      <c r="AP16" s="68"/>
+      <c r="AQ16" s="69"/>
+      <c r="AR16" s="67"/>
+      <c r="AS16" s="67"/>
+      <c r="AT16" s="67"/>
+      <c r="AU16" s="67"/>
+      <c r="AV16" s="67"/>
+      <c r="AW16" s="67"/>
+      <c r="AX16" s="67"/>
+      <c r="AY16" s="67"/>
+      <c r="AZ16" s="67"/>
+      <c r="BA16" s="67"/>
+      <c r="BB16" s="67"/>
+      <c r="BC16" s="67"/>
+      <c r="BD16" s="67"/>
+      <c r="BE16" s="70"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="72"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="76"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="76"/>
-      <c r="M17" s="76"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="75"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="78"/>
-      <c r="R17" s="78"/>
-      <c r="S17" s="78"/>
-      <c r="T17" s="78"/>
-      <c r="U17" s="78"/>
-      <c r="V17" s="78"/>
-      <c r="W17" s="78"/>
-      <c r="X17" s="78"/>
-      <c r="Y17" s="78"/>
-      <c r="Z17" s="78"/>
-      <c r="AA17" s="78"/>
-      <c r="AB17" s="78"/>
-      <c r="AC17" s="78"/>
-      <c r="AD17" s="78"/>
-      <c r="AE17" s="78"/>
-      <c r="AF17" s="78"/>
-      <c r="AG17" s="78"/>
-      <c r="AH17" s="78"/>
-      <c r="AI17" s="78"/>
-      <c r="AJ17" s="78"/>
-      <c r="AK17" s="78"/>
-      <c r="AL17" s="78"/>
-      <c r="AM17" s="78"/>
-      <c r="AN17" s="78"/>
-      <c r="AO17" s="78"/>
-      <c r="AP17" s="79"/>
-      <c r="AQ17" s="80"/>
-      <c r="AR17" s="78"/>
-      <c r="AS17" s="78"/>
-      <c r="AT17" s="78"/>
-      <c r="AU17" s="78"/>
-      <c r="AV17" s="78"/>
-      <c r="AW17" s="78"/>
-      <c r="AX17" s="78"/>
-      <c r="AY17" s="78"/>
-      <c r="AZ17" s="78"/>
-      <c r="BA17" s="78"/>
-      <c r="BB17" s="78"/>
-      <c r="BC17" s="78"/>
-      <c r="BD17" s="78"/>
-      <c r="BE17" s="81"/>
+      <c r="A17" s="61"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="67"/>
+      <c r="W17" s="67"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="67"/>
+      <c r="Z17" s="67"/>
+      <c r="AA17" s="67"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
+      <c r="AD17" s="67"/>
+      <c r="AE17" s="67"/>
+      <c r="AF17" s="67"/>
+      <c r="AG17" s="67"/>
+      <c r="AH17" s="67"/>
+      <c r="AI17" s="67"/>
+      <c r="AJ17" s="67"/>
+      <c r="AK17" s="67"/>
+      <c r="AL17" s="67"/>
+      <c r="AM17" s="67"/>
+      <c r="AN17" s="67"/>
+      <c r="AO17" s="67"/>
+      <c r="AP17" s="68"/>
+      <c r="AQ17" s="69"/>
+      <c r="AR17" s="67"/>
+      <c r="AS17" s="67"/>
+      <c r="AT17" s="67"/>
+      <c r="AU17" s="67"/>
+      <c r="AV17" s="67"/>
+      <c r="AW17" s="67"/>
+      <c r="AX17" s="67"/>
+      <c r="AY17" s="67"/>
+      <c r="AZ17" s="67"/>
+      <c r="BA17" s="67"/>
+      <c r="BB17" s="67"/>
+      <c r="BC17" s="67"/>
+      <c r="BD17" s="67"/>
+      <c r="BE17" s="70"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="72"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="77"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="78"/>
-      <c r="T18" s="78"/>
-      <c r="U18" s="78"/>
-      <c r="V18" s="78"/>
-      <c r="W18" s="78"/>
-      <c r="X18" s="78"/>
-      <c r="Y18" s="78"/>
-      <c r="Z18" s="78"/>
-      <c r="AA18" s="78"/>
-      <c r="AB18" s="78"/>
-      <c r="AC18" s="78"/>
-      <c r="AD18" s="78"/>
-      <c r="AE18" s="78"/>
-      <c r="AF18" s="78"/>
-      <c r="AG18" s="78"/>
-      <c r="AH18" s="78"/>
-      <c r="AI18" s="78"/>
-      <c r="AJ18" s="78"/>
-      <c r="AK18" s="78"/>
-      <c r="AL18" s="78"/>
-      <c r="AM18" s="78"/>
-      <c r="AN18" s="78"/>
-      <c r="AO18" s="78"/>
-      <c r="AP18" s="79"/>
-      <c r="AQ18" s="80"/>
-      <c r="AR18" s="78"/>
-      <c r="AS18" s="78"/>
-      <c r="AT18" s="78"/>
-      <c r="AU18" s="78"/>
-      <c r="AV18" s="78"/>
-      <c r="AW18" s="78"/>
-      <c r="AX18" s="78"/>
-      <c r="AY18" s="78"/>
-      <c r="AZ18" s="78"/>
-      <c r="BA18" s="78"/>
-      <c r="BB18" s="78"/>
-      <c r="BC18" s="78"/>
-      <c r="BD18" s="78"/>
-      <c r="BE18" s="81"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="67"/>
+      <c r="W18" s="67"/>
+      <c r="X18" s="67"/>
+      <c r="Y18" s="67"/>
+      <c r="Z18" s="67"/>
+      <c r="AA18" s="67"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
+      <c r="AD18" s="67"/>
+      <c r="AE18" s="67"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="67"/>
+      <c r="AH18" s="67"/>
+      <c r="AI18" s="67"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="67"/>
+      <c r="AL18" s="67"/>
+      <c r="AM18" s="67"/>
+      <c r="AN18" s="67"/>
+      <c r="AO18" s="67"/>
+      <c r="AP18" s="68"/>
+      <c r="AQ18" s="69"/>
+      <c r="AR18" s="67"/>
+      <c r="AS18" s="67"/>
+      <c r="AT18" s="67"/>
+      <c r="AU18" s="67"/>
+      <c r="AV18" s="67"/>
+      <c r="AW18" s="67"/>
+      <c r="AX18" s="67"/>
+      <c r="AY18" s="67"/>
+      <c r="AZ18" s="67"/>
+      <c r="BA18" s="67"/>
+      <c r="BB18" s="67"/>
+      <c r="BC18" s="67"/>
+      <c r="BD18" s="67"/>
+      <c r="BE18" s="70"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="72"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="78"/>
-      <c r="T19" s="78"/>
-      <c r="U19" s="78"/>
-      <c r="V19" s="78"/>
-      <c r="W19" s="78"/>
-      <c r="X19" s="78"/>
-      <c r="Y19" s="78"/>
-      <c r="Z19" s="78"/>
-      <c r="AA19" s="78"/>
-      <c r="AB19" s="78"/>
-      <c r="AC19" s="78"/>
-      <c r="AD19" s="78"/>
-      <c r="AE19" s="78"/>
-      <c r="AF19" s="78"/>
-      <c r="AG19" s="78"/>
-      <c r="AH19" s="78"/>
-      <c r="AI19" s="78"/>
-      <c r="AJ19" s="78"/>
-      <c r="AK19" s="78"/>
-      <c r="AL19" s="78"/>
-      <c r="AM19" s="78"/>
-      <c r="AN19" s="78"/>
-      <c r="AO19" s="78"/>
-      <c r="AP19" s="79"/>
-      <c r="AQ19" s="80"/>
-      <c r="AR19" s="78"/>
-      <c r="AS19" s="78"/>
-      <c r="AT19" s="78"/>
-      <c r="AU19" s="78"/>
-      <c r="AV19" s="78"/>
-      <c r="AW19" s="78"/>
-      <c r="AX19" s="78"/>
-      <c r="AY19" s="78"/>
-      <c r="AZ19" s="78"/>
-      <c r="BA19" s="78"/>
-      <c r="BB19" s="78"/>
-      <c r="BC19" s="78"/>
-      <c r="BD19" s="78"/>
-      <c r="BE19" s="81"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+      <c r="U19" s="67"/>
+      <c r="V19" s="67"/>
+      <c r="W19" s="67"/>
+      <c r="X19" s="67"/>
+      <c r="Y19" s="67"/>
+      <c r="Z19" s="67"/>
+      <c r="AA19" s="67"/>
+      <c r="AB19" s="67"/>
+      <c r="AC19" s="67"/>
+      <c r="AD19" s="67"/>
+      <c r="AE19" s="67"/>
+      <c r="AF19" s="67"/>
+      <c r="AG19" s="67"/>
+      <c r="AH19" s="67"/>
+      <c r="AI19" s="67"/>
+      <c r="AJ19" s="67"/>
+      <c r="AK19" s="67"/>
+      <c r="AL19" s="67"/>
+      <c r="AM19" s="67"/>
+      <c r="AN19" s="67"/>
+      <c r="AO19" s="67"/>
+      <c r="AP19" s="68"/>
+      <c r="AQ19" s="69"/>
+      <c r="AR19" s="67"/>
+      <c r="AS19" s="67"/>
+      <c r="AT19" s="67"/>
+      <c r="AU19" s="67"/>
+      <c r="AV19" s="67"/>
+      <c r="AW19" s="67"/>
+      <c r="AX19" s="67"/>
+      <c r="AY19" s="67"/>
+      <c r="AZ19" s="67"/>
+      <c r="BA19" s="67"/>
+      <c r="BB19" s="67"/>
+      <c r="BC19" s="67"/>
+      <c r="BD19" s="67"/>
+      <c r="BE19" s="70"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="72"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="76"/>
-      <c r="N20" s="77"/>
-      <c r="O20" s="75"/>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78"/>
-      <c r="R20" s="78"/>
-      <c r="S20" s="78"/>
-      <c r="T20" s="78"/>
-      <c r="U20" s="78"/>
-      <c r="V20" s="78"/>
-      <c r="W20" s="78"/>
-      <c r="X20" s="78"/>
-      <c r="Y20" s="78"/>
-      <c r="Z20" s="78"/>
-      <c r="AA20" s="78"/>
-      <c r="AB20" s="78"/>
-      <c r="AC20" s="78"/>
-      <c r="AD20" s="78"/>
-      <c r="AE20" s="78"/>
-      <c r="AF20" s="78"/>
-      <c r="AG20" s="78"/>
-      <c r="AH20" s="78"/>
-      <c r="AI20" s="78"/>
-      <c r="AJ20" s="78"/>
-      <c r="AK20" s="78"/>
-      <c r="AL20" s="78"/>
-      <c r="AM20" s="78"/>
-      <c r="AN20" s="78"/>
-      <c r="AO20" s="78"/>
-      <c r="AP20" s="79"/>
-      <c r="AQ20" s="80"/>
-      <c r="AR20" s="78"/>
-      <c r="AS20" s="78"/>
-      <c r="AT20" s="78"/>
-      <c r="AU20" s="78"/>
-      <c r="AV20" s="78"/>
-      <c r="AW20" s="78"/>
-      <c r="AX20" s="78"/>
-      <c r="AY20" s="78"/>
-      <c r="AZ20" s="78"/>
-      <c r="BA20" s="78"/>
-      <c r="BB20" s="78"/>
-      <c r="BC20" s="78"/>
-      <c r="BD20" s="78"/>
-      <c r="BE20" s="81"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="67"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="67"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67"/>
+      <c r="Z20" s="67"/>
+      <c r="AA20" s="67"/>
+      <c r="AB20" s="67"/>
+      <c r="AC20" s="67"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="67"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="67"/>
+      <c r="AH20" s="67"/>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="67"/>
+      <c r="AK20" s="67"/>
+      <c r="AL20" s="67"/>
+      <c r="AM20" s="67"/>
+      <c r="AN20" s="67"/>
+      <c r="AO20" s="67"/>
+      <c r="AP20" s="68"/>
+      <c r="AQ20" s="69"/>
+      <c r="AR20" s="67"/>
+      <c r="AS20" s="67"/>
+      <c r="AT20" s="67"/>
+      <c r="AU20" s="67"/>
+      <c r="AV20" s="67"/>
+      <c r="AW20" s="67"/>
+      <c r="AX20" s="67"/>
+      <c r="AY20" s="67"/>
+      <c r="AZ20" s="67"/>
+      <c r="BA20" s="67"/>
+      <c r="BB20" s="67"/>
+      <c r="BC20" s="67"/>
+      <c r="BD20" s="67"/>
+      <c r="BE20" s="70"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="72"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="76"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="75"/>
-      <c r="P21" s="78"/>
-      <c r="Q21" s="78"/>
-      <c r="R21" s="78"/>
-      <c r="S21" s="78"/>
-      <c r="T21" s="78"/>
-      <c r="U21" s="78"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="78"/>
-      <c r="X21" s="78"/>
-      <c r="Y21" s="78"/>
-      <c r="Z21" s="78"/>
-      <c r="AA21" s="78"/>
-      <c r="AB21" s="78"/>
-      <c r="AC21" s="78"/>
-      <c r="AD21" s="78"/>
-      <c r="AE21" s="78"/>
-      <c r="AF21" s="78"/>
-      <c r="AG21" s="78"/>
-      <c r="AH21" s="78"/>
-      <c r="AI21" s="78"/>
-      <c r="AJ21" s="78"/>
-      <c r="AK21" s="78"/>
-      <c r="AL21" s="78"/>
-      <c r="AM21" s="78"/>
-      <c r="AN21" s="78"/>
-      <c r="AO21" s="78"/>
-      <c r="AP21" s="79"/>
-      <c r="AQ21" s="80"/>
-      <c r="AR21" s="78"/>
-      <c r="AS21" s="78"/>
-      <c r="AT21" s="78"/>
-      <c r="AU21" s="78"/>
-      <c r="AV21" s="78"/>
-      <c r="AW21" s="78"/>
-      <c r="AX21" s="78"/>
-      <c r="AY21" s="78"/>
-      <c r="AZ21" s="78"/>
-      <c r="BA21" s="78"/>
-      <c r="BB21" s="78"/>
-      <c r="BC21" s="78"/>
-      <c r="BD21" s="78"/>
-      <c r="BE21" s="81"/>
+      <c r="A21" s="61"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="67"/>
+      <c r="AA21" s="67"/>
+      <c r="AB21" s="67"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="67"/>
+      <c r="AE21" s="67"/>
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="67"/>
+      <c r="AH21" s="67"/>
+      <c r="AI21" s="67"/>
+      <c r="AJ21" s="67"/>
+      <c r="AK21" s="67"/>
+      <c r="AL21" s="67"/>
+      <c r="AM21" s="67"/>
+      <c r="AN21" s="67"/>
+      <c r="AO21" s="67"/>
+      <c r="AP21" s="68"/>
+      <c r="AQ21" s="69"/>
+      <c r="AR21" s="67"/>
+      <c r="AS21" s="67"/>
+      <c r="AT21" s="67"/>
+      <c r="AU21" s="67"/>
+      <c r="AV21" s="67"/>
+      <c r="AW21" s="67"/>
+      <c r="AX21" s="67"/>
+      <c r="AY21" s="67"/>
+      <c r="AZ21" s="67"/>
+      <c r="BA21" s="67"/>
+      <c r="BB21" s="67"/>
+      <c r="BC21" s="67"/>
+      <c r="BD21" s="67"/>
+      <c r="BE21" s="70"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="72"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="75"/>
-      <c r="P22" s="78"/>
-      <c r="Q22" s="78"/>
-      <c r="R22" s="78"/>
-      <c r="S22" s="78"/>
-      <c r="T22" s="78"/>
-      <c r="U22" s="78"/>
-      <c r="V22" s="78"/>
-      <c r="W22" s="78"/>
-      <c r="X22" s="78"/>
-      <c r="Y22" s="78"/>
-      <c r="Z22" s="78"/>
-      <c r="AA22" s="78"/>
-      <c r="AB22" s="78"/>
-      <c r="AC22" s="78"/>
-      <c r="AD22" s="78"/>
-      <c r="AE22" s="78"/>
-      <c r="AF22" s="78"/>
-      <c r="AG22" s="78"/>
-      <c r="AH22" s="78"/>
-      <c r="AI22" s="78"/>
-      <c r="AJ22" s="78"/>
-      <c r="AK22" s="78"/>
-      <c r="AL22" s="78"/>
-      <c r="AM22" s="78"/>
-      <c r="AN22" s="78"/>
-      <c r="AO22" s="78"/>
-      <c r="AP22" s="79"/>
-      <c r="AQ22" s="80"/>
-      <c r="AR22" s="78"/>
-      <c r="AS22" s="78"/>
-      <c r="AT22" s="78"/>
-      <c r="AU22" s="78"/>
-      <c r="AV22" s="78"/>
-      <c r="AW22" s="78"/>
-      <c r="AX22" s="78"/>
-      <c r="AY22" s="78"/>
-      <c r="AZ22" s="78"/>
-      <c r="BA22" s="78"/>
-      <c r="BB22" s="78"/>
-      <c r="BC22" s="78"/>
-      <c r="BD22" s="78"/>
-      <c r="BE22" s="81"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="67"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="67"/>
+      <c r="AA22" s="67"/>
+      <c r="AB22" s="67"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
+      <c r="AK22" s="67"/>
+      <c r="AL22" s="67"/>
+      <c r="AM22" s="67"/>
+      <c r="AN22" s="67"/>
+      <c r="AO22" s="67"/>
+      <c r="AP22" s="68"/>
+      <c r="AQ22" s="69"/>
+      <c r="AR22" s="67"/>
+      <c r="AS22" s="67"/>
+      <c r="AT22" s="67"/>
+      <c r="AU22" s="67"/>
+      <c r="AV22" s="67"/>
+      <c r="AW22" s="67"/>
+      <c r="AX22" s="67"/>
+      <c r="AY22" s="67"/>
+      <c r="AZ22" s="67"/>
+      <c r="BA22" s="67"/>
+      <c r="BB22" s="67"/>
+      <c r="BC22" s="67"/>
+      <c r="BD22" s="67"/>
+      <c r="BE22" s="70"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="72"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="77"/>
-      <c r="O23" s="75"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="78"/>
-      <c r="U23" s="78"/>
-      <c r="V23" s="78"/>
-      <c r="W23" s="78"/>
-      <c r="X23" s="78"/>
-      <c r="Y23" s="78"/>
-      <c r="Z23" s="78"/>
-      <c r="AA23" s="78"/>
-      <c r="AB23" s="78"/>
-      <c r="AC23" s="78"/>
-      <c r="AD23" s="78"/>
-      <c r="AE23" s="78"/>
-      <c r="AF23" s="78"/>
-      <c r="AG23" s="78"/>
-      <c r="AH23" s="78"/>
-      <c r="AI23" s="78"/>
-      <c r="AJ23" s="78"/>
-      <c r="AK23" s="78"/>
-      <c r="AL23" s="78"/>
-      <c r="AM23" s="78"/>
-      <c r="AN23" s="78"/>
-      <c r="AO23" s="78"/>
-      <c r="AP23" s="79"/>
-      <c r="AQ23" s="80"/>
-      <c r="AR23" s="78"/>
-      <c r="AS23" s="78"/>
-      <c r="AT23" s="78"/>
-      <c r="AU23" s="78"/>
-      <c r="AV23" s="78"/>
-      <c r="AW23" s="78"/>
-      <c r="AX23" s="78"/>
-      <c r="AY23" s="78"/>
-      <c r="AZ23" s="78"/>
-      <c r="BA23" s="78"/>
-      <c r="BB23" s="78"/>
-      <c r="BC23" s="78"/>
-      <c r="BD23" s="78"/>
-      <c r="BE23" s="81"/>
+      <c r="A23" s="61"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="67"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="67"/>
+      <c r="AA23" s="67"/>
+      <c r="AB23" s="67"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="67"/>
+      <c r="AE23" s="67"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="67"/>
+      <c r="AH23" s="67"/>
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
+      <c r="AL23" s="67"/>
+      <c r="AM23" s="67"/>
+      <c r="AN23" s="67"/>
+      <c r="AO23" s="67"/>
+      <c r="AP23" s="68"/>
+      <c r="AQ23" s="69"/>
+      <c r="AR23" s="67"/>
+      <c r="AS23" s="67"/>
+      <c r="AT23" s="67"/>
+      <c r="AU23" s="67"/>
+      <c r="AV23" s="67"/>
+      <c r="AW23" s="67"/>
+      <c r="AX23" s="67"/>
+      <c r="AY23" s="67"/>
+      <c r="AZ23" s="67"/>
+      <c r="BA23" s="67"/>
+      <c r="BB23" s="67"/>
+      <c r="BC23" s="67"/>
+      <c r="BD23" s="67"/>
+      <c r="BE23" s="70"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="72"/>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="77"/>
-      <c r="O24" s="75"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="78"/>
-      <c r="R24" s="78"/>
-      <c r="S24" s="78"/>
-      <c r="T24" s="78"/>
-      <c r="U24" s="78"/>
-      <c r="V24" s="78"/>
-      <c r="W24" s="78"/>
-      <c r="X24" s="78"/>
-      <c r="Y24" s="78"/>
-      <c r="Z24" s="78"/>
-      <c r="AA24" s="78"/>
-      <c r="AB24" s="78"/>
-      <c r="AC24" s="78"/>
-      <c r="AD24" s="78"/>
-      <c r="AE24" s="78"/>
-      <c r="AF24" s="78"/>
-      <c r="AG24" s="78"/>
-      <c r="AH24" s="78"/>
-      <c r="AI24" s="78"/>
-      <c r="AJ24" s="78"/>
-      <c r="AK24" s="78"/>
-      <c r="AL24" s="78"/>
-      <c r="AM24" s="78"/>
-      <c r="AN24" s="78"/>
-      <c r="AO24" s="78"/>
-      <c r="AP24" s="79"/>
-      <c r="AQ24" s="80"/>
-      <c r="AR24" s="78"/>
-      <c r="AS24" s="78"/>
-      <c r="AT24" s="78"/>
-      <c r="AU24" s="78"/>
-      <c r="AV24" s="78"/>
-      <c r="AW24" s="78"/>
-      <c r="AX24" s="78"/>
-      <c r="AY24" s="78"/>
-      <c r="AZ24" s="78"/>
-      <c r="BA24" s="78"/>
-      <c r="BB24" s="78"/>
-      <c r="BC24" s="78"/>
-      <c r="BD24" s="78"/>
-      <c r="BE24" s="81"/>
+      <c r="A24" s="61"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="64"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="67"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="67"/>
+      <c r="AE24" s="67"/>
+      <c r="AF24" s="67"/>
+      <c r="AG24" s="67"/>
+      <c r="AH24" s="67"/>
+      <c r="AI24" s="67"/>
+      <c r="AJ24" s="67"/>
+      <c r="AK24" s="67"/>
+      <c r="AL24" s="67"/>
+      <c r="AM24" s="67"/>
+      <c r="AN24" s="67"/>
+      <c r="AO24" s="67"/>
+      <c r="AP24" s="68"/>
+      <c r="AQ24" s="69"/>
+      <c r="AR24" s="67"/>
+      <c r="AS24" s="67"/>
+      <c r="AT24" s="67"/>
+      <c r="AU24" s="67"/>
+      <c r="AV24" s="67"/>
+      <c r="AW24" s="67"/>
+      <c r="AX24" s="67"/>
+      <c r="AY24" s="67"/>
+      <c r="AZ24" s="67"/>
+      <c r="BA24" s="67"/>
+      <c r="BB24" s="67"/>
+      <c r="BC24" s="67"/>
+      <c r="BD24" s="67"/>
+      <c r="BE24" s="70"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="72"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="77"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="78"/>
-      <c r="R25" s="78"/>
-      <c r="S25" s="78"/>
-      <c r="T25" s="78"/>
-      <c r="U25" s="78"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="78"/>
-      <c r="X25" s="78"/>
-      <c r="Y25" s="78"/>
-      <c r="Z25" s="78"/>
-      <c r="AA25" s="78"/>
-      <c r="AB25" s="78"/>
-      <c r="AC25" s="78"/>
-      <c r="AD25" s="78"/>
-      <c r="AE25" s="78"/>
-      <c r="AF25" s="78"/>
-      <c r="AG25" s="78"/>
-      <c r="AH25" s="78"/>
-      <c r="AI25" s="78"/>
-      <c r="AJ25" s="78"/>
-      <c r="AK25" s="78"/>
-      <c r="AL25" s="78"/>
-      <c r="AM25" s="78"/>
-      <c r="AN25" s="78"/>
-      <c r="AO25" s="78"/>
-      <c r="AP25" s="79"/>
-      <c r="AQ25" s="80"/>
-      <c r="AR25" s="78"/>
-      <c r="AS25" s="78"/>
-      <c r="AT25" s="78"/>
-      <c r="AU25" s="78"/>
-      <c r="AV25" s="78"/>
-      <c r="AW25" s="78"/>
-      <c r="AX25" s="78"/>
-      <c r="AY25" s="78"/>
-      <c r="AZ25" s="78"/>
-      <c r="BA25" s="78"/>
-      <c r="BB25" s="78"/>
-      <c r="BC25" s="78"/>
-      <c r="BD25" s="78"/>
-      <c r="BE25" s="81"/>
+      <c r="A25" s="61"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="66"/>
+      <c r="O25" s="64"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="67"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67"/>
+      <c r="Z25" s="67"/>
+      <c r="AA25" s="67"/>
+      <c r="AB25" s="67"/>
+      <c r="AC25" s="67"/>
+      <c r="AD25" s="67"/>
+      <c r="AE25" s="67"/>
+      <c r="AF25" s="67"/>
+      <c r="AG25" s="67"/>
+      <c r="AH25" s="67"/>
+      <c r="AI25" s="67"/>
+      <c r="AJ25" s="67"/>
+      <c r="AK25" s="67"/>
+      <c r="AL25" s="67"/>
+      <c r="AM25" s="67"/>
+      <c r="AN25" s="67"/>
+      <c r="AO25" s="67"/>
+      <c r="AP25" s="68"/>
+      <c r="AQ25" s="69"/>
+      <c r="AR25" s="67"/>
+      <c r="AS25" s="67"/>
+      <c r="AT25" s="67"/>
+      <c r="AU25" s="67"/>
+      <c r="AV25" s="67"/>
+      <c r="AW25" s="67"/>
+      <c r="AX25" s="67"/>
+      <c r="AY25" s="67"/>
+      <c r="AZ25" s="67"/>
+      <c r="BA25" s="67"/>
+      <c r="BB25" s="67"/>
+      <c r="BC25" s="67"/>
+      <c r="BD25" s="67"/>
+      <c r="BE25" s="70"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="72"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="76"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="76"/>
-      <c r="M26" s="76"/>
-      <c r="N26" s="77"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="78"/>
-      <c r="Q26" s="78"/>
-      <c r="R26" s="78"/>
-      <c r="S26" s="78"/>
-      <c r="T26" s="78"/>
-      <c r="U26" s="78"/>
-      <c r="V26" s="78"/>
-      <c r="W26" s="78"/>
-      <c r="X26" s="78"/>
-      <c r="Y26" s="78"/>
-      <c r="Z26" s="78"/>
-      <c r="AA26" s="78"/>
-      <c r="AB26" s="78"/>
-      <c r="AC26" s="78"/>
-      <c r="AD26" s="78"/>
-      <c r="AE26" s="78"/>
-      <c r="AF26" s="78"/>
-      <c r="AG26" s="78"/>
-      <c r="AH26" s="78"/>
-      <c r="AI26" s="78"/>
-      <c r="AJ26" s="78"/>
-      <c r="AK26" s="78"/>
-      <c r="AL26" s="78"/>
-      <c r="AM26" s="78"/>
-      <c r="AN26" s="78"/>
-      <c r="AO26" s="78"/>
-      <c r="AP26" s="79"/>
-      <c r="AQ26" s="80"/>
-      <c r="AR26" s="78"/>
-      <c r="AS26" s="78"/>
-      <c r="AT26" s="78"/>
-      <c r="AU26" s="78"/>
-      <c r="AV26" s="78"/>
-      <c r="AW26" s="78"/>
-      <c r="AX26" s="78"/>
-      <c r="AY26" s="78"/>
-      <c r="AZ26" s="78"/>
-      <c r="BA26" s="78"/>
-      <c r="BB26" s="78"/>
-      <c r="BC26" s="78"/>
-      <c r="BD26" s="78"/>
-      <c r="BE26" s="81"/>
+      <c r="A26" s="61"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="64"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="67"/>
+      <c r="X26" s="67"/>
+      <c r="Y26" s="67"/>
+      <c r="Z26" s="67"/>
+      <c r="AA26" s="67"/>
+      <c r="AB26" s="67"/>
+      <c r="AC26" s="67"/>
+      <c r="AD26" s="67"/>
+      <c r="AE26" s="67"/>
+      <c r="AF26" s="67"/>
+      <c r="AG26" s="67"/>
+      <c r="AH26" s="67"/>
+      <c r="AI26" s="67"/>
+      <c r="AJ26" s="67"/>
+      <c r="AK26" s="67"/>
+      <c r="AL26" s="67"/>
+      <c r="AM26" s="67"/>
+      <c r="AN26" s="67"/>
+      <c r="AO26" s="67"/>
+      <c r="AP26" s="68"/>
+      <c r="AQ26" s="69"/>
+      <c r="AR26" s="67"/>
+      <c r="AS26" s="67"/>
+      <c r="AT26" s="67"/>
+      <c r="AU26" s="67"/>
+      <c r="AV26" s="67"/>
+      <c r="AW26" s="67"/>
+      <c r="AX26" s="67"/>
+      <c r="AY26" s="67"/>
+      <c r="AZ26" s="67"/>
+      <c r="BA26" s="67"/>
+      <c r="BB26" s="67"/>
+      <c r="BC26" s="67"/>
+      <c r="BD26" s="67"/>
+      <c r="BE26" s="70"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="72"/>
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
-      <c r="N27" s="77"/>
-      <c r="O27" s="75"/>
-      <c r="P27" s="78"/>
-      <c r="Q27" s="78"/>
-      <c r="R27" s="78"/>
-      <c r="S27" s="78"/>
-      <c r="T27" s="78"/>
-      <c r="U27" s="78"/>
-      <c r="V27" s="78"/>
-      <c r="W27" s="78"/>
-      <c r="X27" s="78"/>
-      <c r="Y27" s="78"/>
-      <c r="Z27" s="78"/>
-      <c r="AA27" s="78"/>
-      <c r="AB27" s="78"/>
-      <c r="AC27" s="78"/>
-      <c r="AD27" s="78"/>
-      <c r="AE27" s="78"/>
-      <c r="AF27" s="78"/>
-      <c r="AG27" s="78"/>
-      <c r="AH27" s="78"/>
-      <c r="AI27" s="78"/>
-      <c r="AJ27" s="78"/>
-      <c r="AK27" s="78"/>
-      <c r="AL27" s="78"/>
-      <c r="AM27" s="78"/>
-      <c r="AN27" s="78"/>
-      <c r="AO27" s="78"/>
-      <c r="AP27" s="79"/>
-      <c r="AQ27" s="80"/>
-      <c r="AR27" s="78"/>
-      <c r="AS27" s="78"/>
-      <c r="AT27" s="78"/>
-      <c r="AU27" s="78"/>
-      <c r="AV27" s="78"/>
-      <c r="AW27" s="78"/>
-      <c r="AX27" s="78"/>
-      <c r="AY27" s="78"/>
-      <c r="AZ27" s="78"/>
-      <c r="BA27" s="78"/>
-      <c r="BB27" s="78"/>
-      <c r="BC27" s="78"/>
-      <c r="BD27" s="78"/>
-      <c r="BE27" s="81"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+      <c r="U27" s="67"/>
+      <c r="V27" s="67"/>
+      <c r="W27" s="67"/>
+      <c r="X27" s="67"/>
+      <c r="Y27" s="67"/>
+      <c r="Z27" s="67"/>
+      <c r="AA27" s="67"/>
+      <c r="AB27" s="67"/>
+      <c r="AC27" s="67"/>
+      <c r="AD27" s="67"/>
+      <c r="AE27" s="67"/>
+      <c r="AF27" s="67"/>
+      <c r="AG27" s="67"/>
+      <c r="AH27" s="67"/>
+      <c r="AI27" s="67"/>
+      <c r="AJ27" s="67"/>
+      <c r="AK27" s="67"/>
+      <c r="AL27" s="67"/>
+      <c r="AM27" s="67"/>
+      <c r="AN27" s="67"/>
+      <c r="AO27" s="67"/>
+      <c r="AP27" s="68"/>
+      <c r="AQ27" s="69"/>
+      <c r="AR27" s="67"/>
+      <c r="AS27" s="67"/>
+      <c r="AT27" s="67"/>
+      <c r="AU27" s="67"/>
+      <c r="AV27" s="67"/>
+      <c r="AW27" s="67"/>
+      <c r="AX27" s="67"/>
+      <c r="AY27" s="67"/>
+      <c r="AZ27" s="67"/>
+      <c r="BA27" s="67"/>
+      <c r="BB27" s="67"/>
+      <c r="BC27" s="67"/>
+      <c r="BD27" s="67"/>
+      <c r="BE27" s="70"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="72"/>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="76"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="77"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="78"/>
-      <c r="S28" s="78"/>
-      <c r="T28" s="78"/>
-      <c r="U28" s="78"/>
-      <c r="V28" s="78"/>
-      <c r="W28" s="78"/>
-      <c r="X28" s="78"/>
-      <c r="Y28" s="78"/>
-      <c r="Z28" s="78"/>
-      <c r="AA28" s="78"/>
-      <c r="AB28" s="78"/>
-      <c r="AC28" s="78"/>
-      <c r="AD28" s="78"/>
-      <c r="AE28" s="78"/>
-      <c r="AF28" s="78"/>
-      <c r="AG28" s="78"/>
-      <c r="AH28" s="78"/>
-      <c r="AI28" s="78"/>
-      <c r="AJ28" s="78"/>
-      <c r="AK28" s="78"/>
-      <c r="AL28" s="78"/>
-      <c r="AM28" s="78"/>
-      <c r="AN28" s="78"/>
-      <c r="AO28" s="78"/>
-      <c r="AP28" s="79"/>
-      <c r="AQ28" s="80"/>
-      <c r="AR28" s="78"/>
-      <c r="AS28" s="78"/>
-      <c r="AT28" s="78"/>
-      <c r="AU28" s="78"/>
-      <c r="AV28" s="78"/>
-      <c r="AW28" s="78"/>
-      <c r="AX28" s="78"/>
-      <c r="AY28" s="78"/>
-      <c r="AZ28" s="78"/>
-      <c r="BA28" s="78"/>
-      <c r="BB28" s="78"/>
-      <c r="BC28" s="78"/>
-      <c r="BD28" s="78"/>
-      <c r="BE28" s="81"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+      <c r="U28" s="67"/>
+      <c r="V28" s="67"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="67"/>
+      <c r="Y28" s="67"/>
+      <c r="Z28" s="67"/>
+      <c r="AA28" s="67"/>
+      <c r="AB28" s="67"/>
+      <c r="AC28" s="67"/>
+      <c r="AD28" s="67"/>
+      <c r="AE28" s="67"/>
+      <c r="AF28" s="67"/>
+      <c r="AG28" s="67"/>
+      <c r="AH28" s="67"/>
+      <c r="AI28" s="67"/>
+      <c r="AJ28" s="67"/>
+      <c r="AK28" s="67"/>
+      <c r="AL28" s="67"/>
+      <c r="AM28" s="67"/>
+      <c r="AN28" s="67"/>
+      <c r="AO28" s="67"/>
+      <c r="AP28" s="68"/>
+      <c r="AQ28" s="69"/>
+      <c r="AR28" s="67"/>
+      <c r="AS28" s="67"/>
+      <c r="AT28" s="67"/>
+      <c r="AU28" s="67"/>
+      <c r="AV28" s="67"/>
+      <c r="AW28" s="67"/>
+      <c r="AX28" s="67"/>
+      <c r="AY28" s="67"/>
+      <c r="AZ28" s="67"/>
+      <c r="BA28" s="67"/>
+      <c r="BB28" s="67"/>
+      <c r="BC28" s="67"/>
+      <c r="BD28" s="67"/>
+      <c r="BE28" s="70"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="72"/>
-      <c r="B29" s="73"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="76"/>
-      <c r="J29" s="76"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="76"/>
-      <c r="M29" s="76"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="75"/>
-      <c r="P29" s="78"/>
-      <c r="Q29" s="78"/>
-      <c r="R29" s="78"/>
-      <c r="S29" s="78"/>
-      <c r="T29" s="78"/>
-      <c r="U29" s="78"/>
-      <c r="V29" s="78"/>
-      <c r="W29" s="78"/>
-      <c r="X29" s="78"/>
-      <c r="Y29" s="78"/>
-      <c r="Z29" s="78"/>
-      <c r="AA29" s="78"/>
-      <c r="AB29" s="78"/>
-      <c r="AC29" s="78"/>
-      <c r="AD29" s="78"/>
-      <c r="AE29" s="78"/>
-      <c r="AF29" s="78"/>
-      <c r="AG29" s="78"/>
-      <c r="AH29" s="78"/>
-      <c r="AI29" s="78"/>
-      <c r="AJ29" s="78"/>
-      <c r="AK29" s="78"/>
-      <c r="AL29" s="78"/>
-      <c r="AM29" s="78"/>
-      <c r="AN29" s="78"/>
-      <c r="AO29" s="78"/>
-      <c r="AP29" s="79"/>
-      <c r="AQ29" s="80"/>
-      <c r="AR29" s="78"/>
-      <c r="AS29" s="78"/>
-      <c r="AT29" s="78"/>
-      <c r="AU29" s="78"/>
-      <c r="AV29" s="78"/>
-      <c r="AW29" s="78"/>
-      <c r="AX29" s="78"/>
-      <c r="AY29" s="78"/>
-      <c r="AZ29" s="78"/>
-      <c r="BA29" s="78"/>
-      <c r="BB29" s="78"/>
-      <c r="BC29" s="78"/>
-      <c r="BD29" s="78"/>
-      <c r="BE29" s="81"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="67"/>
+      <c r="V29" s="67"/>
+      <c r="W29" s="67"/>
+      <c r="X29" s="67"/>
+      <c r="Y29" s="67"/>
+      <c r="Z29" s="67"/>
+      <c r="AA29" s="67"/>
+      <c r="AB29" s="67"/>
+      <c r="AC29" s="67"/>
+      <c r="AD29" s="67"/>
+      <c r="AE29" s="67"/>
+      <c r="AF29" s="67"/>
+      <c r="AG29" s="67"/>
+      <c r="AH29" s="67"/>
+      <c r="AI29" s="67"/>
+      <c r="AJ29" s="67"/>
+      <c r="AK29" s="67"/>
+      <c r="AL29" s="67"/>
+      <c r="AM29" s="67"/>
+      <c r="AN29" s="67"/>
+      <c r="AO29" s="67"/>
+      <c r="AP29" s="68"/>
+      <c r="AQ29" s="69"/>
+      <c r="AR29" s="67"/>
+      <c r="AS29" s="67"/>
+      <c r="AT29" s="67"/>
+      <c r="AU29" s="67"/>
+      <c r="AV29" s="67"/>
+      <c r="AW29" s="67"/>
+      <c r="AX29" s="67"/>
+      <c r="AY29" s="67"/>
+      <c r="AZ29" s="67"/>
+      <c r="BA29" s="67"/>
+      <c r="BB29" s="67"/>
+      <c r="BC29" s="67"/>
+      <c r="BD29" s="67"/>
+      <c r="BE29" s="70"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="72"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="76"/>
-      <c r="M30" s="76"/>
-      <c r="N30" s="77"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="78"/>
-      <c r="Q30" s="78"/>
-      <c r="R30" s="78"/>
-      <c r="S30" s="78"/>
-      <c r="T30" s="78"/>
-      <c r="U30" s="78"/>
-      <c r="V30" s="78"/>
-      <c r="W30" s="78"/>
-      <c r="X30" s="78"/>
-      <c r="Y30" s="78"/>
-      <c r="Z30" s="78"/>
-      <c r="AA30" s="78"/>
-      <c r="AB30" s="78"/>
-      <c r="AC30" s="78"/>
-      <c r="AD30" s="78"/>
-      <c r="AE30" s="78"/>
-      <c r="AF30" s="78"/>
-      <c r="AG30" s="78"/>
-      <c r="AH30" s="78"/>
-      <c r="AI30" s="78"/>
-      <c r="AJ30" s="78"/>
-      <c r="AK30" s="78"/>
-      <c r="AL30" s="78"/>
-      <c r="AM30" s="78"/>
-      <c r="AN30" s="78"/>
-      <c r="AO30" s="78"/>
-      <c r="AP30" s="79"/>
-      <c r="AQ30" s="80"/>
-      <c r="AR30" s="78"/>
-      <c r="AS30" s="78"/>
-      <c r="AT30" s="78"/>
-      <c r="AU30" s="78"/>
-      <c r="AV30" s="78"/>
-      <c r="AW30" s="78"/>
-      <c r="AX30" s="78"/>
-      <c r="AY30" s="78"/>
-      <c r="AZ30" s="78"/>
-      <c r="BA30" s="78"/>
-      <c r="BB30" s="78"/>
-      <c r="BC30" s="78"/>
-      <c r="BD30" s="78"/>
-      <c r="BE30" s="81"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+      <c r="U30" s="67"/>
+      <c r="V30" s="67"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="67"/>
+      <c r="Y30" s="67"/>
+      <c r="Z30" s="67"/>
+      <c r="AA30" s="67"/>
+      <c r="AB30" s="67"/>
+      <c r="AC30" s="67"/>
+      <c r="AD30" s="67"/>
+      <c r="AE30" s="67"/>
+      <c r="AF30" s="67"/>
+      <c r="AG30" s="67"/>
+      <c r="AH30" s="67"/>
+      <c r="AI30" s="67"/>
+      <c r="AJ30" s="67"/>
+      <c r="AK30" s="67"/>
+      <c r="AL30" s="67"/>
+      <c r="AM30" s="67"/>
+      <c r="AN30" s="67"/>
+      <c r="AO30" s="67"/>
+      <c r="AP30" s="68"/>
+      <c r="AQ30" s="69"/>
+      <c r="AR30" s="67"/>
+      <c r="AS30" s="67"/>
+      <c r="AT30" s="67"/>
+      <c r="AU30" s="67"/>
+      <c r="AV30" s="67"/>
+      <c r="AW30" s="67"/>
+      <c r="AX30" s="67"/>
+      <c r="AY30" s="67"/>
+      <c r="AZ30" s="67"/>
+      <c r="BA30" s="67"/>
+      <c r="BB30" s="67"/>
+      <c r="BC30" s="67"/>
+      <c r="BD30" s="67"/>
+      <c r="BE30" s="70"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="72"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="76"/>
-      <c r="N31" s="77"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="78"/>
-      <c r="R31" s="78"/>
-      <c r="S31" s="78"/>
-      <c r="T31" s="78"/>
-      <c r="U31" s="78"/>
-      <c r="V31" s="78"/>
-      <c r="W31" s="78"/>
-      <c r="X31" s="78"/>
-      <c r="Y31" s="78"/>
-      <c r="Z31" s="78"/>
-      <c r="AA31" s="78"/>
-      <c r="AB31" s="78"/>
-      <c r="AC31" s="78"/>
-      <c r="AD31" s="78"/>
-      <c r="AE31" s="78"/>
-      <c r="AF31" s="78"/>
-      <c r="AG31" s="78"/>
-      <c r="AH31" s="78"/>
-      <c r="AI31" s="78"/>
-      <c r="AJ31" s="78"/>
-      <c r="AK31" s="78"/>
-      <c r="AL31" s="78"/>
-      <c r="AM31" s="78"/>
-      <c r="AN31" s="78"/>
-      <c r="AO31" s="78"/>
-      <c r="AP31" s="79"/>
-      <c r="AQ31" s="80"/>
-      <c r="AR31" s="78"/>
-      <c r="AS31" s="78"/>
-      <c r="AT31" s="78"/>
-      <c r="AU31" s="78"/>
-      <c r="AV31" s="78"/>
-      <c r="AW31" s="78"/>
-      <c r="AX31" s="78"/>
-      <c r="AY31" s="78"/>
-      <c r="AZ31" s="78"/>
-      <c r="BA31" s="78"/>
-      <c r="BB31" s="78"/>
-      <c r="BC31" s="78"/>
-      <c r="BD31" s="78"/>
-      <c r="BE31" s="81"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+      <c r="U31" s="67"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="67"/>
+      <c r="Y31" s="67"/>
+      <c r="Z31" s="67"/>
+      <c r="AA31" s="67"/>
+      <c r="AB31" s="67"/>
+      <c r="AC31" s="67"/>
+      <c r="AD31" s="67"/>
+      <c r="AE31" s="67"/>
+      <c r="AF31" s="67"/>
+      <c r="AG31" s="67"/>
+      <c r="AH31" s="67"/>
+      <c r="AI31" s="67"/>
+      <c r="AJ31" s="67"/>
+      <c r="AK31" s="67"/>
+      <c r="AL31" s="67"/>
+      <c r="AM31" s="67"/>
+      <c r="AN31" s="67"/>
+      <c r="AO31" s="67"/>
+      <c r="AP31" s="68"/>
+      <c r="AQ31" s="69"/>
+      <c r="AR31" s="67"/>
+      <c r="AS31" s="67"/>
+      <c r="AT31" s="67"/>
+      <c r="AU31" s="67"/>
+      <c r="AV31" s="67"/>
+      <c r="AW31" s="67"/>
+      <c r="AX31" s="67"/>
+      <c r="AY31" s="67"/>
+      <c r="AZ31" s="67"/>
+      <c r="BA31" s="67"/>
+      <c r="BB31" s="67"/>
+      <c r="BC31" s="67"/>
+      <c r="BD31" s="67"/>
+      <c r="BE31" s="70"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="72"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="76"/>
-      <c r="L32" s="76"/>
-      <c r="M32" s="76"/>
-      <c r="N32" s="77"/>
-      <c r="O32" s="75"/>
-      <c r="P32" s="78"/>
-      <c r="Q32" s="78"/>
-      <c r="R32" s="78"/>
-      <c r="S32" s="78"/>
-      <c r="T32" s="78"/>
-      <c r="U32" s="78"/>
-      <c r="V32" s="78"/>
-      <c r="W32" s="78"/>
-      <c r="X32" s="78"/>
-      <c r="Y32" s="78"/>
-      <c r="Z32" s="78"/>
-      <c r="AA32" s="78"/>
-      <c r="AB32" s="78"/>
-      <c r="AC32" s="78"/>
-      <c r="AD32" s="78"/>
-      <c r="AE32" s="78"/>
-      <c r="AF32" s="78"/>
-      <c r="AG32" s="78"/>
-      <c r="AH32" s="78"/>
-      <c r="AI32" s="78"/>
-      <c r="AJ32" s="78"/>
-      <c r="AK32" s="78"/>
-      <c r="AL32" s="78"/>
-      <c r="AM32" s="78"/>
-      <c r="AN32" s="78"/>
-      <c r="AO32" s="78"/>
-      <c r="AP32" s="79"/>
-      <c r="AQ32" s="80"/>
-      <c r="AR32" s="78"/>
-      <c r="AS32" s="78"/>
-      <c r="AT32" s="78"/>
-      <c r="AU32" s="78"/>
-      <c r="AV32" s="78"/>
-      <c r="AW32" s="78"/>
-      <c r="AX32" s="78"/>
-      <c r="AY32" s="78"/>
-      <c r="AZ32" s="78"/>
-      <c r="BA32" s="78"/>
-      <c r="BB32" s="78"/>
-      <c r="BC32" s="78"/>
-      <c r="BD32" s="78"/>
-      <c r="BE32" s="81"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="65"/>
+      <c r="L32" s="65"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="64"/>
+      <c r="P32" s="67"/>
+      <c r="Q32" s="67"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="67"/>
+      <c r="U32" s="67"/>
+      <c r="V32" s="67"/>
+      <c r="W32" s="67"/>
+      <c r="X32" s="67"/>
+      <c r="Y32" s="67"/>
+      <c r="Z32" s="67"/>
+      <c r="AA32" s="67"/>
+      <c r="AB32" s="67"/>
+      <c r="AC32" s="67"/>
+      <c r="AD32" s="67"/>
+      <c r="AE32" s="67"/>
+      <c r="AF32" s="67"/>
+      <c r="AG32" s="67"/>
+      <c r="AH32" s="67"/>
+      <c r="AI32" s="67"/>
+      <c r="AJ32" s="67"/>
+      <c r="AK32" s="67"/>
+      <c r="AL32" s="67"/>
+      <c r="AM32" s="67"/>
+      <c r="AN32" s="67"/>
+      <c r="AO32" s="67"/>
+      <c r="AP32" s="68"/>
+      <c r="AQ32" s="69"/>
+      <c r="AR32" s="67"/>
+      <c r="AS32" s="67"/>
+      <c r="AT32" s="67"/>
+      <c r="AU32" s="67"/>
+      <c r="AV32" s="67"/>
+      <c r="AW32" s="67"/>
+      <c r="AX32" s="67"/>
+      <c r="AY32" s="67"/>
+      <c r="AZ32" s="67"/>
+      <c r="BA32" s="67"/>
+      <c r="BB32" s="67"/>
+      <c r="BC32" s="67"/>
+      <c r="BD32" s="67"/>
+      <c r="BE32" s="70"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="72"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="76"/>
-      <c r="L33" s="76"/>
-      <c r="M33" s="76"/>
-      <c r="N33" s="77"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="78"/>
-      <c r="Q33" s="78"/>
-      <c r="R33" s="78"/>
-      <c r="S33" s="78"/>
-      <c r="T33" s="78"/>
-      <c r="U33" s="78"/>
-      <c r="V33" s="78"/>
-      <c r="W33" s="78"/>
-      <c r="X33" s="78"/>
-      <c r="Y33" s="78"/>
-      <c r="Z33" s="78"/>
-      <c r="AA33" s="78"/>
-      <c r="AB33" s="78"/>
-      <c r="AC33" s="78"/>
-      <c r="AD33" s="78"/>
-      <c r="AE33" s="78"/>
-      <c r="AF33" s="78"/>
-      <c r="AG33" s="78"/>
-      <c r="AH33" s="78"/>
-      <c r="AI33" s="78"/>
-      <c r="AJ33" s="78"/>
-      <c r="AK33" s="78"/>
-      <c r="AL33" s="78"/>
-      <c r="AM33" s="78"/>
-      <c r="AN33" s="78"/>
-      <c r="AO33" s="78"/>
-      <c r="AP33" s="79"/>
-      <c r="AQ33" s="80"/>
-      <c r="AR33" s="78"/>
-      <c r="AS33" s="78"/>
-      <c r="AT33" s="78"/>
-      <c r="AU33" s="78"/>
-      <c r="AV33" s="78"/>
-      <c r="AW33" s="78"/>
-      <c r="AX33" s="78"/>
-      <c r="AY33" s="78"/>
-      <c r="AZ33" s="78"/>
-      <c r="BA33" s="78"/>
-      <c r="BB33" s="78"/>
-      <c r="BC33" s="78"/>
-      <c r="BD33" s="78"/>
-      <c r="BE33" s="81"/>
+      <c r="A33" s="61"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="65"/>
+      <c r="L33" s="65"/>
+      <c r="M33" s="65"/>
+      <c r="N33" s="66"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="67"/>
+      <c r="Q33" s="67"/>
+      <c r="R33" s="67"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="67"/>
+      <c r="U33" s="67"/>
+      <c r="V33" s="67"/>
+      <c r="W33" s="67"/>
+      <c r="X33" s="67"/>
+      <c r="Y33" s="67"/>
+      <c r="Z33" s="67"/>
+      <c r="AA33" s="67"/>
+      <c r="AB33" s="67"/>
+      <c r="AC33" s="67"/>
+      <c r="AD33" s="67"/>
+      <c r="AE33" s="67"/>
+      <c r="AF33" s="67"/>
+      <c r="AG33" s="67"/>
+      <c r="AH33" s="67"/>
+      <c r="AI33" s="67"/>
+      <c r="AJ33" s="67"/>
+      <c r="AK33" s="67"/>
+      <c r="AL33" s="67"/>
+      <c r="AM33" s="67"/>
+      <c r="AN33" s="67"/>
+      <c r="AO33" s="67"/>
+      <c r="AP33" s="68"/>
+      <c r="AQ33" s="69"/>
+      <c r="AR33" s="67"/>
+      <c r="AS33" s="67"/>
+      <c r="AT33" s="67"/>
+      <c r="AU33" s="67"/>
+      <c r="AV33" s="67"/>
+      <c r="AW33" s="67"/>
+      <c r="AX33" s="67"/>
+      <c r="AY33" s="67"/>
+      <c r="AZ33" s="67"/>
+      <c r="BA33" s="67"/>
+      <c r="BB33" s="67"/>
+      <c r="BC33" s="67"/>
+      <c r="BD33" s="67"/>
+      <c r="BE33" s="70"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="72"/>
-      <c r="B34" s="73"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
-      <c r="K34" s="76"/>
-      <c r="L34" s="76"/>
-      <c r="M34" s="76"/>
-      <c r="N34" s="77"/>
-      <c r="O34" s="75"/>
-      <c r="P34" s="78"/>
-      <c r="Q34" s="78"/>
-      <c r="R34" s="78"/>
-      <c r="S34" s="78"/>
-      <c r="T34" s="78"/>
-      <c r="U34" s="78"/>
-      <c r="V34" s="78"/>
-      <c r="W34" s="78"/>
-      <c r="X34" s="78"/>
-      <c r="Y34" s="78"/>
-      <c r="Z34" s="78"/>
-      <c r="AA34" s="78"/>
-      <c r="AB34" s="78"/>
-      <c r="AC34" s="78"/>
-      <c r="AD34" s="78"/>
-      <c r="AE34" s="78"/>
-      <c r="AF34" s="78"/>
-      <c r="AG34" s="78"/>
-      <c r="AH34" s="78"/>
-      <c r="AI34" s="78"/>
-      <c r="AJ34" s="78"/>
-      <c r="AK34" s="78"/>
-      <c r="AL34" s="78"/>
-      <c r="AM34" s="78"/>
-      <c r="AN34" s="78"/>
-      <c r="AO34" s="78"/>
-      <c r="AP34" s="79"/>
-      <c r="AQ34" s="80"/>
-      <c r="AR34" s="78"/>
-      <c r="AS34" s="78"/>
-      <c r="AT34" s="78"/>
-      <c r="AU34" s="78"/>
-      <c r="AV34" s="78"/>
-      <c r="AW34" s="78"/>
-      <c r="AX34" s="78"/>
-      <c r="AY34" s="78"/>
-      <c r="AZ34" s="78"/>
-      <c r="BA34" s="78"/>
-      <c r="BB34" s="78"/>
-      <c r="BC34" s="78"/>
-      <c r="BD34" s="78"/>
-      <c r="BE34" s="81"/>
+      <c r="A34" s="61"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="66"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="67"/>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="67"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="67"/>
+      <c r="U34" s="67"/>
+      <c r="V34" s="67"/>
+      <c r="W34" s="67"/>
+      <c r="X34" s="67"/>
+      <c r="Y34" s="67"/>
+      <c r="Z34" s="67"/>
+      <c r="AA34" s="67"/>
+      <c r="AB34" s="67"/>
+      <c r="AC34" s="67"/>
+      <c r="AD34" s="67"/>
+      <c r="AE34" s="67"/>
+      <c r="AF34" s="67"/>
+      <c r="AG34" s="67"/>
+      <c r="AH34" s="67"/>
+      <c r="AI34" s="67"/>
+      <c r="AJ34" s="67"/>
+      <c r="AK34" s="67"/>
+      <c r="AL34" s="67"/>
+      <c r="AM34" s="67"/>
+      <c r="AN34" s="67"/>
+      <c r="AO34" s="67"/>
+      <c r="AP34" s="68"/>
+      <c r="AQ34" s="69"/>
+      <c r="AR34" s="67"/>
+      <c r="AS34" s="67"/>
+      <c r="AT34" s="67"/>
+      <c r="AU34" s="67"/>
+      <c r="AV34" s="67"/>
+      <c r="AW34" s="67"/>
+      <c r="AX34" s="67"/>
+      <c r="AY34" s="67"/>
+      <c r="AZ34" s="67"/>
+      <c r="BA34" s="67"/>
+      <c r="BB34" s="67"/>
+      <c r="BC34" s="67"/>
+      <c r="BD34" s="67"/>
+      <c r="BE34" s="70"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="88"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="91"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="91"/>
-      <c r="P35" s="94"/>
-      <c r="Q35" s="94"/>
-      <c r="R35" s="94"/>
-      <c r="S35" s="94"/>
-      <c r="T35" s="94"/>
-      <c r="U35" s="94"/>
-      <c r="V35" s="94"/>
-      <c r="W35" s="94"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="94"/>
-      <c r="Z35" s="94"/>
-      <c r="AA35" s="94"/>
-      <c r="AB35" s="94"/>
-      <c r="AC35" s="94"/>
-      <c r="AD35" s="94"/>
-      <c r="AE35" s="94"/>
-      <c r="AF35" s="94"/>
-      <c r="AG35" s="94"/>
-      <c r="AH35" s="94"/>
-      <c r="AI35" s="94"/>
-      <c r="AJ35" s="94"/>
-      <c r="AK35" s="94"/>
-      <c r="AL35" s="94"/>
-      <c r="AM35" s="94"/>
-      <c r="AN35" s="94"/>
-      <c r="AO35" s="94"/>
-      <c r="AP35" s="95"/>
-      <c r="AQ35" s="96"/>
-      <c r="AR35" s="94"/>
-      <c r="AS35" s="94"/>
-      <c r="AT35" s="94"/>
-      <c r="AU35" s="94"/>
-      <c r="AV35" s="94"/>
-      <c r="AW35" s="94"/>
-      <c r="AX35" s="94"/>
-      <c r="AY35" s="94"/>
-      <c r="AZ35" s="94"/>
-      <c r="BA35" s="94"/>
-      <c r="BB35" s="94"/>
-      <c r="BC35" s="94"/>
-      <c r="BD35" s="94"/>
-      <c r="BE35" s="97"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="56"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="57"/>
+      <c r="Q35" s="57"/>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="57"/>
+      <c r="V35" s="57"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="57"/>
+      <c r="Y35" s="57"/>
+      <c r="Z35" s="57"/>
+      <c r="AA35" s="57"/>
+      <c r="AB35" s="57"/>
+      <c r="AC35" s="57"/>
+      <c r="AD35" s="57"/>
+      <c r="AE35" s="57"/>
+      <c r="AF35" s="57"/>
+      <c r="AG35" s="57"/>
+      <c r="AH35" s="57"/>
+      <c r="AI35" s="57"/>
+      <c r="AJ35" s="57"/>
+      <c r="AK35" s="57"/>
+      <c r="AL35" s="57"/>
+      <c r="AM35" s="57"/>
+      <c r="AN35" s="57"/>
+      <c r="AO35" s="57"/>
+      <c r="AP35" s="58"/>
+      <c r="AQ35" s="59"/>
+      <c r="AR35" s="57"/>
+      <c r="AS35" s="57"/>
+      <c r="AT35" s="57"/>
+      <c r="AU35" s="57"/>
+      <c r="AV35" s="57"/>
+      <c r="AW35" s="57"/>
+      <c r="AX35" s="57"/>
+      <c r="AY35" s="57"/>
+      <c r="AZ35" s="57"/>
+      <c r="BA35" s="57"/>
+      <c r="BB35" s="57"/>
+      <c r="BC35" s="57"/>
+      <c r="BD35" s="57"/>
+      <c r="BE35" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="H11:N11"/>
     <mergeCell ref="O11:AP11"/>
@@ -16648,27 +16571,98 @@
     <mergeCell ref="H10:N10"/>
     <mergeCell ref="O10:AP10"/>
     <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="AQ34:BE34"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBPA0010_SlsSchdSrch.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBPA0010_SlsSchdSrch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70781FDC-EEA7-4D0C-AC04-7B997649B30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F50794-CE98-4198-BAE2-F52979114183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="3015" windowWidth="19080" windowHeight="10800" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSBBPA0010" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="699">
   <si>
     <t>*</t>
   </si>
@@ -2523,12 +2523,6 @@
     <t>#MA.DT</t>
   </si>
   <si>
-    <t>bill_cst_cd</t>
-  </si>
-  <si>
-    <t>bill_cst_nm</t>
-  </si>
-  <si>
     <t>sls_dpt_cd</t>
   </si>
   <si>
@@ -2541,24 +2535,12 @@
     <t>deal_nm</t>
   </si>
   <si>
-    <t>order_dlv_dt</t>
-  </si>
-  <si>
-    <t>pst_inst_sls_dt</t>
-  </si>
-  <si>
     <t>Product item cd.</t>
   </si>
   <si>
     <t>Product item name</t>
   </si>
   <si>
-    <t>prd_itm_cd</t>
-  </si>
-  <si>
-    <t>prd_itm_nm</t>
-  </si>
-  <si>
     <t>注文書納期ＦＲＯＭ</t>
   </si>
   <si>
@@ -2641,6 +2623,90 @@
   </si>
   <si>
     <t>Project manager user name</t>
+  </si>
+  <si>
+    <t>bcst_cd</t>
+  </si>
+  <si>
+    <t>bcst_nm</t>
+  </si>
+  <si>
+    <t>prd_amt</t>
+  </si>
+  <si>
+    <t>prd_qty</t>
+  </si>
+  <si>
+    <t>cur_cd</t>
+  </si>
+  <si>
+    <t>itm_cd</t>
+  </si>
+  <si>
+    <t>qty</t>
+  </si>
+  <si>
+    <t>upri</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>金額</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>Currency cd.</t>
+  </si>
+  <si>
+    <t>外貨ＣＤ</t>
+  </si>
+  <si>
+    <t>Item cd.</t>
+  </si>
+  <si>
+    <t>品目CD</t>
+  </si>
+  <si>
+    <t>Unit price</t>
+  </si>
+  <si>
+    <t>単価</t>
+  </si>
+  <si>
+    <t>#MA.MONEY</t>
+  </si>
+  <si>
+    <t>#MA.QTY</t>
+  </si>
+  <si>
+    <t>#MA.CUR_CD</t>
+  </si>
+  <si>
+    <t>prod_itm_cd</t>
+  </si>
+  <si>
+    <t>prod_itm_nm</t>
+  </si>
+  <si>
+    <t>ord_dlv_dt</t>
+  </si>
+  <si>
+    <t>post_inst_sls_dt</t>
+  </si>
+  <si>
+    <t>itm_nm</t>
+  </si>
+  <si>
+    <t>品名</t>
+  </si>
+  <si>
+    <t>Item name</t>
   </si>
 </sst>
 </file>
@@ -3427,6 +3493,84 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3488,84 +3632,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3946,7 +4012,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ233"/>
+  <dimension ref="A1:AJ240"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" style="1" customWidth="1"/>
@@ -5547,7 +5613,7 @@
         <v>520</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="G39" s="18" t="s">
         <v>14</v>
@@ -5604,7 +5670,7 @@
         <v>521</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="G40" s="23" t="s">
         <v>14</v>
@@ -5715,10 +5781,10 @@
         <v>38</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>618</v>
@@ -5772,10 +5838,10 @@
         <v>39</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>15</v>
@@ -5829,13 +5895,13 @@
         <v>274</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="H44" s="23"/>
       <c r="I44" s="23" t="s">
@@ -5886,10 +5952,10 @@
         <v>275</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="G45" s="23" t="s">
         <v>15</v>
@@ -5940,13 +6006,13 @@
       <c r="B46" s="23"/>
       <c r="C46" s="23"/>
       <c r="D46" s="23" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="E46" s="24" t="s">
         <v>601</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="G46" s="23" t="s">
         <v>13</v>
@@ -5997,7 +6063,7 @@
       <c r="B47" s="23"/>
       <c r="C47" s="23"/>
       <c r="D47" s="23" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E47" s="24" t="s">
         <v>525</v>
@@ -6064,7 +6130,7 @@
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
       <c r="D48" s="23" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E48" s="24" t="s">
         <v>526</v>
@@ -6248,7 +6314,7 @@
         <v>620</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="H51" s="23"/>
       <c r="I51" s="23" t="s">
@@ -6357,13 +6423,13 @@
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
       <c r="D53" s="23" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="E53" s="24" t="s">
         <v>525</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="G53" s="23" t="s">
         <v>46</v>
@@ -6420,13 +6486,13 @@
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
       <c r="D54" s="23" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E54" s="24" t="s">
         <v>526</v>
       </c>
       <c r="F54" s="23" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="G54" s="23"/>
       <c r="H54" s="23"/>
@@ -6475,7 +6541,7 @@
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>609</v>
@@ -6484,7 +6550,7 @@
         <v>608</v>
       </c>
       <c r="G55" s="23" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="H55" s="23"/>
       <c r="I55" s="23" t="s">
@@ -6538,7 +6604,7 @@
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
       <c r="D56" s="23" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>610</v>
@@ -6593,16 +6659,16 @@
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
       <c r="D57" s="23" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="F57" s="23" t="s">
         <v>629</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="H57" s="23"/>
       <c r="I57" s="23" t="s">
@@ -6656,10 +6722,10 @@
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
       <c r="D58" s="23" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="F58" s="23" t="s">
         <v>630</v>
@@ -6711,7 +6777,7 @@
       <c r="B59" s="23"/>
       <c r="C59" s="23"/>
       <c r="D59" s="23" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>614</v>
@@ -6720,7 +6786,7 @@
         <v>612</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="H59" s="23"/>
       <c r="I59" s="23" t="s">
@@ -6774,7 +6840,7 @@
       <c r="B60" s="23"/>
       <c r="C60" s="23"/>
       <c r="D60" s="23" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E60" s="24" t="s">
         <v>615</v>
@@ -6889,7 +6955,7 @@
       </c>
       <c r="E62" s="24"/>
       <c r="F62" s="23" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="G62" s="23"/>
       <c r="H62" s="23"/>
@@ -13097,7 +13163,7 @@
       <c r="B205" s="18"/>
       <c r="C205" s="18"/>
       <c r="D205" s="18" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="E205" s="19" t="s">
         <v>601</v>
@@ -13154,7 +13220,7 @@
       <c r="B206" s="23"/>
       <c r="C206" s="23"/>
       <c r="D206" s="23" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E206" s="24" t="s">
         <v>603</v>
@@ -13211,7 +13277,7 @@
       <c r="B207" s="23"/>
       <c r="C207" s="23"/>
       <c r="D207" s="23" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E207" s="24" t="s">
         <v>605</v>
@@ -13381,8 +13447,8 @@
       </c>
       <c r="B210" s="23"/>
       <c r="C210" s="23"/>
-      <c r="D210" s="23" t="s">
-        <v>637</v>
+      <c r="D210" s="33" t="s">
+        <v>671</v>
       </c>
       <c r="E210" s="24" t="s">
         <v>622</v>
@@ -13438,8 +13504,8 @@
       </c>
       <c r="B211" s="23"/>
       <c r="C211" s="23"/>
-      <c r="D211" s="23" t="s">
-        <v>638</v>
+      <c r="D211" s="33" t="s">
+        <v>672</v>
       </c>
       <c r="E211" s="24" t="s">
         <v>623</v>
@@ -13496,7 +13562,7 @@
       <c r="B212" s="23"/>
       <c r="C212" s="23"/>
       <c r="D212" s="23" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E212" s="24" t="s">
         <v>609</v>
@@ -13553,7 +13619,7 @@
       <c r="B213" s="23"/>
       <c r="C213" s="23"/>
       <c r="D213" s="23" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E213" s="24" t="s">
         <v>610</v>
@@ -13613,7 +13679,7 @@
         <v>278</v>
       </c>
       <c r="E214" s="24" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="F214" s="23" t="s">
         <v>629</v>
@@ -13670,7 +13736,7 @@
         <v>42</v>
       </c>
       <c r="E215" s="24" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="F215" s="23" t="s">
         <v>630</v>
@@ -13842,10 +13908,10 @@
       <c r="B218" s="23"/>
       <c r="C218" s="23"/>
       <c r="D218" s="23" t="s">
-        <v>647</v>
+        <v>692</v>
       </c>
       <c r="E218" s="24" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="F218" s="23" t="s">
         <v>616</v>
@@ -13899,10 +13965,10 @@
       <c r="B219" s="23"/>
       <c r="C219" s="23"/>
       <c r="D219" s="23" t="s">
-        <v>648</v>
+        <v>693</v>
       </c>
       <c r="E219" s="24" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="F219" s="23" t="s">
         <v>617</v>
@@ -13956,7 +14022,7 @@
       <c r="B220" s="23"/>
       <c r="C220" s="23"/>
       <c r="D220" s="23" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="E220" s="24" t="s">
         <v>634</v>
@@ -14013,7 +14079,7 @@
       <c r="B221" s="23"/>
       <c r="C221" s="23"/>
       <c r="D221" s="23" t="s">
-        <v>644</v>
+        <v>695</v>
       </c>
       <c r="E221" s="24" t="s">
         <v>635</v>
@@ -14064,223 +14130,622 @@
       <c r="AJ221" s="24"/>
     </row>
     <row r="222" spans="1:36">
-      <c r="A222" s="5"/>
-      <c r="AG222" s="36"/>
-      <c r="AH222" s="36"/>
-      <c r="AJ222" s="9"/>
+      <c r="A222" s="23">
+        <v>150</v>
+      </c>
+      <c r="B222" s="28"/>
+      <c r="C222" s="28"/>
+      <c r="D222" s="28" t="s">
+        <v>673</v>
+      </c>
+      <c r="E222" s="31" t="s">
+        <v>679</v>
+      </c>
+      <c r="F222" s="28" t="s">
+        <v>680</v>
+      </c>
+      <c r="G222" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H222" s="28"/>
+      <c r="I222" s="28" t="s">
+        <v>689</v>
+      </c>
+      <c r="J222" s="28"/>
+      <c r="K222" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="L222" s="28"/>
+      <c r="M222" s="28"/>
+      <c r="N222" s="28"/>
+      <c r="O222" s="28"/>
+      <c r="P222" s="28"/>
+      <c r="Q222" s="28"/>
+      <c r="R222" s="28"/>
+      <c r="S222" s="28"/>
+      <c r="T222" s="28"/>
+      <c r="U222" s="28"/>
+      <c r="V222" s="28"/>
+      <c r="W222" s="28"/>
+      <c r="X222" s="28"/>
+      <c r="Z222" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA222" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB222" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AC222" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AG222" s="28"/>
+      <c r="AH222" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ222" s="31"/>
     </row>
     <row r="223" spans="1:36">
-      <c r="A223" s="28">
-        <v>160</v>
-      </c>
-      <c r="B223" s="28" t="s">
-        <v>0</v>
-      </c>
+      <c r="A223" s="23">
+        <v>150</v>
+      </c>
+      <c r="B223" s="28"/>
       <c r="C223" s="28"/>
       <c r="D223" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="E223" s="29"/>
-      <c r="F223" s="28"/>
-      <c r="G223" s="28"/>
+        <v>674</v>
+      </c>
+      <c r="E223" s="31" t="s">
+        <v>681</v>
+      </c>
+      <c r="F223" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="G223" s="23" t="s">
+        <v>13</v>
+      </c>
       <c r="H223" s="28"/>
       <c r="I223" s="28" t="s">
-        <v>327</v>
+        <v>690</v>
       </c>
       <c r="J223" s="28"/>
-      <c r="K223" s="28" t="s">
-        <v>328</v>
+      <c r="K223" s="23" t="s">
+        <v>340</v>
       </c>
       <c r="L223" s="28"/>
-      <c r="M223" s="28" t="s">
-        <v>314</v>
-      </c>
+      <c r="M223" s="28"/>
       <c r="N223" s="28"/>
       <c r="O223" s="28"/>
       <c r="P223" s="28"/>
-      <c r="Q223" s="32"/>
-      <c r="R223" s="32"/>
-      <c r="S223" s="32"/>
-      <c r="T223" s="32"/>
-      <c r="U223" s="32"/>
-      <c r="V223" s="32"/>
-      <c r="W223" s="32"/>
-      <c r="X223" s="32"/>
-      <c r="Y223" s="32"/>
-      <c r="Z223" s="32"/>
-      <c r="AA223" s="32"/>
-      <c r="AB223" s="32"/>
-      <c r="AC223" s="32"/>
-      <c r="AD223" s="32"/>
-      <c r="AE223" s="32"/>
-      <c r="AF223" s="32"/>
+      <c r="Q223" s="28"/>
+      <c r="R223" s="28"/>
+      <c r="S223" s="28"/>
+      <c r="T223" s="28"/>
+      <c r="U223" s="28"/>
+      <c r="V223" s="28"/>
+      <c r="W223" s="28"/>
+      <c r="X223" s="28"/>
+      <c r="Z223" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA223" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB223" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AC223" s="23" t="s">
+        <v>337</v>
+      </c>
       <c r="AG223" s="28"/>
-      <c r="AH223" s="28"/>
-      <c r="AI223" s="32"/>
+      <c r="AH223" s="23" t="s">
+        <v>336</v>
+      </c>
       <c r="AJ223" s="31"/>
     </row>
     <row r="224" spans="1:36">
       <c r="A224" s="23">
-        <v>160</v>
-      </c>
-      <c r="B224" s="23"/>
-      <c r="C224" s="23"/>
-      <c r="D224" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="E224" s="24" t="s">
-        <v>590</v>
-      </c>
-      <c r="F224" s="23" t="s">
-        <v>170</v>
+        <v>150</v>
+      </c>
+      <c r="B224" s="28"/>
+      <c r="C224" s="28"/>
+      <c r="D224" s="28" t="s">
+        <v>675</v>
+      </c>
+      <c r="E224" s="31" t="s">
+        <v>683</v>
+      </c>
+      <c r="F224" s="28" t="s">
+        <v>684</v>
       </c>
       <c r="G224" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H224" s="28"/>
+      <c r="I224" s="28" t="s">
+        <v>691</v>
+      </c>
+      <c r="J224" s="28"/>
+      <c r="K224" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="L224" s="28"/>
+      <c r="M224" s="28"/>
+      <c r="N224" s="28"/>
+      <c r="O224" s="28"/>
+      <c r="P224" s="28"/>
+      <c r="Q224" s="28"/>
+      <c r="R224" s="28"/>
+      <c r="S224" s="28"/>
+      <c r="T224" s="28"/>
+      <c r="U224" s="28"/>
+      <c r="V224" s="28"/>
+      <c r="W224" s="28"/>
+      <c r="X224" s="28"/>
+      <c r="Z224" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA224" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB224" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AC224" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AG224" s="28"/>
+      <c r="AH224" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ224" s="31"/>
+    </row>
+    <row r="225" spans="1:36">
+      <c r="A225" s="23">
+        <v>150</v>
+      </c>
+      <c r="B225" s="28"/>
+      <c r="C225" s="28"/>
+      <c r="D225" s="28" t="s">
+        <v>676</v>
+      </c>
+      <c r="E225" s="31" t="s">
+        <v>685</v>
+      </c>
+      <c r="F225" s="28" t="s">
+        <v>686</v>
+      </c>
+      <c r="G225" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H225" s="28"/>
+      <c r="I225" s="28" t="s">
+        <v>632</v>
+      </c>
+      <c r="J225" s="28"/>
+      <c r="K225" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="L225" s="28"/>
+      <c r="M225" s="28"/>
+      <c r="N225" s="28"/>
+      <c r="O225" s="28"/>
+      <c r="P225" s="28"/>
+      <c r="Q225" s="28"/>
+      <c r="R225" s="28"/>
+      <c r="S225" s="28"/>
+      <c r="T225" s="28"/>
+      <c r="U225" s="28"/>
+      <c r="V225" s="28"/>
+      <c r="W225" s="28"/>
+      <c r="X225" s="28"/>
+      <c r="Z225" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA225" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB225" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AC225" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AG225" s="28"/>
+      <c r="AH225" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ225" s="31"/>
+    </row>
+    <row r="226" spans="1:36">
+      <c r="A226" s="23">
+        <v>150</v>
+      </c>
+      <c r="B226" s="23"/>
+      <c r="C226" s="23"/>
+      <c r="D226" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="E226" s="24" t="s">
+        <v>698</v>
+      </c>
+      <c r="F226" s="23" t="s">
+        <v>697</v>
+      </c>
+      <c r="G226" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H224" s="23"/>
-      <c r="I224" s="23" t="s">
-        <v>472</v>
-      </c>
-      <c r="J224" s="23"/>
-      <c r="K224" s="23" t="s">
-        <v>473</v>
-      </c>
-      <c r="L224" s="23"/>
-      <c r="M224" s="23"/>
-      <c r="N224" s="23"/>
-      <c r="O224" s="23"/>
-      <c r="P224" s="23"/>
-      <c r="Q224" s="23"/>
-      <c r="R224" s="23"/>
-      <c r="S224" s="23"/>
-      <c r="T224" s="23" t="s">
-        <v>475</v>
-      </c>
-      <c r="U224" s="23"/>
-      <c r="V224" s="23"/>
-      <c r="W224" s="23"/>
-      <c r="X224" s="23"/>
-      <c r="Z224" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="AA224" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="AB224" s="23" t="s">
+      <c r="H226" s="23"/>
+      <c r="I226" s="23" t="s">
+        <v>633</v>
+      </c>
+      <c r="J226" s="23"/>
+      <c r="K226" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="L226" s="23"/>
+      <c r="M226" s="23"/>
+      <c r="N226" s="23"/>
+      <c r="O226" s="23"/>
+      <c r="P226" s="23"/>
+      <c r="Q226" s="23"/>
+      <c r="R226" s="23"/>
+      <c r="S226" s="23"/>
+      <c r="T226" s="23"/>
+      <c r="U226" s="23"/>
+      <c r="V226" s="23"/>
+      <c r="W226" s="23"/>
+      <c r="X226" s="23"/>
+      <c r="Z226" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA226" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB226" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AC226" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AG226" s="23"/>
+      <c r="AH226" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="AC224" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="AG224" s="23"/>
-      <c r="AH224" s="23"/>
-      <c r="AJ224" s="24"/>
-    </row>
-    <row r="225" spans="1:36">
-      <c r="A225" s="2"/>
-      <c r="B225" s="3"/>
-      <c r="C225" s="3"/>
-      <c r="D225" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="E225" s="4"/>
-      <c r="F225" s="4"/>
-      <c r="G225" s="4"/>
-      <c r="H225" s="4"/>
-      <c r="I225" s="4"/>
-      <c r="J225" s="4"/>
-      <c r="K225" s="4"/>
-      <c r="L225" s="4"/>
-      <c r="M225" s="4"/>
-      <c r="N225" s="4"/>
-      <c r="O225" s="4"/>
-      <c r="P225" s="4"/>
-      <c r="Q225" s="4"/>
-      <c r="R225" s="4"/>
-      <c r="S225" s="4"/>
-      <c r="T225" s="4"/>
-      <c r="U225" s="4"/>
-      <c r="V225" s="4"/>
-      <c r="W225" s="4"/>
-      <c r="X225" s="4"/>
-      <c r="Y225" s="4"/>
-      <c r="Z225" s="4"/>
-      <c r="AA225" s="4"/>
-      <c r="AB225" s="4"/>
-      <c r="AC225" s="4"/>
-      <c r="AD225" s="4"/>
-      <c r="AE225" s="4"/>
-      <c r="AF225" s="4"/>
-      <c r="AG225" s="4"/>
-      <c r="AH225" s="4"/>
-      <c r="AI225" s="4"/>
-      <c r="AJ225" s="8"/>
-    </row>
-    <row r="226" spans="1:36">
-      <c r="A226" s="5"/>
-      <c r="AJ226" s="9"/>
+      <c r="AJ226" s="24"/>
     </row>
     <row r="227" spans="1:36">
-      <c r="A227" s="5"/>
-      <c r="AJ227" s="9"/>
+      <c r="A227" s="23">
+        <v>150</v>
+      </c>
+      <c r="B227" s="28"/>
+      <c r="C227" s="28"/>
+      <c r="D227" s="28" t="s">
+        <v>677</v>
+      </c>
+      <c r="E227" s="31" t="s">
+        <v>681</v>
+      </c>
+      <c r="F227" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="G227" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H227" s="28"/>
+      <c r="I227" s="28" t="s">
+        <v>690</v>
+      </c>
+      <c r="J227" s="28"/>
+      <c r="K227" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="L227" s="28"/>
+      <c r="M227" s="28"/>
+      <c r="N227" s="28"/>
+      <c r="O227" s="28"/>
+      <c r="P227" s="28"/>
+      <c r="Q227" s="28"/>
+      <c r="R227" s="28"/>
+      <c r="S227" s="28"/>
+      <c r="T227" s="28"/>
+      <c r="U227" s="28"/>
+      <c r="V227" s="28"/>
+      <c r="W227" s="28"/>
+      <c r="X227" s="28"/>
+      <c r="Z227" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA227" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB227" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AC227" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AG227" s="28"/>
+      <c r="AH227" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ227" s="31"/>
     </row>
     <row r="228" spans="1:36">
-      <c r="A228" s="5"/>
-      <c r="AJ228" s="9"/>
+      <c r="A228" s="23">
+        <v>150</v>
+      </c>
+      <c r="B228" s="28"/>
+      <c r="C228" s="28"/>
+      <c r="D228" s="28" t="s">
+        <v>678</v>
+      </c>
+      <c r="E228" s="31" t="s">
+        <v>687</v>
+      </c>
+      <c r="F228" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="G228" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H228" s="28"/>
+      <c r="I228" s="28" t="s">
+        <v>689</v>
+      </c>
+      <c r="J228" s="28"/>
+      <c r="K228" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="L228" s="28"/>
+      <c r="M228" s="28"/>
+      <c r="N228" s="28"/>
+      <c r="O228" s="28"/>
+      <c r="P228" s="28"/>
+      <c r="Q228" s="28"/>
+      <c r="R228" s="28"/>
+      <c r="S228" s="28"/>
+      <c r="T228" s="28"/>
+      <c r="U228" s="28"/>
+      <c r="V228" s="28"/>
+      <c r="W228" s="28"/>
+      <c r="X228" s="28"/>
+      <c r="Z228" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA228" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB228" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AC228" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="AG228" s="28"/>
+      <c r="AH228" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ228" s="31"/>
     </row>
     <row r="229" spans="1:36">
       <c r="A229" s="5"/>
+      <c r="AG229" s="36"/>
+      <c r="AH229" s="36"/>
       <c r="AJ229" s="9"/>
     </row>
     <row r="230" spans="1:36">
-      <c r="A230" s="5"/>
-      <c r="AJ230" s="9"/>
+      <c r="A230" s="28">
+        <v>160</v>
+      </c>
+      <c r="B230" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C230" s="28"/>
+      <c r="D230" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E230" s="29"/>
+      <c r="F230" s="28"/>
+      <c r="G230" s="28"/>
+      <c r="H230" s="28"/>
+      <c r="I230" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="J230" s="28"/>
+      <c r="K230" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="L230" s="28"/>
+      <c r="M230" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="N230" s="28"/>
+      <c r="O230" s="28"/>
+      <c r="P230" s="28"/>
+      <c r="Q230" s="32"/>
+      <c r="R230" s="32"/>
+      <c r="S230" s="32"/>
+      <c r="T230" s="32"/>
+      <c r="U230" s="32"/>
+      <c r="V230" s="32"/>
+      <c r="W230" s="32"/>
+      <c r="X230" s="32"/>
+      <c r="Y230" s="32"/>
+      <c r="Z230" s="32"/>
+      <c r="AA230" s="32"/>
+      <c r="AB230" s="32"/>
+      <c r="AC230" s="32"/>
+      <c r="AD230" s="32"/>
+      <c r="AE230" s="32"/>
+      <c r="AF230" s="32"/>
+      <c r="AG230" s="28"/>
+      <c r="AH230" s="28"/>
+      <c r="AI230" s="32"/>
+      <c r="AJ230" s="31"/>
     </row>
     <row r="231" spans="1:36">
-      <c r="A231" s="5"/>
-      <c r="AJ231" s="9"/>
+      <c r="A231" s="23">
+        <v>160</v>
+      </c>
+      <c r="B231" s="23"/>
+      <c r="C231" s="23"/>
+      <c r="D231" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E231" s="24" t="s">
+        <v>590</v>
+      </c>
+      <c r="F231" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="G231" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H231" s="23"/>
+      <c r="I231" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="J231" s="23"/>
+      <c r="K231" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="L231" s="23"/>
+      <c r="M231" s="23"/>
+      <c r="N231" s="23"/>
+      <c r="O231" s="23"/>
+      <c r="P231" s="23"/>
+      <c r="Q231" s="23"/>
+      <c r="R231" s="23"/>
+      <c r="S231" s="23"/>
+      <c r="T231" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="U231" s="23"/>
+      <c r="V231" s="23"/>
+      <c r="W231" s="23"/>
+      <c r="X231" s="23"/>
+      <c r="Z231" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="AA231" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="AB231" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="AC231" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="AG231" s="23"/>
+      <c r="AH231" s="23"/>
+      <c r="AJ231" s="24"/>
     </row>
     <row r="232" spans="1:36">
-      <c r="A232" s="5"/>
-      <c r="AJ232" s="9"/>
+      <c r="A232" s="2"/>
+      <c r="B232" s="3"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E232" s="4"/>
+      <c r="F232" s="4"/>
+      <c r="G232" s="4"/>
+      <c r="H232" s="4"/>
+      <c r="I232" s="4"/>
+      <c r="J232" s="4"/>
+      <c r="K232" s="4"/>
+      <c r="L232" s="4"/>
+      <c r="M232" s="4"/>
+      <c r="N232" s="4"/>
+      <c r="O232" s="4"/>
+      <c r="P232" s="4"/>
+      <c r="Q232" s="4"/>
+      <c r="R232" s="4"/>
+      <c r="S232" s="4"/>
+      <c r="T232" s="4"/>
+      <c r="U232" s="4"/>
+      <c r="V232" s="4"/>
+      <c r="W232" s="4"/>
+      <c r="X232" s="4"/>
+      <c r="Y232" s="4"/>
+      <c r="Z232" s="4"/>
+      <c r="AA232" s="4"/>
+      <c r="AB232" s="4"/>
+      <c r="AC232" s="4"/>
+      <c r="AD232" s="4"/>
+      <c r="AE232" s="4"/>
+      <c r="AF232" s="4"/>
+      <c r="AG232" s="4"/>
+      <c r="AH232" s="4"/>
+      <c r="AI232" s="4"/>
+      <c r="AJ232" s="8"/>
     </row>
     <row r="233" spans="1:36">
-      <c r="A233" s="16"/>
-      <c r="B233" s="26"/>
-      <c r="C233" s="26"/>
-      <c r="D233" s="26"/>
-      <c r="E233" s="26"/>
-      <c r="F233" s="26"/>
-      <c r="G233" s="26"/>
-      <c r="H233" s="26"/>
-      <c r="I233" s="26"/>
-      <c r="J233" s="26"/>
-      <c r="K233" s="26"/>
-      <c r="L233" s="26"/>
-      <c r="M233" s="26"/>
-      <c r="N233" s="26"/>
-      <c r="O233" s="26"/>
-      <c r="P233" s="26"/>
-      <c r="Q233" s="26"/>
-      <c r="R233" s="26"/>
-      <c r="S233" s="26"/>
-      <c r="T233" s="26"/>
-      <c r="U233" s="26"/>
-      <c r="V233" s="26"/>
-      <c r="W233" s="26"/>
-      <c r="X233" s="26"/>
-      <c r="Y233" s="26"/>
-      <c r="Z233" s="26"/>
-      <c r="AA233" s="26"/>
-      <c r="AB233" s="26"/>
-      <c r="AC233" s="26"/>
-      <c r="AD233" s="26"/>
-      <c r="AE233" s="26"/>
-      <c r="AF233" s="26"/>
-      <c r="AG233" s="26"/>
-      <c r="AH233" s="26"/>
-      <c r="AI233" s="26"/>
-      <c r="AJ233" s="38"/>
+      <c r="A233" s="5"/>
+      <c r="AJ233" s="9"/>
+    </row>
+    <row r="234" spans="1:36">
+      <c r="A234" s="5"/>
+      <c r="AJ234" s="9"/>
+    </row>
+    <row r="235" spans="1:36">
+      <c r="A235" s="5"/>
+      <c r="AJ235" s="9"/>
+    </row>
+    <row r="236" spans="1:36">
+      <c r="A236" s="5"/>
+      <c r="AJ236" s="9"/>
+    </row>
+    <row r="237" spans="1:36">
+      <c r="A237" s="5"/>
+      <c r="AJ237" s="9"/>
+    </row>
+    <row r="238" spans="1:36">
+      <c r="A238" s="5"/>
+      <c r="AJ238" s="9"/>
+    </row>
+    <row r="239" spans="1:36">
+      <c r="A239" s="5"/>
+      <c r="AJ239" s="9"/>
+    </row>
+    <row r="240" spans="1:36">
+      <c r="A240" s="16"/>
+      <c r="B240" s="26"/>
+      <c r="C240" s="26"/>
+      <c r="D240" s="26"/>
+      <c r="E240" s="26"/>
+      <c r="F240" s="26"/>
+      <c r="G240" s="26"/>
+      <c r="H240" s="26"/>
+      <c r="I240" s="26"/>
+      <c r="J240" s="26"/>
+      <c r="K240" s="26"/>
+      <c r="L240" s="26"/>
+      <c r="M240" s="26"/>
+      <c r="N240" s="26"/>
+      <c r="O240" s="26"/>
+      <c r="P240" s="26"/>
+      <c r="Q240" s="26"/>
+      <c r="R240" s="26"/>
+      <c r="S240" s="26"/>
+      <c r="T240" s="26"/>
+      <c r="U240" s="26"/>
+      <c r="V240" s="26"/>
+      <c r="W240" s="26"/>
+      <c r="X240" s="26"/>
+      <c r="Y240" s="26"/>
+      <c r="Z240" s="26"/>
+      <c r="AA240" s="26"/>
+      <c r="AB240" s="26"/>
+      <c r="AC240" s="26"/>
+      <c r="AD240" s="26"/>
+      <c r="AE240" s="26"/>
+      <c r="AF240" s="26"/>
+      <c r="AG240" s="26"/>
+      <c r="AH240" s="26"/>
+      <c r="AI240" s="26"/>
+      <c r="AJ240" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -14456,65 +14921,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="52"/>
-      <c r="AF1" s="52"/>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="52"/>
-      <c r="BB1" s="52"/>
-      <c r="BC1" s="52"/>
-      <c r="BD1" s="52"/>
-      <c r="BE1" s="53"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
+      <c r="AM1" s="78"/>
+      <c r="AN1" s="78"/>
+      <c r="AO1" s="78"/>
+      <c r="AP1" s="78"/>
+      <c r="AQ1" s="78"/>
+      <c r="AR1" s="78"/>
+      <c r="AS1" s="78"/>
+      <c r="AT1" s="78"/>
+      <c r="AU1" s="78"/>
+      <c r="AV1" s="78"/>
+      <c r="AW1" s="78"/>
+      <c r="AX1" s="78"/>
+      <c r="AY1" s="78"/>
+      <c r="AZ1" s="78"/>
+      <c r="BA1" s="78"/>
+      <c r="BB1" s="78"/>
+      <c r="BC1" s="78"/>
+      <c r="BD1" s="78"/>
+      <c r="BE1" s="79"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="11"/>
@@ -14561,2064 +15026,1993 @@
       <c r="AP2" s="11"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57" t="s">
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="57" t="s">
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="58"/>
-      <c r="Y3" s="58"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="58"/>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="58"/>
-      <c r="AD3" s="58"/>
-      <c r="AE3" s="58"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="58"/>
-      <c r="AH3" s="58"/>
-      <c r="AI3" s="58"/>
-      <c r="AJ3" s="58"/>
-      <c r="AK3" s="58"/>
-      <c r="AL3" s="58"/>
-      <c r="AM3" s="58"/>
-      <c r="AN3" s="58"/>
-      <c r="AO3" s="58"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="57" t="s">
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
+      <c r="X3" s="84"/>
+      <c r="Y3" s="84"/>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="84"/>
+      <c r="AC3" s="84"/>
+      <c r="AD3" s="84"/>
+      <c r="AE3" s="84"/>
+      <c r="AF3" s="84"/>
+      <c r="AG3" s="84"/>
+      <c r="AH3" s="84"/>
+      <c r="AI3" s="84"/>
+      <c r="AJ3" s="84"/>
+      <c r="AK3" s="84"/>
+      <c r="AL3" s="84"/>
+      <c r="AM3" s="84"/>
+      <c r="AN3" s="84"/>
+      <c r="AO3" s="84"/>
+      <c r="AP3" s="85"/>
+      <c r="AQ3" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="AR3" s="60"/>
-      <c r="AS3" s="60"/>
-      <c r="AT3" s="60"/>
-      <c r="AU3" s="60"/>
-      <c r="AV3" s="60"/>
-      <c r="AW3" s="60"/>
-      <c r="AX3" s="60"/>
-      <c r="AY3" s="60"/>
-      <c r="AZ3" s="60"/>
-      <c r="BA3" s="60"/>
-      <c r="BB3" s="60"/>
-      <c r="BC3" s="60"/>
-      <c r="BD3" s="60"/>
-      <c r="BE3" s="61"/>
+      <c r="AR3" s="86"/>
+      <c r="AS3" s="86"/>
+      <c r="AT3" s="86"/>
+      <c r="AU3" s="86"/>
+      <c r="AV3" s="86"/>
+      <c r="AW3" s="86"/>
+      <c r="AX3" s="86"/>
+      <c r="AY3" s="86"/>
+      <c r="AZ3" s="86"/>
+      <c r="BA3" s="86"/>
+      <c r="BB3" s="86"/>
+      <c r="BC3" s="86"/>
+      <c r="BD3" s="86"/>
+      <c r="BE3" s="87"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="88">
         <v>1</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="65" t="s">
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="68"/>
-      <c r="U4" s="68"/>
-      <c r="V4" s="68"/>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
-      <c r="Y4" s="68"/>
-      <c r="Z4" s="68"/>
-      <c r="AA4" s="68"/>
-      <c r="AB4" s="68"/>
-      <c r="AC4" s="68"/>
-      <c r="AD4" s="68"/>
-      <c r="AE4" s="68"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
-      <c r="AM4" s="68"/>
-      <c r="AN4" s="68"/>
-      <c r="AO4" s="68"/>
-      <c r="AP4" s="69"/>
-      <c r="AQ4" s="70"/>
-      <c r="AR4" s="68"/>
-      <c r="AS4" s="68"/>
-      <c r="AT4" s="68"/>
-      <c r="AU4" s="68"/>
-      <c r="AV4" s="68"/>
-      <c r="AW4" s="68"/>
-      <c r="AX4" s="68"/>
-      <c r="AY4" s="68"/>
-      <c r="AZ4" s="68"/>
-      <c r="BA4" s="68"/>
-      <c r="BB4" s="68"/>
-      <c r="BC4" s="68"/>
-      <c r="BD4" s="68"/>
-      <c r="BE4" s="71"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="94"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95"/>
+      <c r="AQ4" s="96"/>
+      <c r="AR4" s="94"/>
+      <c r="AS4" s="94"/>
+      <c r="AT4" s="94"/>
+      <c r="AU4" s="94"/>
+      <c r="AV4" s="94"/>
+      <c r="AW4" s="94"/>
+      <c r="AX4" s="94"/>
+      <c r="AY4" s="94"/>
+      <c r="AZ4" s="94"/>
+      <c r="BA4" s="94"/>
+      <c r="BB4" s="94"/>
+      <c r="BC4" s="94"/>
+      <c r="BD4" s="94"/>
+      <c r="BE4" s="97"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1">
-      <c r="A5" s="72">
+      <c r="A5" s="61">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="82" t="s">
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="71" t="s">
         <v>593</v>
       </c>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="83"/>
-      <c r="Y5" s="83"/>
-      <c r="Z5" s="83"/>
-      <c r="AA5" s="83"/>
-      <c r="AB5" s="83"/>
-      <c r="AC5" s="83"/>
-      <c r="AD5" s="83"/>
-      <c r="AE5" s="83"/>
-      <c r="AF5" s="83"/>
-      <c r="AG5" s="83"/>
-      <c r="AH5" s="83"/>
-      <c r="AI5" s="83"/>
-      <c r="AJ5" s="83"/>
-      <c r="AK5" s="83"/>
-      <c r="AL5" s="83"/>
-      <c r="AM5" s="83"/>
-      <c r="AN5" s="83"/>
-      <c r="AO5" s="83"/>
-      <c r="AP5" s="84"/>
-      <c r="AQ5" s="85" t="s">
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="72"/>
+      <c r="U5" s="72"/>
+      <c r="V5" s="72"/>
+      <c r="W5" s="72"/>
+      <c r="X5" s="72"/>
+      <c r="Y5" s="72"/>
+      <c r="Z5" s="72"/>
+      <c r="AA5" s="72"/>
+      <c r="AB5" s="72"/>
+      <c r="AC5" s="72"/>
+      <c r="AD5" s="72"/>
+      <c r="AE5" s="72"/>
+      <c r="AF5" s="72"/>
+      <c r="AG5" s="72"/>
+      <c r="AH5" s="72"/>
+      <c r="AI5" s="72"/>
+      <c r="AJ5" s="72"/>
+      <c r="AK5" s="72"/>
+      <c r="AL5" s="72"/>
+      <c r="AM5" s="72"/>
+      <c r="AN5" s="72"/>
+      <c r="AO5" s="72"/>
+      <c r="AP5" s="73"/>
+      <c r="AQ5" s="74" t="s">
         <v>594</v>
       </c>
-      <c r="AR5" s="86"/>
-      <c r="AS5" s="86"/>
-      <c r="AT5" s="86"/>
-      <c r="AU5" s="86"/>
-      <c r="AV5" s="86"/>
-      <c r="AW5" s="86"/>
-      <c r="AX5" s="86"/>
-      <c r="AY5" s="86"/>
-      <c r="AZ5" s="86"/>
-      <c r="BA5" s="86"/>
-      <c r="BB5" s="86"/>
-      <c r="BC5" s="86"/>
-      <c r="BD5" s="86"/>
-      <c r="BE5" s="87"/>
+      <c r="AR5" s="75"/>
+      <c r="AS5" s="75"/>
+      <c r="AT5" s="75"/>
+      <c r="AU5" s="75"/>
+      <c r="AV5" s="75"/>
+      <c r="AW5" s="75"/>
+      <c r="AX5" s="75"/>
+      <c r="AY5" s="75"/>
+      <c r="AZ5" s="75"/>
+      <c r="BA5" s="75"/>
+      <c r="BB5" s="75"/>
+      <c r="BC5" s="75"/>
+      <c r="BD5" s="75"/>
+      <c r="BE5" s="76"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1">
-      <c r="A6" s="72"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="75"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78"/>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
-      <c r="V6" s="78"/>
-      <c r="W6" s="78"/>
-      <c r="X6" s="78"/>
-      <c r="Y6" s="78"/>
-      <c r="Z6" s="78"/>
-      <c r="AA6" s="78"/>
-      <c r="AB6" s="78"/>
-      <c r="AC6" s="78"/>
-      <c r="AD6" s="78"/>
-      <c r="AE6" s="78"/>
-      <c r="AF6" s="78"/>
-      <c r="AG6" s="78"/>
-      <c r="AH6" s="78"/>
-      <c r="AI6" s="78"/>
-      <c r="AJ6" s="78"/>
-      <c r="AK6" s="78"/>
-      <c r="AL6" s="78"/>
-      <c r="AM6" s="78"/>
-      <c r="AN6" s="78"/>
-      <c r="AO6" s="78"/>
-      <c r="AP6" s="79"/>
-      <c r="AQ6" s="80"/>
-      <c r="AR6" s="78"/>
-      <c r="AS6" s="78"/>
-      <c r="AT6" s="78"/>
-      <c r="AU6" s="78"/>
-      <c r="AV6" s="78"/>
-      <c r="AW6" s="78"/>
-      <c r="AX6" s="78"/>
-      <c r="AY6" s="78"/>
-      <c r="AZ6" s="78"/>
-      <c r="BA6" s="78"/>
-      <c r="BB6" s="78"/>
-      <c r="BC6" s="78"/>
-      <c r="BD6" s="78"/>
-      <c r="BE6" s="81"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="67"/>
+      <c r="AL6" s="67"/>
+      <c r="AM6" s="67"/>
+      <c r="AN6" s="67"/>
+      <c r="AO6" s="67"/>
+      <c r="AP6" s="68"/>
+      <c r="AQ6" s="69"/>
+      <c r="AR6" s="67"/>
+      <c r="AS6" s="67"/>
+      <c r="AT6" s="67"/>
+      <c r="AU6" s="67"/>
+      <c r="AV6" s="67"/>
+      <c r="AW6" s="67"/>
+      <c r="AX6" s="67"/>
+      <c r="AY6" s="67"/>
+      <c r="AZ6" s="67"/>
+      <c r="BA6" s="67"/>
+      <c r="BB6" s="67"/>
+      <c r="BC6" s="67"/>
+      <c r="BD6" s="67"/>
+      <c r="BE6" s="70"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="72"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="76"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="78"/>
-      <c r="S7" s="78"/>
-      <c r="T7" s="78"/>
-      <c r="U7" s="78"/>
-      <c r="V7" s="78"/>
-      <c r="W7" s="78"/>
-      <c r="X7" s="78"/>
-      <c r="Y7" s="78"/>
-      <c r="Z7" s="78"/>
-      <c r="AA7" s="78"/>
-      <c r="AB7" s="78"/>
-      <c r="AC7" s="78"/>
-      <c r="AD7" s="78"/>
-      <c r="AE7" s="78"/>
-      <c r="AF7" s="78"/>
-      <c r="AG7" s="78"/>
-      <c r="AH7" s="78"/>
-      <c r="AI7" s="78"/>
-      <c r="AJ7" s="78"/>
-      <c r="AK7" s="78"/>
-      <c r="AL7" s="78"/>
-      <c r="AM7" s="78"/>
-      <c r="AN7" s="78"/>
-      <c r="AO7" s="78"/>
-      <c r="AP7" s="79"/>
-      <c r="AQ7" s="80"/>
-      <c r="AR7" s="78"/>
-      <c r="AS7" s="78"/>
-      <c r="AT7" s="78"/>
-      <c r="AU7" s="78"/>
-      <c r="AV7" s="78"/>
-      <c r="AW7" s="78"/>
-      <c r="AX7" s="78"/>
-      <c r="AY7" s="78"/>
-      <c r="AZ7" s="78"/>
-      <c r="BA7" s="78"/>
-      <c r="BB7" s="78"/>
-      <c r="BC7" s="78"/>
-      <c r="BD7" s="78"/>
-      <c r="BE7" s="81"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+      <c r="U7" s="67"/>
+      <c r="V7" s="67"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="67"/>
+      <c r="Z7" s="67"/>
+      <c r="AA7" s="67"/>
+      <c r="AB7" s="67"/>
+      <c r="AC7" s="67"/>
+      <c r="AD7" s="67"/>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="67"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
+      <c r="AK7" s="67"/>
+      <c r="AL7" s="67"/>
+      <c r="AM7" s="67"/>
+      <c r="AN7" s="67"/>
+      <c r="AO7" s="67"/>
+      <c r="AP7" s="68"/>
+      <c r="AQ7" s="69"/>
+      <c r="AR7" s="67"/>
+      <c r="AS7" s="67"/>
+      <c r="AT7" s="67"/>
+      <c r="AU7" s="67"/>
+      <c r="AV7" s="67"/>
+      <c r="AW7" s="67"/>
+      <c r="AX7" s="67"/>
+      <c r="AY7" s="67"/>
+      <c r="AZ7" s="67"/>
+      <c r="BA7" s="67"/>
+      <c r="BB7" s="67"/>
+      <c r="BC7" s="67"/>
+      <c r="BD7" s="67"/>
+      <c r="BE7" s="70"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="72"/>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="76"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="75"/>
-      <c r="P8" s="78"/>
-      <c r="Q8" s="78"/>
-      <c r="R8" s="78"/>
-      <c r="S8" s="78"/>
-      <c r="T8" s="78"/>
-      <c r="U8" s="78"/>
-      <c r="V8" s="78"/>
-      <c r="W8" s="78"/>
-      <c r="X8" s="78"/>
-      <c r="Y8" s="78"/>
-      <c r="Z8" s="78"/>
-      <c r="AA8" s="78"/>
-      <c r="AB8" s="78"/>
-      <c r="AC8" s="78"/>
-      <c r="AD8" s="78"/>
-      <c r="AE8" s="78"/>
-      <c r="AF8" s="78"/>
-      <c r="AG8" s="78"/>
-      <c r="AH8" s="78"/>
-      <c r="AI8" s="78"/>
-      <c r="AJ8" s="78"/>
-      <c r="AK8" s="78"/>
-      <c r="AL8" s="78"/>
-      <c r="AM8" s="78"/>
-      <c r="AN8" s="78"/>
-      <c r="AO8" s="78"/>
-      <c r="AP8" s="79"/>
-      <c r="AQ8" s="80"/>
-      <c r="AR8" s="78"/>
-      <c r="AS8" s="78"/>
-      <c r="AT8" s="78"/>
-      <c r="AU8" s="78"/>
-      <c r="AV8" s="78"/>
-      <c r="AW8" s="78"/>
-      <c r="AX8" s="78"/>
-      <c r="AY8" s="78"/>
-      <c r="AZ8" s="78"/>
-      <c r="BA8" s="78"/>
-      <c r="BB8" s="78"/>
-      <c r="BC8" s="78"/>
-      <c r="BD8" s="78"/>
-      <c r="BE8" s="81"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="67"/>
+      <c r="V8" s="67"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="67"/>
+      <c r="Y8" s="67"/>
+      <c r="Z8" s="67"/>
+      <c r="AA8" s="67"/>
+      <c r="AB8" s="67"/>
+      <c r="AC8" s="67"/>
+      <c r="AD8" s="67"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="67"/>
+      <c r="AG8" s="67"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="67"/>
+      <c r="AK8" s="67"/>
+      <c r="AL8" s="67"/>
+      <c r="AM8" s="67"/>
+      <c r="AN8" s="67"/>
+      <c r="AO8" s="67"/>
+      <c r="AP8" s="68"/>
+      <c r="AQ8" s="69"/>
+      <c r="AR8" s="67"/>
+      <c r="AS8" s="67"/>
+      <c r="AT8" s="67"/>
+      <c r="AU8" s="67"/>
+      <c r="AV8" s="67"/>
+      <c r="AW8" s="67"/>
+      <c r="AX8" s="67"/>
+      <c r="AY8" s="67"/>
+      <c r="AZ8" s="67"/>
+      <c r="BA8" s="67"/>
+      <c r="BB8" s="67"/>
+      <c r="BC8" s="67"/>
+      <c r="BD8" s="67"/>
+      <c r="BE8" s="70"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="72"/>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="76"/>
-      <c r="M9" s="76"/>
-      <c r="N9" s="77"/>
-      <c r="O9" s="75"/>
-      <c r="P9" s="78"/>
-      <c r="Q9" s="78"/>
-      <c r="R9" s="78"/>
-      <c r="S9" s="78"/>
-      <c r="T9" s="78"/>
-      <c r="U9" s="78"/>
-      <c r="V9" s="78"/>
-      <c r="W9" s="78"/>
-      <c r="X9" s="78"/>
-      <c r="Y9" s="78"/>
-      <c r="Z9" s="78"/>
-      <c r="AA9" s="78"/>
-      <c r="AB9" s="78"/>
-      <c r="AC9" s="78"/>
-      <c r="AD9" s="78"/>
-      <c r="AE9" s="78"/>
-      <c r="AF9" s="78"/>
-      <c r="AG9" s="78"/>
-      <c r="AH9" s="78"/>
-      <c r="AI9" s="78"/>
-      <c r="AJ9" s="78"/>
-      <c r="AK9" s="78"/>
-      <c r="AL9" s="78"/>
-      <c r="AM9" s="78"/>
-      <c r="AN9" s="78"/>
-      <c r="AO9" s="78"/>
-      <c r="AP9" s="79"/>
-      <c r="AQ9" s="80"/>
-      <c r="AR9" s="78"/>
-      <c r="AS9" s="78"/>
-      <c r="AT9" s="78"/>
-      <c r="AU9" s="78"/>
-      <c r="AV9" s="78"/>
-      <c r="AW9" s="78"/>
-      <c r="AX9" s="78"/>
-      <c r="AY9" s="78"/>
-      <c r="AZ9" s="78"/>
-      <c r="BA9" s="78"/>
-      <c r="BB9" s="78"/>
-      <c r="BC9" s="78"/>
-      <c r="BD9" s="78"/>
-      <c r="BE9" s="81"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="67"/>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="67"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="67"/>
+      <c r="U9" s="67"/>
+      <c r="V9" s="67"/>
+      <c r="W9" s="67"/>
+      <c r="X9" s="67"/>
+      <c r="Y9" s="67"/>
+      <c r="Z9" s="67"/>
+      <c r="AA9" s="67"/>
+      <c r="AB9" s="67"/>
+      <c r="AC9" s="67"/>
+      <c r="AD9" s="67"/>
+      <c r="AE9" s="67"/>
+      <c r="AF9" s="67"/>
+      <c r="AG9" s="67"/>
+      <c r="AH9" s="67"/>
+      <c r="AI9" s="67"/>
+      <c r="AJ9" s="67"/>
+      <c r="AK9" s="67"/>
+      <c r="AL9" s="67"/>
+      <c r="AM9" s="67"/>
+      <c r="AN9" s="67"/>
+      <c r="AO9" s="67"/>
+      <c r="AP9" s="68"/>
+      <c r="AQ9" s="69"/>
+      <c r="AR9" s="67"/>
+      <c r="AS9" s="67"/>
+      <c r="AT9" s="67"/>
+      <c r="AU9" s="67"/>
+      <c r="AV9" s="67"/>
+      <c r="AW9" s="67"/>
+      <c r="AX9" s="67"/>
+      <c r="AY9" s="67"/>
+      <c r="AZ9" s="67"/>
+      <c r="BA9" s="67"/>
+      <c r="BB9" s="67"/>
+      <c r="BC9" s="67"/>
+      <c r="BD9" s="67"/>
+      <c r="BE9" s="70"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="76"/>
-      <c r="K10" s="76"/>
-      <c r="L10" s="76"/>
-      <c r="M10" s="76"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="75"/>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="78"/>
-      <c r="T10" s="78"/>
-      <c r="U10" s="78"/>
-      <c r="V10" s="78"/>
-      <c r="W10" s="78"/>
-      <c r="X10" s="78"/>
-      <c r="Y10" s="78"/>
-      <c r="Z10" s="78"/>
-      <c r="AA10" s="78"/>
-      <c r="AB10" s="78"/>
-      <c r="AC10" s="78"/>
-      <c r="AD10" s="78"/>
-      <c r="AE10" s="78"/>
-      <c r="AF10" s="78"/>
-      <c r="AG10" s="78"/>
-      <c r="AH10" s="78"/>
-      <c r="AI10" s="78"/>
-      <c r="AJ10" s="78"/>
-      <c r="AK10" s="78"/>
-      <c r="AL10" s="78"/>
-      <c r="AM10" s="78"/>
-      <c r="AN10" s="78"/>
-      <c r="AO10" s="78"/>
-      <c r="AP10" s="79"/>
-      <c r="AQ10" s="80"/>
-      <c r="AR10" s="78"/>
-      <c r="AS10" s="78"/>
-      <c r="AT10" s="78"/>
-      <c r="AU10" s="78"/>
-      <c r="AV10" s="78"/>
-      <c r="AW10" s="78"/>
-      <c r="AX10" s="78"/>
-      <c r="AY10" s="78"/>
-      <c r="AZ10" s="78"/>
-      <c r="BA10" s="78"/>
-      <c r="BB10" s="78"/>
-      <c r="BC10" s="78"/>
-      <c r="BD10" s="78"/>
-      <c r="BE10" s="81"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="67"/>
+      <c r="Y10" s="67"/>
+      <c r="Z10" s="67"/>
+      <c r="AA10" s="67"/>
+      <c r="AB10" s="67"/>
+      <c r="AC10" s="67"/>
+      <c r="AD10" s="67"/>
+      <c r="AE10" s="67"/>
+      <c r="AF10" s="67"/>
+      <c r="AG10" s="67"/>
+      <c r="AH10" s="67"/>
+      <c r="AI10" s="67"/>
+      <c r="AJ10" s="67"/>
+      <c r="AK10" s="67"/>
+      <c r="AL10" s="67"/>
+      <c r="AM10" s="67"/>
+      <c r="AN10" s="67"/>
+      <c r="AO10" s="67"/>
+      <c r="AP10" s="68"/>
+      <c r="AQ10" s="69"/>
+      <c r="AR10" s="67"/>
+      <c r="AS10" s="67"/>
+      <c r="AT10" s="67"/>
+      <c r="AU10" s="67"/>
+      <c r="AV10" s="67"/>
+      <c r="AW10" s="67"/>
+      <c r="AX10" s="67"/>
+      <c r="AY10" s="67"/>
+      <c r="AZ10" s="67"/>
+      <c r="BA10" s="67"/>
+      <c r="BB10" s="67"/>
+      <c r="BC10" s="67"/>
+      <c r="BD10" s="67"/>
+      <c r="BE10" s="70"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="76"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="78"/>
-      <c r="Q11" s="78"/>
-      <c r="R11" s="78"/>
-      <c r="S11" s="78"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="78"/>
-      <c r="V11" s="78"/>
-      <c r="W11" s="78"/>
-      <c r="X11" s="78"/>
-      <c r="Y11" s="78"/>
-      <c r="Z11" s="78"/>
-      <c r="AA11" s="78"/>
-      <c r="AB11" s="78"/>
-      <c r="AC11" s="78"/>
-      <c r="AD11" s="78"/>
-      <c r="AE11" s="78"/>
-      <c r="AF11" s="78"/>
-      <c r="AG11" s="78"/>
-      <c r="AH11" s="78"/>
-      <c r="AI11" s="78"/>
-      <c r="AJ11" s="78"/>
-      <c r="AK11" s="78"/>
-      <c r="AL11" s="78"/>
-      <c r="AM11" s="78"/>
-      <c r="AN11" s="78"/>
-      <c r="AO11" s="78"/>
-      <c r="AP11" s="79"/>
-      <c r="AQ11" s="80"/>
-      <c r="AR11" s="78"/>
-      <c r="AS11" s="78"/>
-      <c r="AT11" s="78"/>
-      <c r="AU11" s="78"/>
-      <c r="AV11" s="78"/>
-      <c r="AW11" s="78"/>
-      <c r="AX11" s="78"/>
-      <c r="AY11" s="78"/>
-      <c r="AZ11" s="78"/>
-      <c r="BA11" s="78"/>
-      <c r="BB11" s="78"/>
-      <c r="BC11" s="78"/>
-      <c r="BD11" s="78"/>
-      <c r="BE11" s="81"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="67"/>
+      <c r="V11" s="67"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="67"/>
+      <c r="Z11" s="67"/>
+      <c r="AA11" s="67"/>
+      <c r="AB11" s="67"/>
+      <c r="AC11" s="67"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="67"/>
+      <c r="AF11" s="67"/>
+      <c r="AG11" s="67"/>
+      <c r="AH11" s="67"/>
+      <c r="AI11" s="67"/>
+      <c r="AJ11" s="67"/>
+      <c r="AK11" s="67"/>
+      <c r="AL11" s="67"/>
+      <c r="AM11" s="67"/>
+      <c r="AN11" s="67"/>
+      <c r="AO11" s="67"/>
+      <c r="AP11" s="68"/>
+      <c r="AQ11" s="69"/>
+      <c r="AR11" s="67"/>
+      <c r="AS11" s="67"/>
+      <c r="AT11" s="67"/>
+      <c r="AU11" s="67"/>
+      <c r="AV11" s="67"/>
+      <c r="AW11" s="67"/>
+      <c r="AX11" s="67"/>
+      <c r="AY11" s="67"/>
+      <c r="AZ11" s="67"/>
+      <c r="BA11" s="67"/>
+      <c r="BB11" s="67"/>
+      <c r="BC11" s="67"/>
+      <c r="BD11" s="67"/>
+      <c r="BE11" s="70"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="72"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="75"/>
-      <c r="P12" s="78"/>
-      <c r="Q12" s="78"/>
-      <c r="R12" s="78"/>
-      <c r="S12" s="78"/>
-      <c r="T12" s="78"/>
-      <c r="U12" s="78"/>
-      <c r="V12" s="78"/>
-      <c r="W12" s="78"/>
-      <c r="X12" s="78"/>
-      <c r="Y12" s="78"/>
-      <c r="Z12" s="78"/>
-      <c r="AA12" s="78"/>
-      <c r="AB12" s="78"/>
-      <c r="AC12" s="78"/>
-      <c r="AD12" s="78"/>
-      <c r="AE12" s="78"/>
-      <c r="AF12" s="78"/>
-      <c r="AG12" s="78"/>
-      <c r="AH12" s="78"/>
-      <c r="AI12" s="78"/>
-      <c r="AJ12" s="78"/>
-      <c r="AK12" s="78"/>
-      <c r="AL12" s="78"/>
-      <c r="AM12" s="78"/>
-      <c r="AN12" s="78"/>
-      <c r="AO12" s="78"/>
-      <c r="AP12" s="79"/>
-      <c r="AQ12" s="80"/>
-      <c r="AR12" s="78"/>
-      <c r="AS12" s="78"/>
-      <c r="AT12" s="78"/>
-      <c r="AU12" s="78"/>
-      <c r="AV12" s="78"/>
-      <c r="AW12" s="78"/>
-      <c r="AX12" s="78"/>
-      <c r="AY12" s="78"/>
-      <c r="AZ12" s="78"/>
-      <c r="BA12" s="78"/>
-      <c r="BB12" s="78"/>
-      <c r="BC12" s="78"/>
-      <c r="BD12" s="78"/>
-      <c r="BE12" s="81"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+      <c r="U12" s="67"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="67"/>
+      <c r="Y12" s="67"/>
+      <c r="Z12" s="67"/>
+      <c r="AA12" s="67"/>
+      <c r="AB12" s="67"/>
+      <c r="AC12" s="67"/>
+      <c r="AD12" s="67"/>
+      <c r="AE12" s="67"/>
+      <c r="AF12" s="67"/>
+      <c r="AG12" s="67"/>
+      <c r="AH12" s="67"/>
+      <c r="AI12" s="67"/>
+      <c r="AJ12" s="67"/>
+      <c r="AK12" s="67"/>
+      <c r="AL12" s="67"/>
+      <c r="AM12" s="67"/>
+      <c r="AN12" s="67"/>
+      <c r="AO12" s="67"/>
+      <c r="AP12" s="68"/>
+      <c r="AQ12" s="69"/>
+      <c r="AR12" s="67"/>
+      <c r="AS12" s="67"/>
+      <c r="AT12" s="67"/>
+      <c r="AU12" s="67"/>
+      <c r="AV12" s="67"/>
+      <c r="AW12" s="67"/>
+      <c r="AX12" s="67"/>
+      <c r="AY12" s="67"/>
+      <c r="AZ12" s="67"/>
+      <c r="BA12" s="67"/>
+      <c r="BB12" s="67"/>
+      <c r="BC12" s="67"/>
+      <c r="BD12" s="67"/>
+      <c r="BE12" s="70"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="72"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="77"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="78"/>
-      <c r="R13" s="78"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="78"/>
-      <c r="U13" s="78"/>
-      <c r="V13" s="78"/>
-      <c r="W13" s="78"/>
-      <c r="X13" s="78"/>
-      <c r="Y13" s="78"/>
-      <c r="Z13" s="78"/>
-      <c r="AA13" s="78"/>
-      <c r="AB13" s="78"/>
-      <c r="AC13" s="78"/>
-      <c r="AD13" s="78"/>
-      <c r="AE13" s="78"/>
-      <c r="AF13" s="78"/>
-      <c r="AG13" s="78"/>
-      <c r="AH13" s="78"/>
-      <c r="AI13" s="78"/>
-      <c r="AJ13" s="78"/>
-      <c r="AK13" s="78"/>
-      <c r="AL13" s="78"/>
-      <c r="AM13" s="78"/>
-      <c r="AN13" s="78"/>
-      <c r="AO13" s="78"/>
-      <c r="AP13" s="79"/>
-      <c r="AQ13" s="80"/>
-      <c r="AR13" s="78"/>
-      <c r="AS13" s="78"/>
-      <c r="AT13" s="78"/>
-      <c r="AU13" s="78"/>
-      <c r="AV13" s="78"/>
-      <c r="AW13" s="78"/>
-      <c r="AX13" s="78"/>
-      <c r="AY13" s="78"/>
-      <c r="AZ13" s="78"/>
-      <c r="BA13" s="78"/>
-      <c r="BB13" s="78"/>
-      <c r="BC13" s="78"/>
-      <c r="BD13" s="78"/>
-      <c r="BE13" s="81"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="66"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+      <c r="U13" s="67"/>
+      <c r="V13" s="67"/>
+      <c r="W13" s="67"/>
+      <c r="X13" s="67"/>
+      <c r="Y13" s="67"/>
+      <c r="Z13" s="67"/>
+      <c r="AA13" s="67"/>
+      <c r="AB13" s="67"/>
+      <c r="AC13" s="67"/>
+      <c r="AD13" s="67"/>
+      <c r="AE13" s="67"/>
+      <c r="AF13" s="67"/>
+      <c r="AG13" s="67"/>
+      <c r="AH13" s="67"/>
+      <c r="AI13" s="67"/>
+      <c r="AJ13" s="67"/>
+      <c r="AK13" s="67"/>
+      <c r="AL13" s="67"/>
+      <c r="AM13" s="67"/>
+      <c r="AN13" s="67"/>
+      <c r="AO13" s="67"/>
+      <c r="AP13" s="68"/>
+      <c r="AQ13" s="69"/>
+      <c r="AR13" s="67"/>
+      <c r="AS13" s="67"/>
+      <c r="AT13" s="67"/>
+      <c r="AU13" s="67"/>
+      <c r="AV13" s="67"/>
+      <c r="AW13" s="67"/>
+      <c r="AX13" s="67"/>
+      <c r="AY13" s="67"/>
+      <c r="AZ13" s="67"/>
+      <c r="BA13" s="67"/>
+      <c r="BB13" s="67"/>
+      <c r="BC13" s="67"/>
+      <c r="BD13" s="67"/>
+      <c r="BE13" s="70"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="78"/>
-      <c r="V14" s="78"/>
-      <c r="W14" s="78"/>
-      <c r="X14" s="78"/>
-      <c r="Y14" s="78"/>
-      <c r="Z14" s="78"/>
-      <c r="AA14" s="78"/>
-      <c r="AB14" s="78"/>
-      <c r="AC14" s="78"/>
-      <c r="AD14" s="78"/>
-      <c r="AE14" s="78"/>
-      <c r="AF14" s="78"/>
-      <c r="AG14" s="78"/>
-      <c r="AH14" s="78"/>
-      <c r="AI14" s="78"/>
-      <c r="AJ14" s="78"/>
-      <c r="AK14" s="78"/>
-      <c r="AL14" s="78"/>
-      <c r="AM14" s="78"/>
-      <c r="AN14" s="78"/>
-      <c r="AO14" s="78"/>
-      <c r="AP14" s="79"/>
-      <c r="AQ14" s="80"/>
-      <c r="AR14" s="78"/>
-      <c r="AS14" s="78"/>
-      <c r="AT14" s="78"/>
-      <c r="AU14" s="78"/>
-      <c r="AV14" s="78"/>
-      <c r="AW14" s="78"/>
-      <c r="AX14" s="78"/>
-      <c r="AY14" s="78"/>
-      <c r="AZ14" s="78"/>
-      <c r="BA14" s="78"/>
-      <c r="BB14" s="78"/>
-      <c r="BC14" s="78"/>
-      <c r="BD14" s="78"/>
-      <c r="BE14" s="81"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+      <c r="U14" s="67"/>
+      <c r="V14" s="67"/>
+      <c r="W14" s="67"/>
+      <c r="X14" s="67"/>
+      <c r="Y14" s="67"/>
+      <c r="Z14" s="67"/>
+      <c r="AA14" s="67"/>
+      <c r="AB14" s="67"/>
+      <c r="AC14" s="67"/>
+      <c r="AD14" s="67"/>
+      <c r="AE14" s="67"/>
+      <c r="AF14" s="67"/>
+      <c r="AG14" s="67"/>
+      <c r="AH14" s="67"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="67"/>
+      <c r="AK14" s="67"/>
+      <c r="AL14" s="67"/>
+      <c r="AM14" s="67"/>
+      <c r="AN14" s="67"/>
+      <c r="AO14" s="67"/>
+      <c r="AP14" s="68"/>
+      <c r="AQ14" s="69"/>
+      <c r="AR14" s="67"/>
+      <c r="AS14" s="67"/>
+      <c r="AT14" s="67"/>
+      <c r="AU14" s="67"/>
+      <c r="AV14" s="67"/>
+      <c r="AW14" s="67"/>
+      <c r="AX14" s="67"/>
+      <c r="AY14" s="67"/>
+      <c r="AZ14" s="67"/>
+      <c r="BA14" s="67"/>
+      <c r="BB14" s="67"/>
+      <c r="BC14" s="67"/>
+      <c r="BD14" s="67"/>
+      <c r="BE14" s="70"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="72"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="76"/>
-      <c r="M15" s="76"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="78"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="78"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="78"/>
-      <c r="AB15" s="78"/>
-      <c r="AC15" s="78"/>
-      <c r="AD15" s="78"/>
-      <c r="AE15" s="78"/>
-      <c r="AF15" s="78"/>
-      <c r="AG15" s="78"/>
-      <c r="AH15" s="78"/>
-      <c r="AI15" s="78"/>
-      <c r="AJ15" s="78"/>
-      <c r="AK15" s="78"/>
-      <c r="AL15" s="78"/>
-      <c r="AM15" s="78"/>
-      <c r="AN15" s="78"/>
-      <c r="AO15" s="78"/>
-      <c r="AP15" s="79"/>
-      <c r="AQ15" s="80"/>
-      <c r="AR15" s="78"/>
-      <c r="AS15" s="78"/>
-      <c r="AT15" s="78"/>
-      <c r="AU15" s="78"/>
-      <c r="AV15" s="78"/>
-      <c r="AW15" s="78"/>
-      <c r="AX15" s="78"/>
-      <c r="AY15" s="78"/>
-      <c r="AZ15" s="78"/>
-      <c r="BA15" s="78"/>
-      <c r="BB15" s="78"/>
-      <c r="BC15" s="78"/>
-      <c r="BD15" s="78"/>
-      <c r="BE15" s="81"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="67"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="67"/>
+      <c r="Z15" s="67"/>
+      <c r="AA15" s="67"/>
+      <c r="AB15" s="67"/>
+      <c r="AC15" s="67"/>
+      <c r="AD15" s="67"/>
+      <c r="AE15" s="67"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="67"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="67"/>
+      <c r="AL15" s="67"/>
+      <c r="AM15" s="67"/>
+      <c r="AN15" s="67"/>
+      <c r="AO15" s="67"/>
+      <c r="AP15" s="68"/>
+      <c r="AQ15" s="69"/>
+      <c r="AR15" s="67"/>
+      <c r="AS15" s="67"/>
+      <c r="AT15" s="67"/>
+      <c r="AU15" s="67"/>
+      <c r="AV15" s="67"/>
+      <c r="AW15" s="67"/>
+      <c r="AX15" s="67"/>
+      <c r="AY15" s="67"/>
+      <c r="AZ15" s="67"/>
+      <c r="BA15" s="67"/>
+      <c r="BB15" s="67"/>
+      <c r="BC15" s="67"/>
+      <c r="BD15" s="67"/>
+      <c r="BE15" s="70"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="72"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="76"/>
-      <c r="N16" s="77"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="78"/>
-      <c r="R16" s="78"/>
-      <c r="S16" s="78"/>
-      <c r="T16" s="78"/>
-      <c r="U16" s="78"/>
-      <c r="V16" s="78"/>
-      <c r="W16" s="78"/>
-      <c r="X16" s="78"/>
-      <c r="Y16" s="78"/>
-      <c r="Z16" s="78"/>
-      <c r="AA16" s="78"/>
-      <c r="AB16" s="78"/>
-      <c r="AC16" s="78"/>
-      <c r="AD16" s="78"/>
-      <c r="AE16" s="78"/>
-      <c r="AF16" s="78"/>
-      <c r="AG16" s="78"/>
-      <c r="AH16" s="78"/>
-      <c r="AI16" s="78"/>
-      <c r="AJ16" s="78"/>
-      <c r="AK16" s="78"/>
-      <c r="AL16" s="78"/>
-      <c r="AM16" s="78"/>
-      <c r="AN16" s="78"/>
-      <c r="AO16" s="78"/>
-      <c r="AP16" s="79"/>
-      <c r="AQ16" s="80"/>
-      <c r="AR16" s="78"/>
-      <c r="AS16" s="78"/>
-      <c r="AT16" s="78"/>
-      <c r="AU16" s="78"/>
-      <c r="AV16" s="78"/>
-      <c r="AW16" s="78"/>
-      <c r="AX16" s="78"/>
-      <c r="AY16" s="78"/>
-      <c r="AZ16" s="78"/>
-      <c r="BA16" s="78"/>
-      <c r="BB16" s="78"/>
-      <c r="BC16" s="78"/>
-      <c r="BD16" s="78"/>
-      <c r="BE16" s="81"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="67"/>
+      <c r="W16" s="67"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="67"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
+      <c r="AD16" s="67"/>
+      <c r="AE16" s="67"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="67"/>
+      <c r="AH16" s="67"/>
+      <c r="AI16" s="67"/>
+      <c r="AJ16" s="67"/>
+      <c r="AK16" s="67"/>
+      <c r="AL16" s="67"/>
+      <c r="AM16" s="67"/>
+      <c r="AN16" s="67"/>
+      <c r="AO16" s="67"/>
+      <c r="AP16" s="68"/>
+      <c r="AQ16" s="69"/>
+      <c r="AR16" s="67"/>
+      <c r="AS16" s="67"/>
+      <c r="AT16" s="67"/>
+      <c r="AU16" s="67"/>
+      <c r="AV16" s="67"/>
+      <c r="AW16" s="67"/>
+      <c r="AX16" s="67"/>
+      <c r="AY16" s="67"/>
+      <c r="AZ16" s="67"/>
+      <c r="BA16" s="67"/>
+      <c r="BB16" s="67"/>
+      <c r="BC16" s="67"/>
+      <c r="BD16" s="67"/>
+      <c r="BE16" s="70"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="72"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="76"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="76"/>
-      <c r="M17" s="76"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="75"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="78"/>
-      <c r="R17" s="78"/>
-      <c r="S17" s="78"/>
-      <c r="T17" s="78"/>
-      <c r="U17" s="78"/>
-      <c r="V17" s="78"/>
-      <c r="W17" s="78"/>
-      <c r="X17" s="78"/>
-      <c r="Y17" s="78"/>
-      <c r="Z17" s="78"/>
-      <c r="AA17" s="78"/>
-      <c r="AB17" s="78"/>
-      <c r="AC17" s="78"/>
-      <c r="AD17" s="78"/>
-      <c r="AE17" s="78"/>
-      <c r="AF17" s="78"/>
-      <c r="AG17" s="78"/>
-      <c r="AH17" s="78"/>
-      <c r="AI17" s="78"/>
-      <c r="AJ17" s="78"/>
-      <c r="AK17" s="78"/>
-      <c r="AL17" s="78"/>
-      <c r="AM17" s="78"/>
-      <c r="AN17" s="78"/>
-      <c r="AO17" s="78"/>
-      <c r="AP17" s="79"/>
-      <c r="AQ17" s="80"/>
-      <c r="AR17" s="78"/>
-      <c r="AS17" s="78"/>
-      <c r="AT17" s="78"/>
-      <c r="AU17" s="78"/>
-      <c r="AV17" s="78"/>
-      <c r="AW17" s="78"/>
-      <c r="AX17" s="78"/>
-      <c r="AY17" s="78"/>
-      <c r="AZ17" s="78"/>
-      <c r="BA17" s="78"/>
-      <c r="BB17" s="78"/>
-      <c r="BC17" s="78"/>
-      <c r="BD17" s="78"/>
-      <c r="BE17" s="81"/>
+      <c r="A17" s="61"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="67"/>
+      <c r="W17" s="67"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="67"/>
+      <c r="Z17" s="67"/>
+      <c r="AA17" s="67"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
+      <c r="AD17" s="67"/>
+      <c r="AE17" s="67"/>
+      <c r="AF17" s="67"/>
+      <c r="AG17" s="67"/>
+      <c r="AH17" s="67"/>
+      <c r="AI17" s="67"/>
+      <c r="AJ17" s="67"/>
+      <c r="AK17" s="67"/>
+      <c r="AL17" s="67"/>
+      <c r="AM17" s="67"/>
+      <c r="AN17" s="67"/>
+      <c r="AO17" s="67"/>
+      <c r="AP17" s="68"/>
+      <c r="AQ17" s="69"/>
+      <c r="AR17" s="67"/>
+      <c r="AS17" s="67"/>
+      <c r="AT17" s="67"/>
+      <c r="AU17" s="67"/>
+      <c r="AV17" s="67"/>
+      <c r="AW17" s="67"/>
+      <c r="AX17" s="67"/>
+      <c r="AY17" s="67"/>
+      <c r="AZ17" s="67"/>
+      <c r="BA17" s="67"/>
+      <c r="BB17" s="67"/>
+      <c r="BC17" s="67"/>
+      <c r="BD17" s="67"/>
+      <c r="BE17" s="70"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="72"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="77"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="78"/>
-      <c r="T18" s="78"/>
-      <c r="U18" s="78"/>
-      <c r="V18" s="78"/>
-      <c r="W18" s="78"/>
-      <c r="X18" s="78"/>
-      <c r="Y18" s="78"/>
-      <c r="Z18" s="78"/>
-      <c r="AA18" s="78"/>
-      <c r="AB18" s="78"/>
-      <c r="AC18" s="78"/>
-      <c r="AD18" s="78"/>
-      <c r="AE18" s="78"/>
-      <c r="AF18" s="78"/>
-      <c r="AG18" s="78"/>
-      <c r="AH18" s="78"/>
-      <c r="AI18" s="78"/>
-      <c r="AJ18" s="78"/>
-      <c r="AK18" s="78"/>
-      <c r="AL18" s="78"/>
-      <c r="AM18" s="78"/>
-      <c r="AN18" s="78"/>
-      <c r="AO18" s="78"/>
-      <c r="AP18" s="79"/>
-      <c r="AQ18" s="80"/>
-      <c r="AR18" s="78"/>
-      <c r="AS18" s="78"/>
-      <c r="AT18" s="78"/>
-      <c r="AU18" s="78"/>
-      <c r="AV18" s="78"/>
-      <c r="AW18" s="78"/>
-      <c r="AX18" s="78"/>
-      <c r="AY18" s="78"/>
-      <c r="AZ18" s="78"/>
-      <c r="BA18" s="78"/>
-      <c r="BB18" s="78"/>
-      <c r="BC18" s="78"/>
-      <c r="BD18" s="78"/>
-      <c r="BE18" s="81"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="67"/>
+      <c r="W18" s="67"/>
+      <c r="X18" s="67"/>
+      <c r="Y18" s="67"/>
+      <c r="Z18" s="67"/>
+      <c r="AA18" s="67"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
+      <c r="AD18" s="67"/>
+      <c r="AE18" s="67"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="67"/>
+      <c r="AH18" s="67"/>
+      <c r="AI18" s="67"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="67"/>
+      <c r="AL18" s="67"/>
+      <c r="AM18" s="67"/>
+      <c r="AN18" s="67"/>
+      <c r="AO18" s="67"/>
+      <c r="AP18" s="68"/>
+      <c r="AQ18" s="69"/>
+      <c r="AR18" s="67"/>
+      <c r="AS18" s="67"/>
+      <c r="AT18" s="67"/>
+      <c r="AU18" s="67"/>
+      <c r="AV18" s="67"/>
+      <c r="AW18" s="67"/>
+      <c r="AX18" s="67"/>
+      <c r="AY18" s="67"/>
+      <c r="AZ18" s="67"/>
+      <c r="BA18" s="67"/>
+      <c r="BB18" s="67"/>
+      <c r="BC18" s="67"/>
+      <c r="BD18" s="67"/>
+      <c r="BE18" s="70"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="72"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="78"/>
-      <c r="T19" s="78"/>
-      <c r="U19" s="78"/>
-      <c r="V19" s="78"/>
-      <c r="W19" s="78"/>
-      <c r="X19" s="78"/>
-      <c r="Y19" s="78"/>
-      <c r="Z19" s="78"/>
-      <c r="AA19" s="78"/>
-      <c r="AB19" s="78"/>
-      <c r="AC19" s="78"/>
-      <c r="AD19" s="78"/>
-      <c r="AE19" s="78"/>
-      <c r="AF19" s="78"/>
-      <c r="AG19" s="78"/>
-      <c r="AH19" s="78"/>
-      <c r="AI19" s="78"/>
-      <c r="AJ19" s="78"/>
-      <c r="AK19" s="78"/>
-      <c r="AL19" s="78"/>
-      <c r="AM19" s="78"/>
-      <c r="AN19" s="78"/>
-      <c r="AO19" s="78"/>
-      <c r="AP19" s="79"/>
-      <c r="AQ19" s="80"/>
-      <c r="AR19" s="78"/>
-      <c r="AS19" s="78"/>
-      <c r="AT19" s="78"/>
-      <c r="AU19" s="78"/>
-      <c r="AV19" s="78"/>
-      <c r="AW19" s="78"/>
-      <c r="AX19" s="78"/>
-      <c r="AY19" s="78"/>
-      <c r="AZ19" s="78"/>
-      <c r="BA19" s="78"/>
-      <c r="BB19" s="78"/>
-      <c r="BC19" s="78"/>
-      <c r="BD19" s="78"/>
-      <c r="BE19" s="81"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+      <c r="U19" s="67"/>
+      <c r="V19" s="67"/>
+      <c r="W19" s="67"/>
+      <c r="X19" s="67"/>
+      <c r="Y19" s="67"/>
+      <c r="Z19" s="67"/>
+      <c r="AA19" s="67"/>
+      <c r="AB19" s="67"/>
+      <c r="AC19" s="67"/>
+      <c r="AD19" s="67"/>
+      <c r="AE19" s="67"/>
+      <c r="AF19" s="67"/>
+      <c r="AG19" s="67"/>
+      <c r="AH19" s="67"/>
+      <c r="AI19" s="67"/>
+      <c r="AJ19" s="67"/>
+      <c r="AK19" s="67"/>
+      <c r="AL19" s="67"/>
+      <c r="AM19" s="67"/>
+      <c r="AN19" s="67"/>
+      <c r="AO19" s="67"/>
+      <c r="AP19" s="68"/>
+      <c r="AQ19" s="69"/>
+      <c r="AR19" s="67"/>
+      <c r="AS19" s="67"/>
+      <c r="AT19" s="67"/>
+      <c r="AU19" s="67"/>
+      <c r="AV19" s="67"/>
+      <c r="AW19" s="67"/>
+      <c r="AX19" s="67"/>
+      <c r="AY19" s="67"/>
+      <c r="AZ19" s="67"/>
+      <c r="BA19" s="67"/>
+      <c r="BB19" s="67"/>
+      <c r="BC19" s="67"/>
+      <c r="BD19" s="67"/>
+      <c r="BE19" s="70"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="72"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="76"/>
-      <c r="N20" s="77"/>
-      <c r="O20" s="75"/>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78"/>
-      <c r="R20" s="78"/>
-      <c r="S20" s="78"/>
-      <c r="T20" s="78"/>
-      <c r="U20" s="78"/>
-      <c r="V20" s="78"/>
-      <c r="W20" s="78"/>
-      <c r="X20" s="78"/>
-      <c r="Y20" s="78"/>
-      <c r="Z20" s="78"/>
-      <c r="AA20" s="78"/>
-      <c r="AB20" s="78"/>
-      <c r="AC20" s="78"/>
-      <c r="AD20" s="78"/>
-      <c r="AE20" s="78"/>
-      <c r="AF20" s="78"/>
-      <c r="AG20" s="78"/>
-      <c r="AH20" s="78"/>
-      <c r="AI20" s="78"/>
-      <c r="AJ20" s="78"/>
-      <c r="AK20" s="78"/>
-      <c r="AL20" s="78"/>
-      <c r="AM20" s="78"/>
-      <c r="AN20" s="78"/>
-      <c r="AO20" s="78"/>
-      <c r="AP20" s="79"/>
-      <c r="AQ20" s="80"/>
-      <c r="AR20" s="78"/>
-      <c r="AS20" s="78"/>
-      <c r="AT20" s="78"/>
-      <c r="AU20" s="78"/>
-      <c r="AV20" s="78"/>
-      <c r="AW20" s="78"/>
-      <c r="AX20" s="78"/>
-      <c r="AY20" s="78"/>
-      <c r="AZ20" s="78"/>
-      <c r="BA20" s="78"/>
-      <c r="BB20" s="78"/>
-      <c r="BC20" s="78"/>
-      <c r="BD20" s="78"/>
-      <c r="BE20" s="81"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="67"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="67"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67"/>
+      <c r="Z20" s="67"/>
+      <c r="AA20" s="67"/>
+      <c r="AB20" s="67"/>
+      <c r="AC20" s="67"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="67"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="67"/>
+      <c r="AH20" s="67"/>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="67"/>
+      <c r="AK20" s="67"/>
+      <c r="AL20" s="67"/>
+      <c r="AM20" s="67"/>
+      <c r="AN20" s="67"/>
+      <c r="AO20" s="67"/>
+      <c r="AP20" s="68"/>
+      <c r="AQ20" s="69"/>
+      <c r="AR20" s="67"/>
+      <c r="AS20" s="67"/>
+      <c r="AT20" s="67"/>
+      <c r="AU20" s="67"/>
+      <c r="AV20" s="67"/>
+      <c r="AW20" s="67"/>
+      <c r="AX20" s="67"/>
+      <c r="AY20" s="67"/>
+      <c r="AZ20" s="67"/>
+      <c r="BA20" s="67"/>
+      <c r="BB20" s="67"/>
+      <c r="BC20" s="67"/>
+      <c r="BD20" s="67"/>
+      <c r="BE20" s="70"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="72"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="76"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="75"/>
-      <c r="P21" s="78"/>
-      <c r="Q21" s="78"/>
-      <c r="R21" s="78"/>
-      <c r="S21" s="78"/>
-      <c r="T21" s="78"/>
-      <c r="U21" s="78"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="78"/>
-      <c r="X21" s="78"/>
-      <c r="Y21" s="78"/>
-      <c r="Z21" s="78"/>
-      <c r="AA21" s="78"/>
-      <c r="AB21" s="78"/>
-      <c r="AC21" s="78"/>
-      <c r="AD21" s="78"/>
-      <c r="AE21" s="78"/>
-      <c r="AF21" s="78"/>
-      <c r="AG21" s="78"/>
-      <c r="AH21" s="78"/>
-      <c r="AI21" s="78"/>
-      <c r="AJ21" s="78"/>
-      <c r="AK21" s="78"/>
-      <c r="AL21" s="78"/>
-      <c r="AM21" s="78"/>
-      <c r="AN21" s="78"/>
-      <c r="AO21" s="78"/>
-      <c r="AP21" s="79"/>
-      <c r="AQ21" s="80"/>
-      <c r="AR21" s="78"/>
-      <c r="AS21" s="78"/>
-      <c r="AT21" s="78"/>
-      <c r="AU21" s="78"/>
-      <c r="AV21" s="78"/>
-      <c r="AW21" s="78"/>
-      <c r="AX21" s="78"/>
-      <c r="AY21" s="78"/>
-      <c r="AZ21" s="78"/>
-      <c r="BA21" s="78"/>
-      <c r="BB21" s="78"/>
-      <c r="BC21" s="78"/>
-      <c r="BD21" s="78"/>
-      <c r="BE21" s="81"/>
+      <c r="A21" s="61"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="67"/>
+      <c r="AA21" s="67"/>
+      <c r="AB21" s="67"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="67"/>
+      <c r="AE21" s="67"/>
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="67"/>
+      <c r="AH21" s="67"/>
+      <c r="AI21" s="67"/>
+      <c r="AJ21" s="67"/>
+      <c r="AK21" s="67"/>
+      <c r="AL21" s="67"/>
+      <c r="AM21" s="67"/>
+      <c r="AN21" s="67"/>
+      <c r="AO21" s="67"/>
+      <c r="AP21" s="68"/>
+      <c r="AQ21" s="69"/>
+      <c r="AR21" s="67"/>
+      <c r="AS21" s="67"/>
+      <c r="AT21" s="67"/>
+      <c r="AU21" s="67"/>
+      <c r="AV21" s="67"/>
+      <c r="AW21" s="67"/>
+      <c r="AX21" s="67"/>
+      <c r="AY21" s="67"/>
+      <c r="AZ21" s="67"/>
+      <c r="BA21" s="67"/>
+      <c r="BB21" s="67"/>
+      <c r="BC21" s="67"/>
+      <c r="BD21" s="67"/>
+      <c r="BE21" s="70"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="72"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="75"/>
-      <c r="P22" s="78"/>
-      <c r="Q22" s="78"/>
-      <c r="R22" s="78"/>
-      <c r="S22" s="78"/>
-      <c r="T22" s="78"/>
-      <c r="U22" s="78"/>
-      <c r="V22" s="78"/>
-      <c r="W22" s="78"/>
-      <c r="X22" s="78"/>
-      <c r="Y22" s="78"/>
-      <c r="Z22" s="78"/>
-      <c r="AA22" s="78"/>
-      <c r="AB22" s="78"/>
-      <c r="AC22" s="78"/>
-      <c r="AD22" s="78"/>
-      <c r="AE22" s="78"/>
-      <c r="AF22" s="78"/>
-      <c r="AG22" s="78"/>
-      <c r="AH22" s="78"/>
-      <c r="AI22" s="78"/>
-      <c r="AJ22" s="78"/>
-      <c r="AK22" s="78"/>
-      <c r="AL22" s="78"/>
-      <c r="AM22" s="78"/>
-      <c r="AN22" s="78"/>
-      <c r="AO22" s="78"/>
-      <c r="AP22" s="79"/>
-      <c r="AQ22" s="80"/>
-      <c r="AR22" s="78"/>
-      <c r="AS22" s="78"/>
-      <c r="AT22" s="78"/>
-      <c r="AU22" s="78"/>
-      <c r="AV22" s="78"/>
-      <c r="AW22" s="78"/>
-      <c r="AX22" s="78"/>
-      <c r="AY22" s="78"/>
-      <c r="AZ22" s="78"/>
-      <c r="BA22" s="78"/>
-      <c r="BB22" s="78"/>
-      <c r="BC22" s="78"/>
-      <c r="BD22" s="78"/>
-      <c r="BE22" s="81"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="67"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="67"/>
+      <c r="AA22" s="67"/>
+      <c r="AB22" s="67"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
+      <c r="AK22" s="67"/>
+      <c r="AL22" s="67"/>
+      <c r="AM22" s="67"/>
+      <c r="AN22" s="67"/>
+      <c r="AO22" s="67"/>
+      <c r="AP22" s="68"/>
+      <c r="AQ22" s="69"/>
+      <c r="AR22" s="67"/>
+      <c r="AS22" s="67"/>
+      <c r="AT22" s="67"/>
+      <c r="AU22" s="67"/>
+      <c r="AV22" s="67"/>
+      <c r="AW22" s="67"/>
+      <c r="AX22" s="67"/>
+      <c r="AY22" s="67"/>
+      <c r="AZ22" s="67"/>
+      <c r="BA22" s="67"/>
+      <c r="BB22" s="67"/>
+      <c r="BC22" s="67"/>
+      <c r="BD22" s="67"/>
+      <c r="BE22" s="70"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="72"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="77"/>
-      <c r="O23" s="75"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="78"/>
-      <c r="U23" s="78"/>
-      <c r="V23" s="78"/>
-      <c r="W23" s="78"/>
-      <c r="X23" s="78"/>
-      <c r="Y23" s="78"/>
-      <c r="Z23" s="78"/>
-      <c r="AA23" s="78"/>
-      <c r="AB23" s="78"/>
-      <c r="AC23" s="78"/>
-      <c r="AD23" s="78"/>
-      <c r="AE23" s="78"/>
-      <c r="AF23" s="78"/>
-      <c r="AG23" s="78"/>
-      <c r="AH23" s="78"/>
-      <c r="AI23" s="78"/>
-      <c r="AJ23" s="78"/>
-      <c r="AK23" s="78"/>
-      <c r="AL23" s="78"/>
-      <c r="AM23" s="78"/>
-      <c r="AN23" s="78"/>
-      <c r="AO23" s="78"/>
-      <c r="AP23" s="79"/>
-      <c r="AQ23" s="80"/>
-      <c r="AR23" s="78"/>
-      <c r="AS23" s="78"/>
-      <c r="AT23" s="78"/>
-      <c r="AU23" s="78"/>
-      <c r="AV23" s="78"/>
-      <c r="AW23" s="78"/>
-      <c r="AX23" s="78"/>
-      <c r="AY23" s="78"/>
-      <c r="AZ23" s="78"/>
-      <c r="BA23" s="78"/>
-      <c r="BB23" s="78"/>
-      <c r="BC23" s="78"/>
-      <c r="BD23" s="78"/>
-      <c r="BE23" s="81"/>
+      <c r="A23" s="61"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="67"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="67"/>
+      <c r="AA23" s="67"/>
+      <c r="AB23" s="67"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="67"/>
+      <c r="AE23" s="67"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="67"/>
+      <c r="AH23" s="67"/>
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
+      <c r="AL23" s="67"/>
+      <c r="AM23" s="67"/>
+      <c r="AN23" s="67"/>
+      <c r="AO23" s="67"/>
+      <c r="AP23" s="68"/>
+      <c r="AQ23" s="69"/>
+      <c r="AR23" s="67"/>
+      <c r="AS23" s="67"/>
+      <c r="AT23" s="67"/>
+      <c r="AU23" s="67"/>
+      <c r="AV23" s="67"/>
+      <c r="AW23" s="67"/>
+      <c r="AX23" s="67"/>
+      <c r="AY23" s="67"/>
+      <c r="AZ23" s="67"/>
+      <c r="BA23" s="67"/>
+      <c r="BB23" s="67"/>
+      <c r="BC23" s="67"/>
+      <c r="BD23" s="67"/>
+      <c r="BE23" s="70"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="72"/>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="77"/>
-      <c r="O24" s="75"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="78"/>
-      <c r="R24" s="78"/>
-      <c r="S24" s="78"/>
-      <c r="T24" s="78"/>
-      <c r="U24" s="78"/>
-      <c r="V24" s="78"/>
-      <c r="W24" s="78"/>
-      <c r="X24" s="78"/>
-      <c r="Y24" s="78"/>
-      <c r="Z24" s="78"/>
-      <c r="AA24" s="78"/>
-      <c r="AB24" s="78"/>
-      <c r="AC24" s="78"/>
-      <c r="AD24" s="78"/>
-      <c r="AE24" s="78"/>
-      <c r="AF24" s="78"/>
-      <c r="AG24" s="78"/>
-      <c r="AH24" s="78"/>
-      <c r="AI24" s="78"/>
-      <c r="AJ24" s="78"/>
-      <c r="AK24" s="78"/>
-      <c r="AL24" s="78"/>
-      <c r="AM24" s="78"/>
-      <c r="AN24" s="78"/>
-      <c r="AO24" s="78"/>
-      <c r="AP24" s="79"/>
-      <c r="AQ24" s="80"/>
-      <c r="AR24" s="78"/>
-      <c r="AS24" s="78"/>
-      <c r="AT24" s="78"/>
-      <c r="AU24" s="78"/>
-      <c r="AV24" s="78"/>
-      <c r="AW24" s="78"/>
-      <c r="AX24" s="78"/>
-      <c r="AY24" s="78"/>
-      <c r="AZ24" s="78"/>
-      <c r="BA24" s="78"/>
-      <c r="BB24" s="78"/>
-      <c r="BC24" s="78"/>
-      <c r="BD24" s="78"/>
-      <c r="BE24" s="81"/>
+      <c r="A24" s="61"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="64"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="67"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="67"/>
+      <c r="AE24" s="67"/>
+      <c r="AF24" s="67"/>
+      <c r="AG24" s="67"/>
+      <c r="AH24" s="67"/>
+      <c r="AI24" s="67"/>
+      <c r="AJ24" s="67"/>
+      <c r="AK24" s="67"/>
+      <c r="AL24" s="67"/>
+      <c r="AM24" s="67"/>
+      <c r="AN24" s="67"/>
+      <c r="AO24" s="67"/>
+      <c r="AP24" s="68"/>
+      <c r="AQ24" s="69"/>
+      <c r="AR24" s="67"/>
+      <c r="AS24" s="67"/>
+      <c r="AT24" s="67"/>
+      <c r="AU24" s="67"/>
+      <c r="AV24" s="67"/>
+      <c r="AW24" s="67"/>
+      <c r="AX24" s="67"/>
+      <c r="AY24" s="67"/>
+      <c r="AZ24" s="67"/>
+      <c r="BA24" s="67"/>
+      <c r="BB24" s="67"/>
+      <c r="BC24" s="67"/>
+      <c r="BD24" s="67"/>
+      <c r="BE24" s="70"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="72"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="77"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="78"/>
-      <c r="R25" s="78"/>
-      <c r="S25" s="78"/>
-      <c r="T25" s="78"/>
-      <c r="U25" s="78"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="78"/>
-      <c r="X25" s="78"/>
-      <c r="Y25" s="78"/>
-      <c r="Z25" s="78"/>
-      <c r="AA25" s="78"/>
-      <c r="AB25" s="78"/>
-      <c r="AC25" s="78"/>
-      <c r="AD25" s="78"/>
-      <c r="AE25" s="78"/>
-      <c r="AF25" s="78"/>
-      <c r="AG25" s="78"/>
-      <c r="AH25" s="78"/>
-      <c r="AI25" s="78"/>
-      <c r="AJ25" s="78"/>
-      <c r="AK25" s="78"/>
-      <c r="AL25" s="78"/>
-      <c r="AM25" s="78"/>
-      <c r="AN25" s="78"/>
-      <c r="AO25" s="78"/>
-      <c r="AP25" s="79"/>
-      <c r="AQ25" s="80"/>
-      <c r="AR25" s="78"/>
-      <c r="AS25" s="78"/>
-      <c r="AT25" s="78"/>
-      <c r="AU25" s="78"/>
-      <c r="AV25" s="78"/>
-      <c r="AW25" s="78"/>
-      <c r="AX25" s="78"/>
-      <c r="AY25" s="78"/>
-      <c r="AZ25" s="78"/>
-      <c r="BA25" s="78"/>
-      <c r="BB25" s="78"/>
-      <c r="BC25" s="78"/>
-      <c r="BD25" s="78"/>
-      <c r="BE25" s="81"/>
+      <c r="A25" s="61"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="66"/>
+      <c r="O25" s="64"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="67"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67"/>
+      <c r="Z25" s="67"/>
+      <c r="AA25" s="67"/>
+      <c r="AB25" s="67"/>
+      <c r="AC25" s="67"/>
+      <c r="AD25" s="67"/>
+      <c r="AE25" s="67"/>
+      <c r="AF25" s="67"/>
+      <c r="AG25" s="67"/>
+      <c r="AH25" s="67"/>
+      <c r="AI25" s="67"/>
+      <c r="AJ25" s="67"/>
+      <c r="AK25" s="67"/>
+      <c r="AL25" s="67"/>
+      <c r="AM25" s="67"/>
+      <c r="AN25" s="67"/>
+      <c r="AO25" s="67"/>
+      <c r="AP25" s="68"/>
+      <c r="AQ25" s="69"/>
+      <c r="AR25" s="67"/>
+      <c r="AS25" s="67"/>
+      <c r="AT25" s="67"/>
+      <c r="AU25" s="67"/>
+      <c r="AV25" s="67"/>
+      <c r="AW25" s="67"/>
+      <c r="AX25" s="67"/>
+      <c r="AY25" s="67"/>
+      <c r="AZ25" s="67"/>
+      <c r="BA25" s="67"/>
+      <c r="BB25" s="67"/>
+      <c r="BC25" s="67"/>
+      <c r="BD25" s="67"/>
+      <c r="BE25" s="70"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="72"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="76"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="76"/>
-      <c r="M26" s="76"/>
-      <c r="N26" s="77"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="78"/>
-      <c r="Q26" s="78"/>
-      <c r="R26" s="78"/>
-      <c r="S26" s="78"/>
-      <c r="T26" s="78"/>
-      <c r="U26" s="78"/>
-      <c r="V26" s="78"/>
-      <c r="W26" s="78"/>
-      <c r="X26" s="78"/>
-      <c r="Y26" s="78"/>
-      <c r="Z26" s="78"/>
-      <c r="AA26" s="78"/>
-      <c r="AB26" s="78"/>
-      <c r="AC26" s="78"/>
-      <c r="AD26" s="78"/>
-      <c r="AE26" s="78"/>
-      <c r="AF26" s="78"/>
-      <c r="AG26" s="78"/>
-      <c r="AH26" s="78"/>
-      <c r="AI26" s="78"/>
-      <c r="AJ26" s="78"/>
-      <c r="AK26" s="78"/>
-      <c r="AL26" s="78"/>
-      <c r="AM26" s="78"/>
-      <c r="AN26" s="78"/>
-      <c r="AO26" s="78"/>
-      <c r="AP26" s="79"/>
-      <c r="AQ26" s="80"/>
-      <c r="AR26" s="78"/>
-      <c r="AS26" s="78"/>
-      <c r="AT26" s="78"/>
-      <c r="AU26" s="78"/>
-      <c r="AV26" s="78"/>
-      <c r="AW26" s="78"/>
-      <c r="AX26" s="78"/>
-      <c r="AY26" s="78"/>
-      <c r="AZ26" s="78"/>
-      <c r="BA26" s="78"/>
-      <c r="BB26" s="78"/>
-      <c r="BC26" s="78"/>
-      <c r="BD26" s="78"/>
-      <c r="BE26" s="81"/>
+      <c r="A26" s="61"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="64"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="67"/>
+      <c r="X26" s="67"/>
+      <c r="Y26" s="67"/>
+      <c r="Z26" s="67"/>
+      <c r="AA26" s="67"/>
+      <c r="AB26" s="67"/>
+      <c r="AC26" s="67"/>
+      <c r="AD26" s="67"/>
+      <c r="AE26" s="67"/>
+      <c r="AF26" s="67"/>
+      <c r="AG26" s="67"/>
+      <c r="AH26" s="67"/>
+      <c r="AI26" s="67"/>
+      <c r="AJ26" s="67"/>
+      <c r="AK26" s="67"/>
+      <c r="AL26" s="67"/>
+      <c r="AM26" s="67"/>
+      <c r="AN26" s="67"/>
+      <c r="AO26" s="67"/>
+      <c r="AP26" s="68"/>
+      <c r="AQ26" s="69"/>
+      <c r="AR26" s="67"/>
+      <c r="AS26" s="67"/>
+      <c r="AT26" s="67"/>
+      <c r="AU26" s="67"/>
+      <c r="AV26" s="67"/>
+      <c r="AW26" s="67"/>
+      <c r="AX26" s="67"/>
+      <c r="AY26" s="67"/>
+      <c r="AZ26" s="67"/>
+      <c r="BA26" s="67"/>
+      <c r="BB26" s="67"/>
+      <c r="BC26" s="67"/>
+      <c r="BD26" s="67"/>
+      <c r="BE26" s="70"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="72"/>
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
-      <c r="N27" s="77"/>
-      <c r="O27" s="75"/>
-      <c r="P27" s="78"/>
-      <c r="Q27" s="78"/>
-      <c r="R27" s="78"/>
-      <c r="S27" s="78"/>
-      <c r="T27" s="78"/>
-      <c r="U27" s="78"/>
-      <c r="V27" s="78"/>
-      <c r="W27" s="78"/>
-      <c r="X27" s="78"/>
-      <c r="Y27" s="78"/>
-      <c r="Z27" s="78"/>
-      <c r="AA27" s="78"/>
-      <c r="AB27" s="78"/>
-      <c r="AC27" s="78"/>
-      <c r="AD27" s="78"/>
-      <c r="AE27" s="78"/>
-      <c r="AF27" s="78"/>
-      <c r="AG27" s="78"/>
-      <c r="AH27" s="78"/>
-      <c r="AI27" s="78"/>
-      <c r="AJ27" s="78"/>
-      <c r="AK27" s="78"/>
-      <c r="AL27" s="78"/>
-      <c r="AM27" s="78"/>
-      <c r="AN27" s="78"/>
-      <c r="AO27" s="78"/>
-      <c r="AP27" s="79"/>
-      <c r="AQ27" s="80"/>
-      <c r="AR27" s="78"/>
-      <c r="AS27" s="78"/>
-      <c r="AT27" s="78"/>
-      <c r="AU27" s="78"/>
-      <c r="AV27" s="78"/>
-      <c r="AW27" s="78"/>
-      <c r="AX27" s="78"/>
-      <c r="AY27" s="78"/>
-      <c r="AZ27" s="78"/>
-      <c r="BA27" s="78"/>
-      <c r="BB27" s="78"/>
-      <c r="BC27" s="78"/>
-      <c r="BD27" s="78"/>
-      <c r="BE27" s="81"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+      <c r="U27" s="67"/>
+      <c r="V27" s="67"/>
+      <c r="W27" s="67"/>
+      <c r="X27" s="67"/>
+      <c r="Y27" s="67"/>
+      <c r="Z27" s="67"/>
+      <c r="AA27" s="67"/>
+      <c r="AB27" s="67"/>
+      <c r="AC27" s="67"/>
+      <c r="AD27" s="67"/>
+      <c r="AE27" s="67"/>
+      <c r="AF27" s="67"/>
+      <c r="AG27" s="67"/>
+      <c r="AH27" s="67"/>
+      <c r="AI27" s="67"/>
+      <c r="AJ27" s="67"/>
+      <c r="AK27" s="67"/>
+      <c r="AL27" s="67"/>
+      <c r="AM27" s="67"/>
+      <c r="AN27" s="67"/>
+      <c r="AO27" s="67"/>
+      <c r="AP27" s="68"/>
+      <c r="AQ27" s="69"/>
+      <c r="AR27" s="67"/>
+      <c r="AS27" s="67"/>
+      <c r="AT27" s="67"/>
+      <c r="AU27" s="67"/>
+      <c r="AV27" s="67"/>
+      <c r="AW27" s="67"/>
+      <c r="AX27" s="67"/>
+      <c r="AY27" s="67"/>
+      <c r="AZ27" s="67"/>
+      <c r="BA27" s="67"/>
+      <c r="BB27" s="67"/>
+      <c r="BC27" s="67"/>
+      <c r="BD27" s="67"/>
+      <c r="BE27" s="70"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="72"/>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="76"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="77"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="78"/>
-      <c r="S28" s="78"/>
-      <c r="T28" s="78"/>
-      <c r="U28" s="78"/>
-      <c r="V28" s="78"/>
-      <c r="W28" s="78"/>
-      <c r="X28" s="78"/>
-      <c r="Y28" s="78"/>
-      <c r="Z28" s="78"/>
-      <c r="AA28" s="78"/>
-      <c r="AB28" s="78"/>
-      <c r="AC28" s="78"/>
-      <c r="AD28" s="78"/>
-      <c r="AE28" s="78"/>
-      <c r="AF28" s="78"/>
-      <c r="AG28" s="78"/>
-      <c r="AH28" s="78"/>
-      <c r="AI28" s="78"/>
-      <c r="AJ28" s="78"/>
-      <c r="AK28" s="78"/>
-      <c r="AL28" s="78"/>
-      <c r="AM28" s="78"/>
-      <c r="AN28" s="78"/>
-      <c r="AO28" s="78"/>
-      <c r="AP28" s="79"/>
-      <c r="AQ28" s="80"/>
-      <c r="AR28" s="78"/>
-      <c r="AS28" s="78"/>
-      <c r="AT28" s="78"/>
-      <c r="AU28" s="78"/>
-      <c r="AV28" s="78"/>
-      <c r="AW28" s="78"/>
-      <c r="AX28" s="78"/>
-      <c r="AY28" s="78"/>
-      <c r="AZ28" s="78"/>
-      <c r="BA28" s="78"/>
-      <c r="BB28" s="78"/>
-      <c r="BC28" s="78"/>
-      <c r="BD28" s="78"/>
-      <c r="BE28" s="81"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+      <c r="U28" s="67"/>
+      <c r="V28" s="67"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="67"/>
+      <c r="Y28" s="67"/>
+      <c r="Z28" s="67"/>
+      <c r="AA28" s="67"/>
+      <c r="AB28" s="67"/>
+      <c r="AC28" s="67"/>
+      <c r="AD28" s="67"/>
+      <c r="AE28" s="67"/>
+      <c r="AF28" s="67"/>
+      <c r="AG28" s="67"/>
+      <c r="AH28" s="67"/>
+      <c r="AI28" s="67"/>
+      <c r="AJ28" s="67"/>
+      <c r="AK28" s="67"/>
+      <c r="AL28" s="67"/>
+      <c r="AM28" s="67"/>
+      <c r="AN28" s="67"/>
+      <c r="AO28" s="67"/>
+      <c r="AP28" s="68"/>
+      <c r="AQ28" s="69"/>
+      <c r="AR28" s="67"/>
+      <c r="AS28" s="67"/>
+      <c r="AT28" s="67"/>
+      <c r="AU28" s="67"/>
+      <c r="AV28" s="67"/>
+      <c r="AW28" s="67"/>
+      <c r="AX28" s="67"/>
+      <c r="AY28" s="67"/>
+      <c r="AZ28" s="67"/>
+      <c r="BA28" s="67"/>
+      <c r="BB28" s="67"/>
+      <c r="BC28" s="67"/>
+      <c r="BD28" s="67"/>
+      <c r="BE28" s="70"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="72"/>
-      <c r="B29" s="73"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="76"/>
-      <c r="J29" s="76"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="76"/>
-      <c r="M29" s="76"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="75"/>
-      <c r="P29" s="78"/>
-      <c r="Q29" s="78"/>
-      <c r="R29" s="78"/>
-      <c r="S29" s="78"/>
-      <c r="T29" s="78"/>
-      <c r="U29" s="78"/>
-      <c r="V29" s="78"/>
-      <c r="W29" s="78"/>
-      <c r="X29" s="78"/>
-      <c r="Y29" s="78"/>
-      <c r="Z29" s="78"/>
-      <c r="AA29" s="78"/>
-      <c r="AB29" s="78"/>
-      <c r="AC29" s="78"/>
-      <c r="AD29" s="78"/>
-      <c r="AE29" s="78"/>
-      <c r="AF29" s="78"/>
-      <c r="AG29" s="78"/>
-      <c r="AH29" s="78"/>
-      <c r="AI29" s="78"/>
-      <c r="AJ29" s="78"/>
-      <c r="AK29" s="78"/>
-      <c r="AL29" s="78"/>
-      <c r="AM29" s="78"/>
-      <c r="AN29" s="78"/>
-      <c r="AO29" s="78"/>
-      <c r="AP29" s="79"/>
-      <c r="AQ29" s="80"/>
-      <c r="AR29" s="78"/>
-      <c r="AS29" s="78"/>
-      <c r="AT29" s="78"/>
-      <c r="AU29" s="78"/>
-      <c r="AV29" s="78"/>
-      <c r="AW29" s="78"/>
-      <c r="AX29" s="78"/>
-      <c r="AY29" s="78"/>
-      <c r="AZ29" s="78"/>
-      <c r="BA29" s="78"/>
-      <c r="BB29" s="78"/>
-      <c r="BC29" s="78"/>
-      <c r="BD29" s="78"/>
-      <c r="BE29" s="81"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="67"/>
+      <c r="V29" s="67"/>
+      <c r="W29" s="67"/>
+      <c r="X29" s="67"/>
+      <c r="Y29" s="67"/>
+      <c r="Z29" s="67"/>
+      <c r="AA29" s="67"/>
+      <c r="AB29" s="67"/>
+      <c r="AC29" s="67"/>
+      <c r="AD29" s="67"/>
+      <c r="AE29" s="67"/>
+      <c r="AF29" s="67"/>
+      <c r="AG29" s="67"/>
+      <c r="AH29" s="67"/>
+      <c r="AI29" s="67"/>
+      <c r="AJ29" s="67"/>
+      <c r="AK29" s="67"/>
+      <c r="AL29" s="67"/>
+      <c r="AM29" s="67"/>
+      <c r="AN29" s="67"/>
+      <c r="AO29" s="67"/>
+      <c r="AP29" s="68"/>
+      <c r="AQ29" s="69"/>
+      <c r="AR29" s="67"/>
+      <c r="AS29" s="67"/>
+      <c r="AT29" s="67"/>
+      <c r="AU29" s="67"/>
+      <c r="AV29" s="67"/>
+      <c r="AW29" s="67"/>
+      <c r="AX29" s="67"/>
+      <c r="AY29" s="67"/>
+      <c r="AZ29" s="67"/>
+      <c r="BA29" s="67"/>
+      <c r="BB29" s="67"/>
+      <c r="BC29" s="67"/>
+      <c r="BD29" s="67"/>
+      <c r="BE29" s="70"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="72"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="76"/>
-      <c r="M30" s="76"/>
-      <c r="N30" s="77"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="78"/>
-      <c r="Q30" s="78"/>
-      <c r="R30" s="78"/>
-      <c r="S30" s="78"/>
-      <c r="T30" s="78"/>
-      <c r="U30" s="78"/>
-      <c r="V30" s="78"/>
-      <c r="W30" s="78"/>
-      <c r="X30" s="78"/>
-      <c r="Y30" s="78"/>
-      <c r="Z30" s="78"/>
-      <c r="AA30" s="78"/>
-      <c r="AB30" s="78"/>
-      <c r="AC30" s="78"/>
-      <c r="AD30" s="78"/>
-      <c r="AE30" s="78"/>
-      <c r="AF30" s="78"/>
-      <c r="AG30" s="78"/>
-      <c r="AH30" s="78"/>
-      <c r="AI30" s="78"/>
-      <c r="AJ30" s="78"/>
-      <c r="AK30" s="78"/>
-      <c r="AL30" s="78"/>
-      <c r="AM30" s="78"/>
-      <c r="AN30" s="78"/>
-      <c r="AO30" s="78"/>
-      <c r="AP30" s="79"/>
-      <c r="AQ30" s="80"/>
-      <c r="AR30" s="78"/>
-      <c r="AS30" s="78"/>
-      <c r="AT30" s="78"/>
-      <c r="AU30" s="78"/>
-      <c r="AV30" s="78"/>
-      <c r="AW30" s="78"/>
-      <c r="AX30" s="78"/>
-      <c r="AY30" s="78"/>
-      <c r="AZ30" s="78"/>
-      <c r="BA30" s="78"/>
-      <c r="BB30" s="78"/>
-      <c r="BC30" s="78"/>
-      <c r="BD30" s="78"/>
-      <c r="BE30" s="81"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+      <c r="U30" s="67"/>
+      <c r="V30" s="67"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="67"/>
+      <c r="Y30" s="67"/>
+      <c r="Z30" s="67"/>
+      <c r="AA30" s="67"/>
+      <c r="AB30" s="67"/>
+      <c r="AC30" s="67"/>
+      <c r="AD30" s="67"/>
+      <c r="AE30" s="67"/>
+      <c r="AF30" s="67"/>
+      <c r="AG30" s="67"/>
+      <c r="AH30" s="67"/>
+      <c r="AI30" s="67"/>
+      <c r="AJ30" s="67"/>
+      <c r="AK30" s="67"/>
+      <c r="AL30" s="67"/>
+      <c r="AM30" s="67"/>
+      <c r="AN30" s="67"/>
+      <c r="AO30" s="67"/>
+      <c r="AP30" s="68"/>
+      <c r="AQ30" s="69"/>
+      <c r="AR30" s="67"/>
+      <c r="AS30" s="67"/>
+      <c r="AT30" s="67"/>
+      <c r="AU30" s="67"/>
+      <c r="AV30" s="67"/>
+      <c r="AW30" s="67"/>
+      <c r="AX30" s="67"/>
+      <c r="AY30" s="67"/>
+      <c r="AZ30" s="67"/>
+      <c r="BA30" s="67"/>
+      <c r="BB30" s="67"/>
+      <c r="BC30" s="67"/>
+      <c r="BD30" s="67"/>
+      <c r="BE30" s="70"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="72"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="76"/>
-      <c r="N31" s="77"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="78"/>
-      <c r="R31" s="78"/>
-      <c r="S31" s="78"/>
-      <c r="T31" s="78"/>
-      <c r="U31" s="78"/>
-      <c r="V31" s="78"/>
-      <c r="W31" s="78"/>
-      <c r="X31" s="78"/>
-      <c r="Y31" s="78"/>
-      <c r="Z31" s="78"/>
-      <c r="AA31" s="78"/>
-      <c r="AB31" s="78"/>
-      <c r="AC31" s="78"/>
-      <c r="AD31" s="78"/>
-      <c r="AE31" s="78"/>
-      <c r="AF31" s="78"/>
-      <c r="AG31" s="78"/>
-      <c r="AH31" s="78"/>
-      <c r="AI31" s="78"/>
-      <c r="AJ31" s="78"/>
-      <c r="AK31" s="78"/>
-      <c r="AL31" s="78"/>
-      <c r="AM31" s="78"/>
-      <c r="AN31" s="78"/>
-      <c r="AO31" s="78"/>
-      <c r="AP31" s="79"/>
-      <c r="AQ31" s="80"/>
-      <c r="AR31" s="78"/>
-      <c r="AS31" s="78"/>
-      <c r="AT31" s="78"/>
-      <c r="AU31" s="78"/>
-      <c r="AV31" s="78"/>
-      <c r="AW31" s="78"/>
-      <c r="AX31" s="78"/>
-      <c r="AY31" s="78"/>
-      <c r="AZ31" s="78"/>
-      <c r="BA31" s="78"/>
-      <c r="BB31" s="78"/>
-      <c r="BC31" s="78"/>
-      <c r="BD31" s="78"/>
-      <c r="BE31" s="81"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+      <c r="U31" s="67"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="67"/>
+      <c r="Y31" s="67"/>
+      <c r="Z31" s="67"/>
+      <c r="AA31" s="67"/>
+      <c r="AB31" s="67"/>
+      <c r="AC31" s="67"/>
+      <c r="AD31" s="67"/>
+      <c r="AE31" s="67"/>
+      <c r="AF31" s="67"/>
+      <c r="AG31" s="67"/>
+      <c r="AH31" s="67"/>
+      <c r="AI31" s="67"/>
+      <c r="AJ31" s="67"/>
+      <c r="AK31" s="67"/>
+      <c r="AL31" s="67"/>
+      <c r="AM31" s="67"/>
+      <c r="AN31" s="67"/>
+      <c r="AO31" s="67"/>
+      <c r="AP31" s="68"/>
+      <c r="AQ31" s="69"/>
+      <c r="AR31" s="67"/>
+      <c r="AS31" s="67"/>
+      <c r="AT31" s="67"/>
+      <c r="AU31" s="67"/>
+      <c r="AV31" s="67"/>
+      <c r="AW31" s="67"/>
+      <c r="AX31" s="67"/>
+      <c r="AY31" s="67"/>
+      <c r="AZ31" s="67"/>
+      <c r="BA31" s="67"/>
+      <c r="BB31" s="67"/>
+      <c r="BC31" s="67"/>
+      <c r="BD31" s="67"/>
+      <c r="BE31" s="70"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="72"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="76"/>
-      <c r="L32" s="76"/>
-      <c r="M32" s="76"/>
-      <c r="N32" s="77"/>
-      <c r="O32" s="75"/>
-      <c r="P32" s="78"/>
-      <c r="Q32" s="78"/>
-      <c r="R32" s="78"/>
-      <c r="S32" s="78"/>
-      <c r="T32" s="78"/>
-      <c r="U32" s="78"/>
-      <c r="V32" s="78"/>
-      <c r="W32" s="78"/>
-      <c r="X32" s="78"/>
-      <c r="Y32" s="78"/>
-      <c r="Z32" s="78"/>
-      <c r="AA32" s="78"/>
-      <c r="AB32" s="78"/>
-      <c r="AC32" s="78"/>
-      <c r="AD32" s="78"/>
-      <c r="AE32" s="78"/>
-      <c r="AF32" s="78"/>
-      <c r="AG32" s="78"/>
-      <c r="AH32" s="78"/>
-      <c r="AI32" s="78"/>
-      <c r="AJ32" s="78"/>
-      <c r="AK32" s="78"/>
-      <c r="AL32" s="78"/>
-      <c r="AM32" s="78"/>
-      <c r="AN32" s="78"/>
-      <c r="AO32" s="78"/>
-      <c r="AP32" s="79"/>
-      <c r="AQ32" s="80"/>
-      <c r="AR32" s="78"/>
-      <c r="AS32" s="78"/>
-      <c r="AT32" s="78"/>
-      <c r="AU32" s="78"/>
-      <c r="AV32" s="78"/>
-      <c r="AW32" s="78"/>
-      <c r="AX32" s="78"/>
-      <c r="AY32" s="78"/>
-      <c r="AZ32" s="78"/>
-      <c r="BA32" s="78"/>
-      <c r="BB32" s="78"/>
-      <c r="BC32" s="78"/>
-      <c r="BD32" s="78"/>
-      <c r="BE32" s="81"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="65"/>
+      <c r="L32" s="65"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="64"/>
+      <c r="P32" s="67"/>
+      <c r="Q32" s="67"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="67"/>
+      <c r="U32" s="67"/>
+      <c r="V32" s="67"/>
+      <c r="W32" s="67"/>
+      <c r="X32" s="67"/>
+      <c r="Y32" s="67"/>
+      <c r="Z32" s="67"/>
+      <c r="AA32" s="67"/>
+      <c r="AB32" s="67"/>
+      <c r="AC32" s="67"/>
+      <c r="AD32" s="67"/>
+      <c r="AE32" s="67"/>
+      <c r="AF32" s="67"/>
+      <c r="AG32" s="67"/>
+      <c r="AH32" s="67"/>
+      <c r="AI32" s="67"/>
+      <c r="AJ32" s="67"/>
+      <c r="AK32" s="67"/>
+      <c r="AL32" s="67"/>
+      <c r="AM32" s="67"/>
+      <c r="AN32" s="67"/>
+      <c r="AO32" s="67"/>
+      <c r="AP32" s="68"/>
+      <c r="AQ32" s="69"/>
+      <c r="AR32" s="67"/>
+      <c r="AS32" s="67"/>
+      <c r="AT32" s="67"/>
+      <c r="AU32" s="67"/>
+      <c r="AV32" s="67"/>
+      <c r="AW32" s="67"/>
+      <c r="AX32" s="67"/>
+      <c r="AY32" s="67"/>
+      <c r="AZ32" s="67"/>
+      <c r="BA32" s="67"/>
+      <c r="BB32" s="67"/>
+      <c r="BC32" s="67"/>
+      <c r="BD32" s="67"/>
+      <c r="BE32" s="70"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="72"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="76"/>
-      <c r="L33" s="76"/>
-      <c r="M33" s="76"/>
-      <c r="N33" s="77"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="78"/>
-      <c r="Q33" s="78"/>
-      <c r="R33" s="78"/>
-      <c r="S33" s="78"/>
-      <c r="T33" s="78"/>
-      <c r="U33" s="78"/>
-      <c r="V33" s="78"/>
-      <c r="W33" s="78"/>
-      <c r="X33" s="78"/>
-      <c r="Y33" s="78"/>
-      <c r="Z33" s="78"/>
-      <c r="AA33" s="78"/>
-      <c r="AB33" s="78"/>
-      <c r="AC33" s="78"/>
-      <c r="AD33" s="78"/>
-      <c r="AE33" s="78"/>
-      <c r="AF33" s="78"/>
-      <c r="AG33" s="78"/>
-      <c r="AH33" s="78"/>
-      <c r="AI33" s="78"/>
-      <c r="AJ33" s="78"/>
-      <c r="AK33" s="78"/>
-      <c r="AL33" s="78"/>
-      <c r="AM33" s="78"/>
-      <c r="AN33" s="78"/>
-      <c r="AO33" s="78"/>
-      <c r="AP33" s="79"/>
-      <c r="AQ33" s="80"/>
-      <c r="AR33" s="78"/>
-      <c r="AS33" s="78"/>
-      <c r="AT33" s="78"/>
-      <c r="AU33" s="78"/>
-      <c r="AV33" s="78"/>
-      <c r="AW33" s="78"/>
-      <c r="AX33" s="78"/>
-      <c r="AY33" s="78"/>
-      <c r="AZ33" s="78"/>
-      <c r="BA33" s="78"/>
-      <c r="BB33" s="78"/>
-      <c r="BC33" s="78"/>
-      <c r="BD33" s="78"/>
-      <c r="BE33" s="81"/>
+      <c r="A33" s="61"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="65"/>
+      <c r="L33" s="65"/>
+      <c r="M33" s="65"/>
+      <c r="N33" s="66"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="67"/>
+      <c r="Q33" s="67"/>
+      <c r="R33" s="67"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="67"/>
+      <c r="U33" s="67"/>
+      <c r="V33" s="67"/>
+      <c r="W33" s="67"/>
+      <c r="X33" s="67"/>
+      <c r="Y33" s="67"/>
+      <c r="Z33" s="67"/>
+      <c r="AA33" s="67"/>
+      <c r="AB33" s="67"/>
+      <c r="AC33" s="67"/>
+      <c r="AD33" s="67"/>
+      <c r="AE33" s="67"/>
+      <c r="AF33" s="67"/>
+      <c r="AG33" s="67"/>
+      <c r="AH33" s="67"/>
+      <c r="AI33" s="67"/>
+      <c r="AJ33" s="67"/>
+      <c r="AK33" s="67"/>
+      <c r="AL33" s="67"/>
+      <c r="AM33" s="67"/>
+      <c r="AN33" s="67"/>
+      <c r="AO33" s="67"/>
+      <c r="AP33" s="68"/>
+      <c r="AQ33" s="69"/>
+      <c r="AR33" s="67"/>
+      <c r="AS33" s="67"/>
+      <c r="AT33" s="67"/>
+      <c r="AU33" s="67"/>
+      <c r="AV33" s="67"/>
+      <c r="AW33" s="67"/>
+      <c r="AX33" s="67"/>
+      <c r="AY33" s="67"/>
+      <c r="AZ33" s="67"/>
+      <c r="BA33" s="67"/>
+      <c r="BB33" s="67"/>
+      <c r="BC33" s="67"/>
+      <c r="BD33" s="67"/>
+      <c r="BE33" s="70"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="72"/>
-      <c r="B34" s="73"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
-      <c r="K34" s="76"/>
-      <c r="L34" s="76"/>
-      <c r="M34" s="76"/>
-      <c r="N34" s="77"/>
-      <c r="O34" s="75"/>
-      <c r="P34" s="78"/>
-      <c r="Q34" s="78"/>
-      <c r="R34" s="78"/>
-      <c r="S34" s="78"/>
-      <c r="T34" s="78"/>
-      <c r="U34" s="78"/>
-      <c r="V34" s="78"/>
-      <c r="W34" s="78"/>
-      <c r="X34" s="78"/>
-      <c r="Y34" s="78"/>
-      <c r="Z34" s="78"/>
-      <c r="AA34" s="78"/>
-      <c r="AB34" s="78"/>
-      <c r="AC34" s="78"/>
-      <c r="AD34" s="78"/>
-      <c r="AE34" s="78"/>
-      <c r="AF34" s="78"/>
-      <c r="AG34" s="78"/>
-      <c r="AH34" s="78"/>
-      <c r="AI34" s="78"/>
-      <c r="AJ34" s="78"/>
-      <c r="AK34" s="78"/>
-      <c r="AL34" s="78"/>
-      <c r="AM34" s="78"/>
-      <c r="AN34" s="78"/>
-      <c r="AO34" s="78"/>
-      <c r="AP34" s="79"/>
-      <c r="AQ34" s="80"/>
-      <c r="AR34" s="78"/>
-      <c r="AS34" s="78"/>
-      <c r="AT34" s="78"/>
-      <c r="AU34" s="78"/>
-      <c r="AV34" s="78"/>
-      <c r="AW34" s="78"/>
-      <c r="AX34" s="78"/>
-      <c r="AY34" s="78"/>
-      <c r="AZ34" s="78"/>
-      <c r="BA34" s="78"/>
-      <c r="BB34" s="78"/>
-      <c r="BC34" s="78"/>
-      <c r="BD34" s="78"/>
-      <c r="BE34" s="81"/>
+      <c r="A34" s="61"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="66"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="67"/>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="67"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="67"/>
+      <c r="U34" s="67"/>
+      <c r="V34" s="67"/>
+      <c r="W34" s="67"/>
+      <c r="X34" s="67"/>
+      <c r="Y34" s="67"/>
+      <c r="Z34" s="67"/>
+      <c r="AA34" s="67"/>
+      <c r="AB34" s="67"/>
+      <c r="AC34" s="67"/>
+      <c r="AD34" s="67"/>
+      <c r="AE34" s="67"/>
+      <c r="AF34" s="67"/>
+      <c r="AG34" s="67"/>
+      <c r="AH34" s="67"/>
+      <c r="AI34" s="67"/>
+      <c r="AJ34" s="67"/>
+      <c r="AK34" s="67"/>
+      <c r="AL34" s="67"/>
+      <c r="AM34" s="67"/>
+      <c r="AN34" s="67"/>
+      <c r="AO34" s="67"/>
+      <c r="AP34" s="68"/>
+      <c r="AQ34" s="69"/>
+      <c r="AR34" s="67"/>
+      <c r="AS34" s="67"/>
+      <c r="AT34" s="67"/>
+      <c r="AU34" s="67"/>
+      <c r="AV34" s="67"/>
+      <c r="AW34" s="67"/>
+      <c r="AX34" s="67"/>
+      <c r="AY34" s="67"/>
+      <c r="AZ34" s="67"/>
+      <c r="BA34" s="67"/>
+      <c r="BB34" s="67"/>
+      <c r="BC34" s="67"/>
+      <c r="BD34" s="67"/>
+      <c r="BE34" s="70"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="88"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="91"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="91"/>
-      <c r="P35" s="94"/>
-      <c r="Q35" s="94"/>
-      <c r="R35" s="94"/>
-      <c r="S35" s="94"/>
-      <c r="T35" s="94"/>
-      <c r="U35" s="94"/>
-      <c r="V35" s="94"/>
-      <c r="W35" s="94"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="94"/>
-      <c r="Z35" s="94"/>
-      <c r="AA35" s="94"/>
-      <c r="AB35" s="94"/>
-      <c r="AC35" s="94"/>
-      <c r="AD35" s="94"/>
-      <c r="AE35" s="94"/>
-      <c r="AF35" s="94"/>
-      <c r="AG35" s="94"/>
-      <c r="AH35" s="94"/>
-      <c r="AI35" s="94"/>
-      <c r="AJ35" s="94"/>
-      <c r="AK35" s="94"/>
-      <c r="AL35" s="94"/>
-      <c r="AM35" s="94"/>
-      <c r="AN35" s="94"/>
-      <c r="AO35" s="94"/>
-      <c r="AP35" s="95"/>
-      <c r="AQ35" s="96"/>
-      <c r="AR35" s="94"/>
-      <c r="AS35" s="94"/>
-      <c r="AT35" s="94"/>
-      <c r="AU35" s="94"/>
-      <c r="AV35" s="94"/>
-      <c r="AW35" s="94"/>
-      <c r="AX35" s="94"/>
-      <c r="AY35" s="94"/>
-      <c r="AZ35" s="94"/>
-      <c r="BA35" s="94"/>
-      <c r="BB35" s="94"/>
-      <c r="BC35" s="94"/>
-      <c r="BD35" s="94"/>
-      <c r="BE35" s="97"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="56"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="57"/>
+      <c r="Q35" s="57"/>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="57"/>
+      <c r="V35" s="57"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="57"/>
+      <c r="Y35" s="57"/>
+      <c r="Z35" s="57"/>
+      <c r="AA35" s="57"/>
+      <c r="AB35" s="57"/>
+      <c r="AC35" s="57"/>
+      <c r="AD35" s="57"/>
+      <c r="AE35" s="57"/>
+      <c r="AF35" s="57"/>
+      <c r="AG35" s="57"/>
+      <c r="AH35" s="57"/>
+      <c r="AI35" s="57"/>
+      <c r="AJ35" s="57"/>
+      <c r="AK35" s="57"/>
+      <c r="AL35" s="57"/>
+      <c r="AM35" s="57"/>
+      <c r="AN35" s="57"/>
+      <c r="AO35" s="57"/>
+      <c r="AP35" s="58"/>
+      <c r="AQ35" s="59"/>
+      <c r="AR35" s="57"/>
+      <c r="AS35" s="57"/>
+      <c r="AT35" s="57"/>
+      <c r="AU35" s="57"/>
+      <c r="AV35" s="57"/>
+      <c r="AW35" s="57"/>
+      <c r="AX35" s="57"/>
+      <c r="AY35" s="57"/>
+      <c r="AZ35" s="57"/>
+      <c r="BA35" s="57"/>
+      <c r="BB35" s="57"/>
+      <c r="BC35" s="57"/>
+      <c r="BD35" s="57"/>
+      <c r="BE35" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="H11:N11"/>
     <mergeCell ref="O11:AP11"/>
@@ -16639,27 +17033,98 @@
     <mergeCell ref="H10:N10"/>
     <mergeCell ref="O10:AP10"/>
     <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="AQ34:BE34"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
